--- a/public/templates/events-import.xlsx
+++ b/public/templates/events-import.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="活动导入" sheetId="1" r:id="Re189c04613994e0c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="填写说明" sheetId="2" r:id="Rfcd0da21ef97452b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="活动导入" sheetId="1" r:id="R1e2e94096a51434e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="填写说明" sheetId="2" r:id="R8515639d00464497"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,7 +18,7 @@
     <x:numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
     <x:numFmt numFmtId="201" formatCode="hh:mm"/>
   </x:numFmts>
-  <x:fonts count="3">
+  <x:fonts count="4">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -31,6 +31,12 @@
       <x:b/>
       <x:sz val="11"/>
       <x:color rgb="FFFFFFFF"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF333333"/>
       <x:name val="Arial"/>
     </x:font>
   </x:fonts>
@@ -58,7 +64,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="10">
+  <x:cellXfs count="11">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -81,6 +87,9 @@
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="201" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -285,13 +294,13 @@
   <x:cols>
     <x:col min="1" max="1" width="20" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="20" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="20" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="30" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="30" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="30" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="35" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="35" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="35" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="35" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="30" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="20" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="20" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="30" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="20" hidden="0" customWidth="1"/>
     <x:col min="11" max="11" width="20" hidden="0" customWidth="1"/>
     <x:col min="12" max="12" width="38" hidden="0" customWidth="1"/>
@@ -300,145 +309,129 @@
     <x:col min="15" max="15" width="20" hidden="0" customWidth="1"/>
     <x:col min="16" max="16" width="20" hidden="0" customWidth="1"/>
     <x:col min="17" max="17" width="20" hidden="0" customWidth="1"/>
-    <x:col min="18" max="18" width="20" hidden="0" customWidth="1"/>
-    <x:col min="19" max="19" width="20" hidden="0" customWidth="1"/>
-    <x:col min="20" max="20" width="20" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="34" customHeight="1">
       <x:c r="A1" s="4" t="str">
-        <x:v>行用途</x:v>
+        <x:v>date</x:v>
       </x:c>
       <x:c r="B1" s="4" t="str">
-        <x:v>日期</x:v>
+        <x:v>time</x:v>
       </x:c>
       <x:c r="C1" s="4" t="str">
-        <x:v>时间</x:v>
+        <x:v>name</x:v>
       </x:c>
       <x:c r="D1" s="4" t="str">
-        <x:v>艺人名称</x:v>
+        <x:v>activity</x:v>
       </x:c>
       <x:c r="E1" s="4" t="str">
-        <x:v>活动名称</x:v>
+        <x:v>venue</x:v>
       </x:c>
       <x:c r="F1" s="4" t="str">
-        <x:v>场地</x:v>
+        <x:v>city</x:v>
       </x:c>
       <x:c r="G1" s="4" t="str">
-        <x:v>城市</x:v>
+        <x:v>category</x:v>
       </x:c>
       <x:c r="H1" s="4" t="str">
-        <x:v>活动类型</x:v>
+        <x:v>region</x:v>
       </x:c>
       <x:c r="I1" s="4" t="str">
-        <x:v>地区</x:v>
+        <x:v>participation_condition</x:v>
       </x:c>
       <x:c r="J1" s="4" t="str">
-        <x:v>参与方式</x:v>
+        <x:v>roll_call</x:v>
       </x:c>
       <x:c r="K1" s="4" t="str">
-        <x:v>点名</x:v>
+        <x:v>ticket_url</x:v>
       </x:c>
       <x:c r="L1" s="4" t="str">
-        <x:v>票务链接</x:v>
+        <x:v>picture_url</x:v>
       </x:c>
       <x:c r="M1" s="4" t="str">
-        <x:v>图片链接</x:v>
+        <x:v>note</x:v>
       </x:c>
       <x:c r="N1" s="4" t="str">
-        <x:v>备注</x:v>
+        <x:v>sale_date</x:v>
       </x:c>
       <x:c r="O1" s="4" t="str">
-        <x:v>公司</x:v>
+        <x:v>sale_time</x:v>
       </x:c>
       <x:c r="P1" s="4" t="str">
-        <x:v>艺人类别</x:v>
+        <x:v>sale_end_date</x:v>
       </x:c>
       <x:c r="Q1" s="4" t="str">
-        <x:v>开票日期</x:v>
-      </x:c>
-      <x:c r="R1" s="4" t="str">
-        <x:v>开票时间</x:v>
-      </x:c>
-      <x:c r="S1" s="4" t="str">
-        <x:v>开票结束日期</x:v>
-      </x:c>
-      <x:c r="T1" s="4" t="str">
-        <x:v>开票结束时间</x:v>
+        <x:v>sale_end_time</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="64" customHeight="1">
-      <x:c r="A2" s="5" t="str">
-        <x:v>示例</x:v>
-      </x:c>
-      <x:c r="B2" s="6" t="n">
-        <x:v>46310</x:v>
-      </x:c>
-      <x:c r="C2" s="8" t="n">
-        <x:v>0.5833333333333334</x:v>
-      </x:c>
-      <x:c r="D2" s="5" t="str">
-        <x:v>请替换为资料库中的艺人显示名称</x:v>
-      </x:c>
-      <x:c r="E2" s="5" t="str">
-        <x:v>示例活动（请替换）</x:v>
-      </x:c>
-      <x:c r="F2" s="5" t="str">
-        <x:v>示例商场一楼</x:v>
-      </x:c>
-      <x:c r="G2" s="5" t="str">
-        <x:v>曼谷</x:v>
-      </x:c>
-      <x:c r="H2" s="5" t="str">
-        <x:v>站台活动</x:v>
-      </x:c>
-      <x:c r="I2" s="5" t="str">
-        <x:v>泰国</x:v>
-      </x:c>
+      <x:c r="A2" s="10" t="str">
+        <x:v>以下为示例，请填写完成后删掉</x:v>
+      </x:c>
+      <x:c r="B2" s="10" t="str"/>
+      <x:c r="C2" s="10" t="str"/>
+      <x:c r="D2" s="10" t="str"/>
+      <x:c r="E2" s="10" t="str"/>
+      <x:c r="F2" s="10" t="str"/>
+      <x:c r="G2" s="5" t="str"/>
+      <x:c r="H2" s="5" t="str"/>
+      <x:c r="I2" s="5" t="str"/>
       <x:c r="J2" s="5" t="str"/>
-      <x:c r="K2" s="5" t="str">
-        <x:v>否</x:v>
-      </x:c>
-      <x:c r="L2" s="5" t="str">
-        <x:v>https://example.com/event</x:v>
-      </x:c>
+      <x:c r="K2" s="5" t="str"/>
+      <x:c r="L2" s="5" t="str"/>
       <x:c r="M2" s="5" t="str"/>
-      <x:c r="N2" s="5" t="str">
-        <x:v>请替换为真实活动；行用途改为导入后才会提交</x:v>
-      </x:c>
+      <x:c r="N2" s="5" t="str"/>
       <x:c r="O2" s="5" t="str"/>
       <x:c r="P2" s="5" t="str"/>
-      <x:c r="Q2" s="6" t="str"/>
-      <x:c r="R2" s="8" t="str"/>
-      <x:c r="S2" s="6" t="str"/>
-      <x:c r="T2" s="8" t="str"/>
-    </x:row>
-    <x:row r="3">
-      <x:c r="A3" s="1"/>
-      <x:c r="B3" s="7"/>
-      <x:c r="C3" s="9"/>
-      <x:c r="D3" s="1"/>
-      <x:c r="E3" s="1"/>
-      <x:c r="F3" s="1"/>
-      <x:c r="G3" s="1"/>
-      <x:c r="H3" s="1"/>
-      <x:c r="I3" s="1"/>
-      <x:c r="J3" s="1"/>
-      <x:c r="K3" s="1"/>
-      <x:c r="L3" s="1"/>
-      <x:c r="M3" s="1"/>
-      <x:c r="N3" s="1"/>
-      <x:c r="O3" s="1"/>
-      <x:c r="P3" s="1"/>
-      <x:c r="Q3" s="7"/>
-      <x:c r="R3" s="9"/>
-      <x:c r="S3" s="7"/>
-      <x:c r="T3" s="9"/>
+      <x:c r="Q2" s="5" t="str"/>
+    </x:row>
+    <x:row r="3" ht="105" customHeight="1">
+      <x:c r="A3" s="6" t="n">
+        <x:v>46295</x:v>
+      </x:c>
+      <x:c r="B3" s="8" t="n">
+        <x:v>0.7916666666666666</x:v>
+      </x:c>
+      <x:c r="C3" s="5" t="str">
+        <x:v>Auau Thanaphum / Patji Jirachart / Ryujin Tinnapat / Save Worapong</x:v>
+      </x:c>
+      <x:c r="D3" s="5" t="str">
+        <x:v>Flex Talk电台</x:v>
+      </x:c>
+      <x:c r="E3" s="5" t="str">
+        <x:v>Flex 104.5 Studio</x:v>
+      </x:c>
+      <x:c r="F3" s="5" t="str">
+        <x:v>线上直播</x:v>
+      </x:c>
+      <x:c r="G3" s="5" t="str">
+        <x:v>影视宣传</x:v>
+      </x:c>
+      <x:c r="H3" s="5" t="str">
+        <x:v>泰国</x:v>
+      </x:c>
+      <x:c r="I3" s="5" t="str"/>
+      <x:c r="J3" s="5" t="str">
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="K3" s="5" t="str">
+        <x:v>https://x.com/Flex_Connect/status/2104085029093843014</x:v>
+      </x:c>
+      <x:c r="L3" s="5" t="str">
+        <x:v>https://pbs.twimg.com/media/HTM2A3RasAAEAYT.jpg</x:v>
+      </x:c>
+      <x:c r="M3" s="5" t="str">
+        <x:v>电台节目；粉丝可到工作室附近加油，详情后续公布</x:v>
+      </x:c>
+      <x:c r="N3" s="6" t="str"/>
+      <x:c r="O3" s="8" t="str"/>
+      <x:c r="P3" s="6" t="str"/>
+      <x:c r="Q3" s="8" t="str"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="1"/>
-      <x:c r="B4" s="7"/>
-      <x:c r="C4" s="9"/>
+      <x:c r="A4" s="7"/>
+      <x:c r="B4" s="9"/>
+      <x:c r="C4" s="1"/>
       <x:c r="D4" s="1"/>
       <x:c r="E4" s="1"/>
       <x:c r="F4" s="1"/>
@@ -449,18 +442,15 @@
       <x:c r="K4" s="1"/>
       <x:c r="L4" s="1"/>
       <x:c r="M4" s="1"/>
-      <x:c r="N4" s="1"/>
-      <x:c r="O4" s="1"/>
-      <x:c r="P4" s="1"/>
-      <x:c r="Q4" s="7"/>
-      <x:c r="R4" s="9"/>
-      <x:c r="S4" s="7"/>
-      <x:c r="T4" s="9"/>
+      <x:c r="N4" s="7"/>
+      <x:c r="O4" s="9"/>
+      <x:c r="P4" s="7"/>
+      <x:c r="Q4" s="9"/>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="1"/>
-      <x:c r="B5" s="7"/>
-      <x:c r="C5" s="9"/>
+      <x:c r="A5" s="7"/>
+      <x:c r="B5" s="9"/>
+      <x:c r="C5" s="1"/>
       <x:c r="D5" s="1"/>
       <x:c r="E5" s="1"/>
       <x:c r="F5" s="1"/>
@@ -471,18 +461,15 @@
       <x:c r="K5" s="1"/>
       <x:c r="L5" s="1"/>
       <x:c r="M5" s="1"/>
-      <x:c r="N5" s="1"/>
-      <x:c r="O5" s="1"/>
-      <x:c r="P5" s="1"/>
-      <x:c r="Q5" s="7"/>
-      <x:c r="R5" s="9"/>
-      <x:c r="S5" s="7"/>
-      <x:c r="T5" s="9"/>
+      <x:c r="N5" s="7"/>
+      <x:c r="O5" s="9"/>
+      <x:c r="P5" s="7"/>
+      <x:c r="Q5" s="9"/>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="1"/>
-      <x:c r="B6" s="7"/>
-      <x:c r="C6" s="9"/>
+      <x:c r="A6" s="7"/>
+      <x:c r="B6" s="9"/>
+      <x:c r="C6" s="1"/>
       <x:c r="D6" s="1"/>
       <x:c r="E6" s="1"/>
       <x:c r="F6" s="1"/>
@@ -493,18 +480,15 @@
       <x:c r="K6" s="1"/>
       <x:c r="L6" s="1"/>
       <x:c r="M6" s="1"/>
-      <x:c r="N6" s="1"/>
-      <x:c r="O6" s="1"/>
-      <x:c r="P6" s="1"/>
-      <x:c r="Q6" s="7"/>
-      <x:c r="R6" s="9"/>
-      <x:c r="S6" s="7"/>
-      <x:c r="T6" s="9"/>
+      <x:c r="N6" s="7"/>
+      <x:c r="O6" s="9"/>
+      <x:c r="P6" s="7"/>
+      <x:c r="Q6" s="9"/>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="1"/>
-      <x:c r="B7" s="7"/>
-      <x:c r="C7" s="9"/>
+      <x:c r="A7" s="7"/>
+      <x:c r="B7" s="9"/>
+      <x:c r="C7" s="1"/>
       <x:c r="D7" s="1"/>
       <x:c r="E7" s="1"/>
       <x:c r="F7" s="1"/>
@@ -515,18 +499,15 @@
       <x:c r="K7" s="1"/>
       <x:c r="L7" s="1"/>
       <x:c r="M7" s="1"/>
-      <x:c r="N7" s="1"/>
-      <x:c r="O7" s="1"/>
-      <x:c r="P7" s="1"/>
-      <x:c r="Q7" s="7"/>
-      <x:c r="R7" s="9"/>
-      <x:c r="S7" s="7"/>
-      <x:c r="T7" s="9"/>
+      <x:c r="N7" s="7"/>
+      <x:c r="O7" s="9"/>
+      <x:c r="P7" s="7"/>
+      <x:c r="Q7" s="9"/>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="1"/>
-      <x:c r="B8" s="7"/>
-      <x:c r="C8" s="9"/>
+      <x:c r="A8" s="7"/>
+      <x:c r="B8" s="9"/>
+      <x:c r="C8" s="1"/>
       <x:c r="D8" s="1"/>
       <x:c r="E8" s="1"/>
       <x:c r="F8" s="1"/>
@@ -537,18 +518,15 @@
       <x:c r="K8" s="1"/>
       <x:c r="L8" s="1"/>
       <x:c r="M8" s="1"/>
-      <x:c r="N8" s="1"/>
-      <x:c r="O8" s="1"/>
-      <x:c r="P8" s="1"/>
-      <x:c r="Q8" s="7"/>
-      <x:c r="R8" s="9"/>
-      <x:c r="S8" s="7"/>
-      <x:c r="T8" s="9"/>
+      <x:c r="N8" s="7"/>
+      <x:c r="O8" s="9"/>
+      <x:c r="P8" s="7"/>
+      <x:c r="Q8" s="9"/>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="1"/>
-      <x:c r="B9" s="7"/>
-      <x:c r="C9" s="9"/>
+      <x:c r="A9" s="7"/>
+      <x:c r="B9" s="9"/>
+      <x:c r="C9" s="1"/>
       <x:c r="D9" s="1"/>
       <x:c r="E9" s="1"/>
       <x:c r="F9" s="1"/>
@@ -559,18 +537,15 @@
       <x:c r="K9" s="1"/>
       <x:c r="L9" s="1"/>
       <x:c r="M9" s="1"/>
-      <x:c r="N9" s="1"/>
-      <x:c r="O9" s="1"/>
-      <x:c r="P9" s="1"/>
-      <x:c r="Q9" s="7"/>
-      <x:c r="R9" s="9"/>
-      <x:c r="S9" s="7"/>
-      <x:c r="T9" s="9"/>
+      <x:c r="N9" s="7"/>
+      <x:c r="O9" s="9"/>
+      <x:c r="P9" s="7"/>
+      <x:c r="Q9" s="9"/>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="1"/>
-      <x:c r="B10" s="7"/>
-      <x:c r="C10" s="9"/>
+      <x:c r="A10" s="7"/>
+      <x:c r="B10" s="9"/>
+      <x:c r="C10" s="1"/>
       <x:c r="D10" s="1"/>
       <x:c r="E10" s="1"/>
       <x:c r="F10" s="1"/>
@@ -581,18 +556,15 @@
       <x:c r="K10" s="1"/>
       <x:c r="L10" s="1"/>
       <x:c r="M10" s="1"/>
-      <x:c r="N10" s="1"/>
-      <x:c r="O10" s="1"/>
-      <x:c r="P10" s="1"/>
-      <x:c r="Q10" s="7"/>
-      <x:c r="R10" s="9"/>
-      <x:c r="S10" s="7"/>
-      <x:c r="T10" s="9"/>
+      <x:c r="N10" s="7"/>
+      <x:c r="O10" s="9"/>
+      <x:c r="P10" s="7"/>
+      <x:c r="Q10" s="9"/>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="1"/>
-      <x:c r="B11" s="7"/>
-      <x:c r="C11" s="9"/>
+      <x:c r="A11" s="7"/>
+      <x:c r="B11" s="9"/>
+      <x:c r="C11" s="1"/>
       <x:c r="D11" s="1"/>
       <x:c r="E11" s="1"/>
       <x:c r="F11" s="1"/>
@@ -603,18 +575,15 @@
       <x:c r="K11" s="1"/>
       <x:c r="L11" s="1"/>
       <x:c r="M11" s="1"/>
-      <x:c r="N11" s="1"/>
-      <x:c r="O11" s="1"/>
-      <x:c r="P11" s="1"/>
-      <x:c r="Q11" s="7"/>
-      <x:c r="R11" s="9"/>
-      <x:c r="S11" s="7"/>
-      <x:c r="T11" s="9"/>
+      <x:c r="N11" s="7"/>
+      <x:c r="O11" s="9"/>
+      <x:c r="P11" s="7"/>
+      <x:c r="Q11" s="9"/>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="1"/>
-      <x:c r="B12" s="7"/>
-      <x:c r="C12" s="9"/>
+      <x:c r="A12" s="7"/>
+      <x:c r="B12" s="9"/>
+      <x:c r="C12" s="1"/>
       <x:c r="D12" s="1"/>
       <x:c r="E12" s="1"/>
       <x:c r="F12" s="1"/>
@@ -625,18 +594,15 @@
       <x:c r="K12" s="1"/>
       <x:c r="L12" s="1"/>
       <x:c r="M12" s="1"/>
-      <x:c r="N12" s="1"/>
-      <x:c r="O12" s="1"/>
-      <x:c r="P12" s="1"/>
-      <x:c r="Q12" s="7"/>
-      <x:c r="R12" s="9"/>
-      <x:c r="S12" s="7"/>
-      <x:c r="T12" s="9"/>
+      <x:c r="N12" s="7"/>
+      <x:c r="O12" s="9"/>
+      <x:c r="P12" s="7"/>
+      <x:c r="Q12" s="9"/>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="1"/>
-      <x:c r="B13" s="7"/>
-      <x:c r="C13" s="9"/>
+      <x:c r="A13" s="7"/>
+      <x:c r="B13" s="9"/>
+      <x:c r="C13" s="1"/>
       <x:c r="D13" s="1"/>
       <x:c r="E13" s="1"/>
       <x:c r="F13" s="1"/>
@@ -647,18 +613,15 @@
       <x:c r="K13" s="1"/>
       <x:c r="L13" s="1"/>
       <x:c r="M13" s="1"/>
-      <x:c r="N13" s="1"/>
-      <x:c r="O13" s="1"/>
-      <x:c r="P13" s="1"/>
-      <x:c r="Q13" s="7"/>
-      <x:c r="R13" s="9"/>
-      <x:c r="S13" s="7"/>
-      <x:c r="T13" s="9"/>
+      <x:c r="N13" s="7"/>
+      <x:c r="O13" s="9"/>
+      <x:c r="P13" s="7"/>
+      <x:c r="Q13" s="9"/>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="1"/>
-      <x:c r="B14" s="7"/>
-      <x:c r="C14" s="9"/>
+      <x:c r="A14" s="7"/>
+      <x:c r="B14" s="9"/>
+      <x:c r="C14" s="1"/>
       <x:c r="D14" s="1"/>
       <x:c r="E14" s="1"/>
       <x:c r="F14" s="1"/>
@@ -669,18 +632,15 @@
       <x:c r="K14" s="1"/>
       <x:c r="L14" s="1"/>
       <x:c r="M14" s="1"/>
-      <x:c r="N14" s="1"/>
-      <x:c r="O14" s="1"/>
-      <x:c r="P14" s="1"/>
-      <x:c r="Q14" s="7"/>
-      <x:c r="R14" s="9"/>
-      <x:c r="S14" s="7"/>
-      <x:c r="T14" s="9"/>
+      <x:c r="N14" s="7"/>
+      <x:c r="O14" s="9"/>
+      <x:c r="P14" s="7"/>
+      <x:c r="Q14" s="9"/>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="1"/>
-      <x:c r="B15" s="7"/>
-      <x:c r="C15" s="9"/>
+      <x:c r="A15" s="7"/>
+      <x:c r="B15" s="9"/>
+      <x:c r="C15" s="1"/>
       <x:c r="D15" s="1"/>
       <x:c r="E15" s="1"/>
       <x:c r="F15" s="1"/>
@@ -691,18 +651,15 @@
       <x:c r="K15" s="1"/>
       <x:c r="L15" s="1"/>
       <x:c r="M15" s="1"/>
-      <x:c r="N15" s="1"/>
-      <x:c r="O15" s="1"/>
-      <x:c r="P15" s="1"/>
-      <x:c r="Q15" s="7"/>
-      <x:c r="R15" s="9"/>
-      <x:c r="S15" s="7"/>
-      <x:c r="T15" s="9"/>
+      <x:c r="N15" s="7"/>
+      <x:c r="O15" s="9"/>
+      <x:c r="P15" s="7"/>
+      <x:c r="Q15" s="9"/>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" s="1"/>
-      <x:c r="B16" s="7"/>
-      <x:c r="C16" s="9"/>
+      <x:c r="A16" s="7"/>
+      <x:c r="B16" s="9"/>
+      <x:c r="C16" s="1"/>
       <x:c r="D16" s="1"/>
       <x:c r="E16" s="1"/>
       <x:c r="F16" s="1"/>
@@ -713,18 +670,15 @@
       <x:c r="K16" s="1"/>
       <x:c r="L16" s="1"/>
       <x:c r="M16" s="1"/>
-      <x:c r="N16" s="1"/>
-      <x:c r="O16" s="1"/>
-      <x:c r="P16" s="1"/>
-      <x:c r="Q16" s="7"/>
-      <x:c r="R16" s="9"/>
-      <x:c r="S16" s="7"/>
-      <x:c r="T16" s="9"/>
+      <x:c r="N16" s="7"/>
+      <x:c r="O16" s="9"/>
+      <x:c r="P16" s="7"/>
+      <x:c r="Q16" s="9"/>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" s="1"/>
-      <x:c r="B17" s="7"/>
-      <x:c r="C17" s="9"/>
+      <x:c r="A17" s="7"/>
+      <x:c r="B17" s="9"/>
+      <x:c r="C17" s="1"/>
       <x:c r="D17" s="1"/>
       <x:c r="E17" s="1"/>
       <x:c r="F17" s="1"/>
@@ -735,18 +689,15 @@
       <x:c r="K17" s="1"/>
       <x:c r="L17" s="1"/>
       <x:c r="M17" s="1"/>
-      <x:c r="N17" s="1"/>
-      <x:c r="O17" s="1"/>
-      <x:c r="P17" s="1"/>
-      <x:c r="Q17" s="7"/>
-      <x:c r="R17" s="9"/>
-      <x:c r="S17" s="7"/>
-      <x:c r="T17" s="9"/>
+      <x:c r="N17" s="7"/>
+      <x:c r="O17" s="9"/>
+      <x:c r="P17" s="7"/>
+      <x:c r="Q17" s="9"/>
     </x:row>
     <x:row r="18">
-      <x:c r="A18" s="1"/>
-      <x:c r="B18" s="7"/>
-      <x:c r="C18" s="9"/>
+      <x:c r="A18" s="7"/>
+      <x:c r="B18" s="9"/>
+      <x:c r="C18" s="1"/>
       <x:c r="D18" s="1"/>
       <x:c r="E18" s="1"/>
       <x:c r="F18" s="1"/>
@@ -757,18 +708,15 @@
       <x:c r="K18" s="1"/>
       <x:c r="L18" s="1"/>
       <x:c r="M18" s="1"/>
-      <x:c r="N18" s="1"/>
-      <x:c r="O18" s="1"/>
-      <x:c r="P18" s="1"/>
-      <x:c r="Q18" s="7"/>
-      <x:c r="R18" s="9"/>
-      <x:c r="S18" s="7"/>
-      <x:c r="T18" s="9"/>
+      <x:c r="N18" s="7"/>
+      <x:c r="O18" s="9"/>
+      <x:c r="P18" s="7"/>
+      <x:c r="Q18" s="9"/>
     </x:row>
     <x:row r="19">
-      <x:c r="A19" s="1"/>
-      <x:c r="B19" s="7"/>
-      <x:c r="C19" s="9"/>
+      <x:c r="A19" s="7"/>
+      <x:c r="B19" s="9"/>
+      <x:c r="C19" s="1"/>
       <x:c r="D19" s="1"/>
       <x:c r="E19" s="1"/>
       <x:c r="F19" s="1"/>
@@ -779,18 +727,15 @@
       <x:c r="K19" s="1"/>
       <x:c r="L19" s="1"/>
       <x:c r="M19" s="1"/>
-      <x:c r="N19" s="1"/>
-      <x:c r="O19" s="1"/>
-      <x:c r="P19" s="1"/>
-      <x:c r="Q19" s="7"/>
-      <x:c r="R19" s="9"/>
-      <x:c r="S19" s="7"/>
-      <x:c r="T19" s="9"/>
+      <x:c r="N19" s="7"/>
+      <x:c r="O19" s="9"/>
+      <x:c r="P19" s="7"/>
+      <x:c r="Q19" s="9"/>
     </x:row>
     <x:row r="20">
-      <x:c r="A20" s="1"/>
-      <x:c r="B20" s="7"/>
-      <x:c r="C20" s="9"/>
+      <x:c r="A20" s="7"/>
+      <x:c r="B20" s="9"/>
+      <x:c r="C20" s="1"/>
       <x:c r="D20" s="1"/>
       <x:c r="E20" s="1"/>
       <x:c r="F20" s="1"/>
@@ -801,18 +746,15 @@
       <x:c r="K20" s="1"/>
       <x:c r="L20" s="1"/>
       <x:c r="M20" s="1"/>
-      <x:c r="N20" s="1"/>
-      <x:c r="O20" s="1"/>
-      <x:c r="P20" s="1"/>
-      <x:c r="Q20" s="7"/>
-      <x:c r="R20" s="9"/>
-      <x:c r="S20" s="7"/>
-      <x:c r="T20" s="9"/>
+      <x:c r="N20" s="7"/>
+      <x:c r="O20" s="9"/>
+      <x:c r="P20" s="7"/>
+      <x:c r="Q20" s="9"/>
     </x:row>
     <x:row r="21">
-      <x:c r="A21" s="1"/>
-      <x:c r="B21" s="7"/>
-      <x:c r="C21" s="9"/>
+      <x:c r="A21" s="7"/>
+      <x:c r="B21" s="9"/>
+      <x:c r="C21" s="1"/>
       <x:c r="D21" s="1"/>
       <x:c r="E21" s="1"/>
       <x:c r="F21" s="1"/>
@@ -823,18 +765,15 @@
       <x:c r="K21" s="1"/>
       <x:c r="L21" s="1"/>
       <x:c r="M21" s="1"/>
-      <x:c r="N21" s="1"/>
-      <x:c r="O21" s="1"/>
-      <x:c r="P21" s="1"/>
-      <x:c r="Q21" s="7"/>
-      <x:c r="R21" s="9"/>
-      <x:c r="S21" s="7"/>
-      <x:c r="T21" s="9"/>
+      <x:c r="N21" s="7"/>
+      <x:c r="O21" s="9"/>
+      <x:c r="P21" s="7"/>
+      <x:c r="Q21" s="9"/>
     </x:row>
     <x:row r="22">
-      <x:c r="A22" s="1"/>
-      <x:c r="B22" s="7"/>
-      <x:c r="C22" s="9"/>
+      <x:c r="A22" s="7"/>
+      <x:c r="B22" s="9"/>
+      <x:c r="C22" s="1"/>
       <x:c r="D22" s="1"/>
       <x:c r="E22" s="1"/>
       <x:c r="F22" s="1"/>
@@ -845,18 +784,15 @@
       <x:c r="K22" s="1"/>
       <x:c r="L22" s="1"/>
       <x:c r="M22" s="1"/>
-      <x:c r="N22" s="1"/>
-      <x:c r="O22" s="1"/>
-      <x:c r="P22" s="1"/>
-      <x:c r="Q22" s="7"/>
-      <x:c r="R22" s="9"/>
-      <x:c r="S22" s="7"/>
-      <x:c r="T22" s="9"/>
+      <x:c r="N22" s="7"/>
+      <x:c r="O22" s="9"/>
+      <x:c r="P22" s="7"/>
+      <x:c r="Q22" s="9"/>
     </x:row>
     <x:row r="23">
-      <x:c r="A23" s="1"/>
-      <x:c r="B23" s="7"/>
-      <x:c r="C23" s="9"/>
+      <x:c r="A23" s="7"/>
+      <x:c r="B23" s="9"/>
+      <x:c r="C23" s="1"/>
       <x:c r="D23" s="1"/>
       <x:c r="E23" s="1"/>
       <x:c r="F23" s="1"/>
@@ -867,18 +803,15 @@
       <x:c r="K23" s="1"/>
       <x:c r="L23" s="1"/>
       <x:c r="M23" s="1"/>
-      <x:c r="N23" s="1"/>
-      <x:c r="O23" s="1"/>
-      <x:c r="P23" s="1"/>
-      <x:c r="Q23" s="7"/>
-      <x:c r="R23" s="9"/>
-      <x:c r="S23" s="7"/>
-      <x:c r="T23" s="9"/>
+      <x:c r="N23" s="7"/>
+      <x:c r="O23" s="9"/>
+      <x:c r="P23" s="7"/>
+      <x:c r="Q23" s="9"/>
     </x:row>
     <x:row r="24">
-      <x:c r="A24" s="1"/>
-      <x:c r="B24" s="7"/>
-      <x:c r="C24" s="9"/>
+      <x:c r="A24" s="7"/>
+      <x:c r="B24" s="9"/>
+      <x:c r="C24" s="1"/>
       <x:c r="D24" s="1"/>
       <x:c r="E24" s="1"/>
       <x:c r="F24" s="1"/>
@@ -889,18 +822,15 @@
       <x:c r="K24" s="1"/>
       <x:c r="L24" s="1"/>
       <x:c r="M24" s="1"/>
-      <x:c r="N24" s="1"/>
-      <x:c r="O24" s="1"/>
-      <x:c r="P24" s="1"/>
-      <x:c r="Q24" s="7"/>
-      <x:c r="R24" s="9"/>
-      <x:c r="S24" s="7"/>
-      <x:c r="T24" s="9"/>
+      <x:c r="N24" s="7"/>
+      <x:c r="O24" s="9"/>
+      <x:c r="P24" s="7"/>
+      <x:c r="Q24" s="9"/>
     </x:row>
     <x:row r="25">
-      <x:c r="A25" s="1"/>
-      <x:c r="B25" s="7"/>
-      <x:c r="C25" s="9"/>
+      <x:c r="A25" s="7"/>
+      <x:c r="B25" s="9"/>
+      <x:c r="C25" s="1"/>
       <x:c r="D25" s="1"/>
       <x:c r="E25" s="1"/>
       <x:c r="F25" s="1"/>
@@ -911,18 +841,15 @@
       <x:c r="K25" s="1"/>
       <x:c r="L25" s="1"/>
       <x:c r="M25" s="1"/>
-      <x:c r="N25" s="1"/>
-      <x:c r="O25" s="1"/>
-      <x:c r="P25" s="1"/>
-      <x:c r="Q25" s="7"/>
-      <x:c r="R25" s="9"/>
-      <x:c r="S25" s="7"/>
-      <x:c r="T25" s="9"/>
+      <x:c r="N25" s="7"/>
+      <x:c r="O25" s="9"/>
+      <x:c r="P25" s="7"/>
+      <x:c r="Q25" s="9"/>
     </x:row>
     <x:row r="26">
-      <x:c r="A26" s="1"/>
-      <x:c r="B26" s="7"/>
-      <x:c r="C26" s="9"/>
+      <x:c r="A26" s="7"/>
+      <x:c r="B26" s="9"/>
+      <x:c r="C26" s="1"/>
       <x:c r="D26" s="1"/>
       <x:c r="E26" s="1"/>
       <x:c r="F26" s="1"/>
@@ -933,18 +860,15 @@
       <x:c r="K26" s="1"/>
       <x:c r="L26" s="1"/>
       <x:c r="M26" s="1"/>
-      <x:c r="N26" s="1"/>
-      <x:c r="O26" s="1"/>
-      <x:c r="P26" s="1"/>
-      <x:c r="Q26" s="7"/>
-      <x:c r="R26" s="9"/>
-      <x:c r="S26" s="7"/>
-      <x:c r="T26" s="9"/>
+      <x:c r="N26" s="7"/>
+      <x:c r="O26" s="9"/>
+      <x:c r="P26" s="7"/>
+      <x:c r="Q26" s="9"/>
     </x:row>
     <x:row r="27">
-      <x:c r="A27" s="1"/>
-      <x:c r="B27" s="7"/>
-      <x:c r="C27" s="9"/>
+      <x:c r="A27" s="7"/>
+      <x:c r="B27" s="9"/>
+      <x:c r="C27" s="1"/>
       <x:c r="D27" s="1"/>
       <x:c r="E27" s="1"/>
       <x:c r="F27" s="1"/>
@@ -955,18 +879,15 @@
       <x:c r="K27" s="1"/>
       <x:c r="L27" s="1"/>
       <x:c r="M27" s="1"/>
-      <x:c r="N27" s="1"/>
-      <x:c r="O27" s="1"/>
-      <x:c r="P27" s="1"/>
-      <x:c r="Q27" s="7"/>
-      <x:c r="R27" s="9"/>
-      <x:c r="S27" s="7"/>
-      <x:c r="T27" s="9"/>
+      <x:c r="N27" s="7"/>
+      <x:c r="O27" s="9"/>
+      <x:c r="P27" s="7"/>
+      <x:c r="Q27" s="9"/>
     </x:row>
     <x:row r="28">
-      <x:c r="A28" s="1"/>
-      <x:c r="B28" s="7"/>
-      <x:c r="C28" s="9"/>
+      <x:c r="A28" s="7"/>
+      <x:c r="B28" s="9"/>
+      <x:c r="C28" s="1"/>
       <x:c r="D28" s="1"/>
       <x:c r="E28" s="1"/>
       <x:c r="F28" s="1"/>
@@ -977,18 +898,15 @@
       <x:c r="K28" s="1"/>
       <x:c r="L28" s="1"/>
       <x:c r="M28" s="1"/>
-      <x:c r="N28" s="1"/>
-      <x:c r="O28" s="1"/>
-      <x:c r="P28" s="1"/>
-      <x:c r="Q28" s="7"/>
-      <x:c r="R28" s="9"/>
-      <x:c r="S28" s="7"/>
-      <x:c r="T28" s="9"/>
+      <x:c r="N28" s="7"/>
+      <x:c r="O28" s="9"/>
+      <x:c r="P28" s="7"/>
+      <x:c r="Q28" s="9"/>
     </x:row>
     <x:row r="29">
-      <x:c r="A29" s="1"/>
-      <x:c r="B29" s="7"/>
-      <x:c r="C29" s="9"/>
+      <x:c r="A29" s="7"/>
+      <x:c r="B29" s="9"/>
+      <x:c r="C29" s="1"/>
       <x:c r="D29" s="1"/>
       <x:c r="E29" s="1"/>
       <x:c r="F29" s="1"/>
@@ -999,18 +917,15 @@
       <x:c r="K29" s="1"/>
       <x:c r="L29" s="1"/>
       <x:c r="M29" s="1"/>
-      <x:c r="N29" s="1"/>
-      <x:c r="O29" s="1"/>
-      <x:c r="P29" s="1"/>
-      <x:c r="Q29" s="7"/>
-      <x:c r="R29" s="9"/>
-      <x:c r="S29" s="7"/>
-      <x:c r="T29" s="9"/>
+      <x:c r="N29" s="7"/>
+      <x:c r="O29" s="9"/>
+      <x:c r="P29" s="7"/>
+      <x:c r="Q29" s="9"/>
     </x:row>
     <x:row r="30">
-      <x:c r="A30" s="1"/>
-      <x:c r="B30" s="7"/>
-      <x:c r="C30" s="9"/>
+      <x:c r="A30" s="7"/>
+      <x:c r="B30" s="9"/>
+      <x:c r="C30" s="1"/>
       <x:c r="D30" s="1"/>
       <x:c r="E30" s="1"/>
       <x:c r="F30" s="1"/>
@@ -1021,18 +936,15 @@
       <x:c r="K30" s="1"/>
       <x:c r="L30" s="1"/>
       <x:c r="M30" s="1"/>
-      <x:c r="N30" s="1"/>
-      <x:c r="O30" s="1"/>
-      <x:c r="P30" s="1"/>
-      <x:c r="Q30" s="7"/>
-      <x:c r="R30" s="9"/>
-      <x:c r="S30" s="7"/>
-      <x:c r="T30" s="9"/>
+      <x:c r="N30" s="7"/>
+      <x:c r="O30" s="9"/>
+      <x:c r="P30" s="7"/>
+      <x:c r="Q30" s="9"/>
     </x:row>
     <x:row r="31">
-      <x:c r="A31" s="1"/>
-      <x:c r="B31" s="7"/>
-      <x:c r="C31" s="9"/>
+      <x:c r="A31" s="7"/>
+      <x:c r="B31" s="9"/>
+      <x:c r="C31" s="1"/>
       <x:c r="D31" s="1"/>
       <x:c r="E31" s="1"/>
       <x:c r="F31" s="1"/>
@@ -1043,18 +955,15 @@
       <x:c r="K31" s="1"/>
       <x:c r="L31" s="1"/>
       <x:c r="M31" s="1"/>
-      <x:c r="N31" s="1"/>
-      <x:c r="O31" s="1"/>
-      <x:c r="P31" s="1"/>
-      <x:c r="Q31" s="7"/>
-      <x:c r="R31" s="9"/>
-      <x:c r="S31" s="7"/>
-      <x:c r="T31" s="9"/>
+      <x:c r="N31" s="7"/>
+      <x:c r="O31" s="9"/>
+      <x:c r="P31" s="7"/>
+      <x:c r="Q31" s="9"/>
     </x:row>
     <x:row r="32">
-      <x:c r="A32" s="1"/>
-      <x:c r="B32" s="7"/>
-      <x:c r="C32" s="9"/>
+      <x:c r="A32" s="7"/>
+      <x:c r="B32" s="9"/>
+      <x:c r="C32" s="1"/>
       <x:c r="D32" s="1"/>
       <x:c r="E32" s="1"/>
       <x:c r="F32" s="1"/>
@@ -1065,18 +974,15 @@
       <x:c r="K32" s="1"/>
       <x:c r="L32" s="1"/>
       <x:c r="M32" s="1"/>
-      <x:c r="N32" s="1"/>
-      <x:c r="O32" s="1"/>
-      <x:c r="P32" s="1"/>
-      <x:c r="Q32" s="7"/>
-      <x:c r="R32" s="9"/>
-      <x:c r="S32" s="7"/>
-      <x:c r="T32" s="9"/>
+      <x:c r="N32" s="7"/>
+      <x:c r="O32" s="9"/>
+      <x:c r="P32" s="7"/>
+      <x:c r="Q32" s="9"/>
     </x:row>
     <x:row r="33">
-      <x:c r="A33" s="1"/>
-      <x:c r="B33" s="7"/>
-      <x:c r="C33" s="9"/>
+      <x:c r="A33" s="7"/>
+      <x:c r="B33" s="9"/>
+      <x:c r="C33" s="1"/>
       <x:c r="D33" s="1"/>
       <x:c r="E33" s="1"/>
       <x:c r="F33" s="1"/>
@@ -1087,18 +993,15 @@
       <x:c r="K33" s="1"/>
       <x:c r="L33" s="1"/>
       <x:c r="M33" s="1"/>
-      <x:c r="N33" s="1"/>
-      <x:c r="O33" s="1"/>
-      <x:c r="P33" s="1"/>
-      <x:c r="Q33" s="7"/>
-      <x:c r="R33" s="9"/>
-      <x:c r="S33" s="7"/>
-      <x:c r="T33" s="9"/>
+      <x:c r="N33" s="7"/>
+      <x:c r="O33" s="9"/>
+      <x:c r="P33" s="7"/>
+      <x:c r="Q33" s="9"/>
     </x:row>
     <x:row r="34">
-      <x:c r="A34" s="1"/>
-      <x:c r="B34" s="7"/>
-      <x:c r="C34" s="9"/>
+      <x:c r="A34" s="7"/>
+      <x:c r="B34" s="9"/>
+      <x:c r="C34" s="1"/>
       <x:c r="D34" s="1"/>
       <x:c r="E34" s="1"/>
       <x:c r="F34" s="1"/>
@@ -1109,18 +1012,15 @@
       <x:c r="K34" s="1"/>
       <x:c r="L34" s="1"/>
       <x:c r="M34" s="1"/>
-      <x:c r="N34" s="1"/>
-      <x:c r="O34" s="1"/>
-      <x:c r="P34" s="1"/>
-      <x:c r="Q34" s="7"/>
-      <x:c r="R34" s="9"/>
-      <x:c r="S34" s="7"/>
-      <x:c r="T34" s="9"/>
+      <x:c r="N34" s="7"/>
+      <x:c r="O34" s="9"/>
+      <x:c r="P34" s="7"/>
+      <x:c r="Q34" s="9"/>
     </x:row>
     <x:row r="35">
-      <x:c r="A35" s="1"/>
-      <x:c r="B35" s="7"/>
-      <x:c r="C35" s="9"/>
+      <x:c r="A35" s="7"/>
+      <x:c r="B35" s="9"/>
+      <x:c r="C35" s="1"/>
       <x:c r="D35" s="1"/>
       <x:c r="E35" s="1"/>
       <x:c r="F35" s="1"/>
@@ -1131,18 +1031,15 @@
       <x:c r="K35" s="1"/>
       <x:c r="L35" s="1"/>
       <x:c r="M35" s="1"/>
-      <x:c r="N35" s="1"/>
-      <x:c r="O35" s="1"/>
-      <x:c r="P35" s="1"/>
-      <x:c r="Q35" s="7"/>
-      <x:c r="R35" s="9"/>
-      <x:c r="S35" s="7"/>
-      <x:c r="T35" s="9"/>
+      <x:c r="N35" s="7"/>
+      <x:c r="O35" s="9"/>
+      <x:c r="P35" s="7"/>
+      <x:c r="Q35" s="9"/>
     </x:row>
     <x:row r="36">
-      <x:c r="A36" s="1"/>
-      <x:c r="B36" s="7"/>
-      <x:c r="C36" s="9"/>
+      <x:c r="A36" s="7"/>
+      <x:c r="B36" s="9"/>
+      <x:c r="C36" s="1"/>
       <x:c r="D36" s="1"/>
       <x:c r="E36" s="1"/>
       <x:c r="F36" s="1"/>
@@ -1153,18 +1050,15 @@
       <x:c r="K36" s="1"/>
       <x:c r="L36" s="1"/>
       <x:c r="M36" s="1"/>
-      <x:c r="N36" s="1"/>
-      <x:c r="O36" s="1"/>
-      <x:c r="P36" s="1"/>
-      <x:c r="Q36" s="7"/>
-      <x:c r="R36" s="9"/>
-      <x:c r="S36" s="7"/>
-      <x:c r="T36" s="9"/>
+      <x:c r="N36" s="7"/>
+      <x:c r="O36" s="9"/>
+      <x:c r="P36" s="7"/>
+      <x:c r="Q36" s="9"/>
     </x:row>
     <x:row r="37">
-      <x:c r="A37" s="1"/>
-      <x:c r="B37" s="7"/>
-      <x:c r="C37" s="9"/>
+      <x:c r="A37" s="7"/>
+      <x:c r="B37" s="9"/>
+      <x:c r="C37" s="1"/>
       <x:c r="D37" s="1"/>
       <x:c r="E37" s="1"/>
       <x:c r="F37" s="1"/>
@@ -1175,18 +1069,15 @@
       <x:c r="K37" s="1"/>
       <x:c r="L37" s="1"/>
       <x:c r="M37" s="1"/>
-      <x:c r="N37" s="1"/>
-      <x:c r="O37" s="1"/>
-      <x:c r="P37" s="1"/>
-      <x:c r="Q37" s="7"/>
-      <x:c r="R37" s="9"/>
-      <x:c r="S37" s="7"/>
-      <x:c r="T37" s="9"/>
+      <x:c r="N37" s="7"/>
+      <x:c r="O37" s="9"/>
+      <x:c r="P37" s="7"/>
+      <x:c r="Q37" s="9"/>
     </x:row>
     <x:row r="38">
-      <x:c r="A38" s="1"/>
-      <x:c r="B38" s="7"/>
-      <x:c r="C38" s="9"/>
+      <x:c r="A38" s="7"/>
+      <x:c r="B38" s="9"/>
+      <x:c r="C38" s="1"/>
       <x:c r="D38" s="1"/>
       <x:c r="E38" s="1"/>
       <x:c r="F38" s="1"/>
@@ -1197,18 +1088,15 @@
       <x:c r="K38" s="1"/>
       <x:c r="L38" s="1"/>
       <x:c r="M38" s="1"/>
-      <x:c r="N38" s="1"/>
-      <x:c r="O38" s="1"/>
-      <x:c r="P38" s="1"/>
-      <x:c r="Q38" s="7"/>
-      <x:c r="R38" s="9"/>
-      <x:c r="S38" s="7"/>
-      <x:c r="T38" s="9"/>
+      <x:c r="N38" s="7"/>
+      <x:c r="O38" s="9"/>
+      <x:c r="P38" s="7"/>
+      <x:c r="Q38" s="9"/>
     </x:row>
     <x:row r="39">
-      <x:c r="A39" s="1"/>
-      <x:c r="B39" s="7"/>
-      <x:c r="C39" s="9"/>
+      <x:c r="A39" s="7"/>
+      <x:c r="B39" s="9"/>
+      <x:c r="C39" s="1"/>
       <x:c r="D39" s="1"/>
       <x:c r="E39" s="1"/>
       <x:c r="F39" s="1"/>
@@ -1219,18 +1107,15 @@
       <x:c r="K39" s="1"/>
       <x:c r="L39" s="1"/>
       <x:c r="M39" s="1"/>
-      <x:c r="N39" s="1"/>
-      <x:c r="O39" s="1"/>
-      <x:c r="P39" s="1"/>
-      <x:c r="Q39" s="7"/>
-      <x:c r="R39" s="9"/>
-      <x:c r="S39" s="7"/>
-      <x:c r="T39" s="9"/>
+      <x:c r="N39" s="7"/>
+      <x:c r="O39" s="9"/>
+      <x:c r="P39" s="7"/>
+      <x:c r="Q39" s="9"/>
     </x:row>
     <x:row r="40">
-      <x:c r="A40" s="1"/>
-      <x:c r="B40" s="7"/>
-      <x:c r="C40" s="9"/>
+      <x:c r="A40" s="7"/>
+      <x:c r="B40" s="9"/>
+      <x:c r="C40" s="1"/>
       <x:c r="D40" s="1"/>
       <x:c r="E40" s="1"/>
       <x:c r="F40" s="1"/>
@@ -1241,18 +1126,15 @@
       <x:c r="K40" s="1"/>
       <x:c r="L40" s="1"/>
       <x:c r="M40" s="1"/>
-      <x:c r="N40" s="1"/>
-      <x:c r="O40" s="1"/>
-      <x:c r="P40" s="1"/>
-      <x:c r="Q40" s="7"/>
-      <x:c r="R40" s="9"/>
-      <x:c r="S40" s="7"/>
-      <x:c r="T40" s="9"/>
+      <x:c r="N40" s="7"/>
+      <x:c r="O40" s="9"/>
+      <x:c r="P40" s="7"/>
+      <x:c r="Q40" s="9"/>
     </x:row>
     <x:row r="41">
-      <x:c r="A41" s="1"/>
-      <x:c r="B41" s="7"/>
-      <x:c r="C41" s="9"/>
+      <x:c r="A41" s="7"/>
+      <x:c r="B41" s="9"/>
+      <x:c r="C41" s="1"/>
       <x:c r="D41" s="1"/>
       <x:c r="E41" s="1"/>
       <x:c r="F41" s="1"/>
@@ -1263,18 +1145,15 @@
       <x:c r="K41" s="1"/>
       <x:c r="L41" s="1"/>
       <x:c r="M41" s="1"/>
-      <x:c r="N41" s="1"/>
-      <x:c r="O41" s="1"/>
-      <x:c r="P41" s="1"/>
-      <x:c r="Q41" s="7"/>
-      <x:c r="R41" s="9"/>
-      <x:c r="S41" s="7"/>
-      <x:c r="T41" s="9"/>
+      <x:c r="N41" s="7"/>
+      <x:c r="O41" s="9"/>
+      <x:c r="P41" s="7"/>
+      <x:c r="Q41" s="9"/>
     </x:row>
     <x:row r="42">
-      <x:c r="A42" s="1"/>
-      <x:c r="B42" s="7"/>
-      <x:c r="C42" s="9"/>
+      <x:c r="A42" s="7"/>
+      <x:c r="B42" s="9"/>
+      <x:c r="C42" s="1"/>
       <x:c r="D42" s="1"/>
       <x:c r="E42" s="1"/>
       <x:c r="F42" s="1"/>
@@ -1285,18 +1164,15 @@
       <x:c r="K42" s="1"/>
       <x:c r="L42" s="1"/>
       <x:c r="M42" s="1"/>
-      <x:c r="N42" s="1"/>
-      <x:c r="O42" s="1"/>
-      <x:c r="P42" s="1"/>
-      <x:c r="Q42" s="7"/>
-      <x:c r="R42" s="9"/>
-      <x:c r="S42" s="7"/>
-      <x:c r="T42" s="9"/>
+      <x:c r="N42" s="7"/>
+      <x:c r="O42" s="9"/>
+      <x:c r="P42" s="7"/>
+      <x:c r="Q42" s="9"/>
     </x:row>
     <x:row r="43">
-      <x:c r="A43" s="1"/>
-      <x:c r="B43" s="7"/>
-      <x:c r="C43" s="9"/>
+      <x:c r="A43" s="7"/>
+      <x:c r="B43" s="9"/>
+      <x:c r="C43" s="1"/>
       <x:c r="D43" s="1"/>
       <x:c r="E43" s="1"/>
       <x:c r="F43" s="1"/>
@@ -1307,18 +1183,15 @@
       <x:c r="K43" s="1"/>
       <x:c r="L43" s="1"/>
       <x:c r="M43" s="1"/>
-      <x:c r="N43" s="1"/>
-      <x:c r="O43" s="1"/>
-      <x:c r="P43" s="1"/>
-      <x:c r="Q43" s="7"/>
-      <x:c r="R43" s="9"/>
-      <x:c r="S43" s="7"/>
-      <x:c r="T43" s="9"/>
+      <x:c r="N43" s="7"/>
+      <x:c r="O43" s="9"/>
+      <x:c r="P43" s="7"/>
+      <x:c r="Q43" s="9"/>
     </x:row>
     <x:row r="44">
-      <x:c r="A44" s="1"/>
-      <x:c r="B44" s="7"/>
-      <x:c r="C44" s="9"/>
+      <x:c r="A44" s="7"/>
+      <x:c r="B44" s="9"/>
+      <x:c r="C44" s="1"/>
       <x:c r="D44" s="1"/>
       <x:c r="E44" s="1"/>
       <x:c r="F44" s="1"/>
@@ -1329,18 +1202,15 @@
       <x:c r="K44" s="1"/>
       <x:c r="L44" s="1"/>
       <x:c r="M44" s="1"/>
-      <x:c r="N44" s="1"/>
-      <x:c r="O44" s="1"/>
-      <x:c r="P44" s="1"/>
-      <x:c r="Q44" s="7"/>
-      <x:c r="R44" s="9"/>
-      <x:c r="S44" s="7"/>
-      <x:c r="T44" s="9"/>
+      <x:c r="N44" s="7"/>
+      <x:c r="O44" s="9"/>
+      <x:c r="P44" s="7"/>
+      <x:c r="Q44" s="9"/>
     </x:row>
     <x:row r="45">
-      <x:c r="A45" s="1"/>
-      <x:c r="B45" s="7"/>
-      <x:c r="C45" s="9"/>
+      <x:c r="A45" s="7"/>
+      <x:c r="B45" s="9"/>
+      <x:c r="C45" s="1"/>
       <x:c r="D45" s="1"/>
       <x:c r="E45" s="1"/>
       <x:c r="F45" s="1"/>
@@ -1351,18 +1221,15 @@
       <x:c r="K45" s="1"/>
       <x:c r="L45" s="1"/>
       <x:c r="M45" s="1"/>
-      <x:c r="N45" s="1"/>
-      <x:c r="O45" s="1"/>
-      <x:c r="P45" s="1"/>
-      <x:c r="Q45" s="7"/>
-      <x:c r="R45" s="9"/>
-      <x:c r="S45" s="7"/>
-      <x:c r="T45" s="9"/>
+      <x:c r="N45" s="7"/>
+      <x:c r="O45" s="9"/>
+      <x:c r="P45" s="7"/>
+      <x:c r="Q45" s="9"/>
     </x:row>
     <x:row r="46">
-      <x:c r="A46" s="1"/>
-      <x:c r="B46" s="7"/>
-      <x:c r="C46" s="9"/>
+      <x:c r="A46" s="7"/>
+      <x:c r="B46" s="9"/>
+      <x:c r="C46" s="1"/>
       <x:c r="D46" s="1"/>
       <x:c r="E46" s="1"/>
       <x:c r="F46" s="1"/>
@@ -1373,18 +1240,15 @@
       <x:c r="K46" s="1"/>
       <x:c r="L46" s="1"/>
       <x:c r="M46" s="1"/>
-      <x:c r="N46" s="1"/>
-      <x:c r="O46" s="1"/>
-      <x:c r="P46" s="1"/>
-      <x:c r="Q46" s="7"/>
-      <x:c r="R46" s="9"/>
-      <x:c r="S46" s="7"/>
-      <x:c r="T46" s="9"/>
+      <x:c r="N46" s="7"/>
+      <x:c r="O46" s="9"/>
+      <x:c r="P46" s="7"/>
+      <x:c r="Q46" s="9"/>
     </x:row>
     <x:row r="47">
-      <x:c r="A47" s="1"/>
-      <x:c r="B47" s="7"/>
-      <x:c r="C47" s="9"/>
+      <x:c r="A47" s="7"/>
+      <x:c r="B47" s="9"/>
+      <x:c r="C47" s="1"/>
       <x:c r="D47" s="1"/>
       <x:c r="E47" s="1"/>
       <x:c r="F47" s="1"/>
@@ -1395,18 +1259,15 @@
       <x:c r="K47" s="1"/>
       <x:c r="L47" s="1"/>
       <x:c r="M47" s="1"/>
-      <x:c r="N47" s="1"/>
-      <x:c r="O47" s="1"/>
-      <x:c r="P47" s="1"/>
-      <x:c r="Q47" s="7"/>
-      <x:c r="R47" s="9"/>
-      <x:c r="S47" s="7"/>
-      <x:c r="T47" s="9"/>
+      <x:c r="N47" s="7"/>
+      <x:c r="O47" s="9"/>
+      <x:c r="P47" s="7"/>
+      <x:c r="Q47" s="9"/>
     </x:row>
     <x:row r="48">
-      <x:c r="A48" s="1"/>
-      <x:c r="B48" s="7"/>
-      <x:c r="C48" s="9"/>
+      <x:c r="A48" s="7"/>
+      <x:c r="B48" s="9"/>
+      <x:c r="C48" s="1"/>
       <x:c r="D48" s="1"/>
       <x:c r="E48" s="1"/>
       <x:c r="F48" s="1"/>
@@ -1417,18 +1278,15 @@
       <x:c r="K48" s="1"/>
       <x:c r="L48" s="1"/>
       <x:c r="M48" s="1"/>
-      <x:c r="N48" s="1"/>
-      <x:c r="O48" s="1"/>
-      <x:c r="P48" s="1"/>
-      <x:c r="Q48" s="7"/>
-      <x:c r="R48" s="9"/>
-      <x:c r="S48" s="7"/>
-      <x:c r="T48" s="9"/>
+      <x:c r="N48" s="7"/>
+      <x:c r="O48" s="9"/>
+      <x:c r="P48" s="7"/>
+      <x:c r="Q48" s="9"/>
     </x:row>
     <x:row r="49">
-      <x:c r="A49" s="1"/>
-      <x:c r="B49" s="7"/>
-      <x:c r="C49" s="9"/>
+      <x:c r="A49" s="7"/>
+      <x:c r="B49" s="9"/>
+      <x:c r="C49" s="1"/>
       <x:c r="D49" s="1"/>
       <x:c r="E49" s="1"/>
       <x:c r="F49" s="1"/>
@@ -1439,18 +1297,15 @@
       <x:c r="K49" s="1"/>
       <x:c r="L49" s="1"/>
       <x:c r="M49" s="1"/>
-      <x:c r="N49" s="1"/>
-      <x:c r="O49" s="1"/>
-      <x:c r="P49" s="1"/>
-      <x:c r="Q49" s="7"/>
-      <x:c r="R49" s="9"/>
-      <x:c r="S49" s="7"/>
-      <x:c r="T49" s="9"/>
+      <x:c r="N49" s="7"/>
+      <x:c r="O49" s="9"/>
+      <x:c r="P49" s="7"/>
+      <x:c r="Q49" s="9"/>
     </x:row>
     <x:row r="50">
-      <x:c r="A50" s="1"/>
-      <x:c r="B50" s="7"/>
-      <x:c r="C50" s="9"/>
+      <x:c r="A50" s="7"/>
+      <x:c r="B50" s="9"/>
+      <x:c r="C50" s="1"/>
       <x:c r="D50" s="1"/>
       <x:c r="E50" s="1"/>
       <x:c r="F50" s="1"/>
@@ -1461,18 +1316,15 @@
       <x:c r="K50" s="1"/>
       <x:c r="L50" s="1"/>
       <x:c r="M50" s="1"/>
-      <x:c r="N50" s="1"/>
-      <x:c r="O50" s="1"/>
-      <x:c r="P50" s="1"/>
-      <x:c r="Q50" s="7"/>
-      <x:c r="R50" s="9"/>
-      <x:c r="S50" s="7"/>
-      <x:c r="T50" s="9"/>
+      <x:c r="N50" s="7"/>
+      <x:c r="O50" s="9"/>
+      <x:c r="P50" s="7"/>
+      <x:c r="Q50" s="9"/>
     </x:row>
     <x:row r="51">
-      <x:c r="A51" s="1"/>
-      <x:c r="B51" s="7"/>
-      <x:c r="C51" s="9"/>
+      <x:c r="A51" s="7"/>
+      <x:c r="B51" s="9"/>
+      <x:c r="C51" s="1"/>
       <x:c r="D51" s="1"/>
       <x:c r="E51" s="1"/>
       <x:c r="F51" s="1"/>
@@ -1483,18 +1335,15 @@
       <x:c r="K51" s="1"/>
       <x:c r="L51" s="1"/>
       <x:c r="M51" s="1"/>
-      <x:c r="N51" s="1"/>
-      <x:c r="O51" s="1"/>
-      <x:c r="P51" s="1"/>
-      <x:c r="Q51" s="7"/>
-      <x:c r="R51" s="9"/>
-      <x:c r="S51" s="7"/>
-      <x:c r="T51" s="9"/>
+      <x:c r="N51" s="7"/>
+      <x:c r="O51" s="9"/>
+      <x:c r="P51" s="7"/>
+      <x:c r="Q51" s="9"/>
     </x:row>
     <x:row r="52">
-      <x:c r="A52" s="1"/>
-      <x:c r="B52" s="7"/>
-      <x:c r="C52" s="9"/>
+      <x:c r="A52" s="7"/>
+      <x:c r="B52" s="9"/>
+      <x:c r="C52" s="1"/>
       <x:c r="D52" s="1"/>
       <x:c r="E52" s="1"/>
       <x:c r="F52" s="1"/>
@@ -1505,18 +1354,15 @@
       <x:c r="K52" s="1"/>
       <x:c r="L52" s="1"/>
       <x:c r="M52" s="1"/>
-      <x:c r="N52" s="1"/>
-      <x:c r="O52" s="1"/>
-      <x:c r="P52" s="1"/>
-      <x:c r="Q52" s="7"/>
-      <x:c r="R52" s="9"/>
-      <x:c r="S52" s="7"/>
-      <x:c r="T52" s="9"/>
+      <x:c r="N52" s="7"/>
+      <x:c r="O52" s="9"/>
+      <x:c r="P52" s="7"/>
+      <x:c r="Q52" s="9"/>
     </x:row>
     <x:row r="53">
-      <x:c r="A53" s="1"/>
-      <x:c r="B53" s="7"/>
-      <x:c r="C53" s="9"/>
+      <x:c r="A53" s="7"/>
+      <x:c r="B53" s="9"/>
+      <x:c r="C53" s="1"/>
       <x:c r="D53" s="1"/>
       <x:c r="E53" s="1"/>
       <x:c r="F53" s="1"/>
@@ -1527,18 +1373,15 @@
       <x:c r="K53" s="1"/>
       <x:c r="L53" s="1"/>
       <x:c r="M53" s="1"/>
-      <x:c r="N53" s="1"/>
-      <x:c r="O53" s="1"/>
-      <x:c r="P53" s="1"/>
-      <x:c r="Q53" s="7"/>
-      <x:c r="R53" s="9"/>
-      <x:c r="S53" s="7"/>
-      <x:c r="T53" s="9"/>
+      <x:c r="N53" s="7"/>
+      <x:c r="O53" s="9"/>
+      <x:c r="P53" s="7"/>
+      <x:c r="Q53" s="9"/>
     </x:row>
     <x:row r="54">
-      <x:c r="A54" s="1"/>
-      <x:c r="B54" s="7"/>
-      <x:c r="C54" s="9"/>
+      <x:c r="A54" s="7"/>
+      <x:c r="B54" s="9"/>
+      <x:c r="C54" s="1"/>
       <x:c r="D54" s="1"/>
       <x:c r="E54" s="1"/>
       <x:c r="F54" s="1"/>
@@ -1549,18 +1392,15 @@
       <x:c r="K54" s="1"/>
       <x:c r="L54" s="1"/>
       <x:c r="M54" s="1"/>
-      <x:c r="N54" s="1"/>
-      <x:c r="O54" s="1"/>
-      <x:c r="P54" s="1"/>
-      <x:c r="Q54" s="7"/>
-      <x:c r="R54" s="9"/>
-      <x:c r="S54" s="7"/>
-      <x:c r="T54" s="9"/>
+      <x:c r="N54" s="7"/>
+      <x:c r="O54" s="9"/>
+      <x:c r="P54" s="7"/>
+      <x:c r="Q54" s="9"/>
     </x:row>
     <x:row r="55">
-      <x:c r="A55" s="1"/>
-      <x:c r="B55" s="7"/>
-      <x:c r="C55" s="9"/>
+      <x:c r="A55" s="7"/>
+      <x:c r="B55" s="9"/>
+      <x:c r="C55" s="1"/>
       <x:c r="D55" s="1"/>
       <x:c r="E55" s="1"/>
       <x:c r="F55" s="1"/>
@@ -1571,18 +1411,15 @@
       <x:c r="K55" s="1"/>
       <x:c r="L55" s="1"/>
       <x:c r="M55" s="1"/>
-      <x:c r="N55" s="1"/>
-      <x:c r="O55" s="1"/>
-      <x:c r="P55" s="1"/>
-      <x:c r="Q55" s="7"/>
-      <x:c r="R55" s="9"/>
-      <x:c r="S55" s="7"/>
-      <x:c r="T55" s="9"/>
+      <x:c r="N55" s="7"/>
+      <x:c r="O55" s="9"/>
+      <x:c r="P55" s="7"/>
+      <x:c r="Q55" s="9"/>
     </x:row>
     <x:row r="56">
-      <x:c r="A56" s="1"/>
-      <x:c r="B56" s="7"/>
-      <x:c r="C56" s="9"/>
+      <x:c r="A56" s="7"/>
+      <x:c r="B56" s="9"/>
+      <x:c r="C56" s="1"/>
       <x:c r="D56" s="1"/>
       <x:c r="E56" s="1"/>
       <x:c r="F56" s="1"/>
@@ -1593,18 +1430,15 @@
       <x:c r="K56" s="1"/>
       <x:c r="L56" s="1"/>
       <x:c r="M56" s="1"/>
-      <x:c r="N56" s="1"/>
-      <x:c r="O56" s="1"/>
-      <x:c r="P56" s="1"/>
-      <x:c r="Q56" s="7"/>
-      <x:c r="R56" s="9"/>
-      <x:c r="S56" s="7"/>
-      <x:c r="T56" s="9"/>
+      <x:c r="N56" s="7"/>
+      <x:c r="O56" s="9"/>
+      <x:c r="P56" s="7"/>
+      <x:c r="Q56" s="9"/>
     </x:row>
     <x:row r="57">
-      <x:c r="A57" s="1"/>
-      <x:c r="B57" s="7"/>
-      <x:c r="C57" s="9"/>
+      <x:c r="A57" s="7"/>
+      <x:c r="B57" s="9"/>
+      <x:c r="C57" s="1"/>
       <x:c r="D57" s="1"/>
       <x:c r="E57" s="1"/>
       <x:c r="F57" s="1"/>
@@ -1615,18 +1449,15 @@
       <x:c r="K57" s="1"/>
       <x:c r="L57" s="1"/>
       <x:c r="M57" s="1"/>
-      <x:c r="N57" s="1"/>
-      <x:c r="O57" s="1"/>
-      <x:c r="P57" s="1"/>
-      <x:c r="Q57" s="7"/>
-      <x:c r="R57" s="9"/>
-      <x:c r="S57" s="7"/>
-      <x:c r="T57" s="9"/>
+      <x:c r="N57" s="7"/>
+      <x:c r="O57" s="9"/>
+      <x:c r="P57" s="7"/>
+      <x:c r="Q57" s="9"/>
     </x:row>
     <x:row r="58">
-      <x:c r="A58" s="1"/>
-      <x:c r="B58" s="7"/>
-      <x:c r="C58" s="9"/>
+      <x:c r="A58" s="7"/>
+      <x:c r="B58" s="9"/>
+      <x:c r="C58" s="1"/>
       <x:c r="D58" s="1"/>
       <x:c r="E58" s="1"/>
       <x:c r="F58" s="1"/>
@@ -1637,18 +1468,15 @@
       <x:c r="K58" s="1"/>
       <x:c r="L58" s="1"/>
       <x:c r="M58" s="1"/>
-      <x:c r="N58" s="1"/>
-      <x:c r="O58" s="1"/>
-      <x:c r="P58" s="1"/>
-      <x:c r="Q58" s="7"/>
-      <x:c r="R58" s="9"/>
-      <x:c r="S58" s="7"/>
-      <x:c r="T58" s="9"/>
+      <x:c r="N58" s="7"/>
+      <x:c r="O58" s="9"/>
+      <x:c r="P58" s="7"/>
+      <x:c r="Q58" s="9"/>
     </x:row>
     <x:row r="59">
-      <x:c r="A59" s="1"/>
-      <x:c r="B59" s="7"/>
-      <x:c r="C59" s="9"/>
+      <x:c r="A59" s="7"/>
+      <x:c r="B59" s="9"/>
+      <x:c r="C59" s="1"/>
       <x:c r="D59" s="1"/>
       <x:c r="E59" s="1"/>
       <x:c r="F59" s="1"/>
@@ -1659,18 +1487,15 @@
       <x:c r="K59" s="1"/>
       <x:c r="L59" s="1"/>
       <x:c r="M59" s="1"/>
-      <x:c r="N59" s="1"/>
-      <x:c r="O59" s="1"/>
-      <x:c r="P59" s="1"/>
-      <x:c r="Q59" s="7"/>
-      <x:c r="R59" s="9"/>
-      <x:c r="S59" s="7"/>
-      <x:c r="T59" s="9"/>
+      <x:c r="N59" s="7"/>
+      <x:c r="O59" s="9"/>
+      <x:c r="P59" s="7"/>
+      <x:c r="Q59" s="9"/>
     </x:row>
     <x:row r="60">
-      <x:c r="A60" s="1"/>
-      <x:c r="B60" s="7"/>
-      <x:c r="C60" s="9"/>
+      <x:c r="A60" s="7"/>
+      <x:c r="B60" s="9"/>
+      <x:c r="C60" s="1"/>
       <x:c r="D60" s="1"/>
       <x:c r="E60" s="1"/>
       <x:c r="F60" s="1"/>
@@ -1681,18 +1506,15 @@
       <x:c r="K60" s="1"/>
       <x:c r="L60" s="1"/>
       <x:c r="M60" s="1"/>
-      <x:c r="N60" s="1"/>
-      <x:c r="O60" s="1"/>
-      <x:c r="P60" s="1"/>
-      <x:c r="Q60" s="7"/>
-      <x:c r="R60" s="9"/>
-      <x:c r="S60" s="7"/>
-      <x:c r="T60" s="9"/>
+      <x:c r="N60" s="7"/>
+      <x:c r="O60" s="9"/>
+      <x:c r="P60" s="7"/>
+      <x:c r="Q60" s="9"/>
     </x:row>
     <x:row r="61">
-      <x:c r="A61" s="1"/>
-      <x:c r="B61" s="7"/>
-      <x:c r="C61" s="9"/>
+      <x:c r="A61" s="7"/>
+      <x:c r="B61" s="9"/>
+      <x:c r="C61" s="1"/>
       <x:c r="D61" s="1"/>
       <x:c r="E61" s="1"/>
       <x:c r="F61" s="1"/>
@@ -1703,18 +1525,15 @@
       <x:c r="K61" s="1"/>
       <x:c r="L61" s="1"/>
       <x:c r="M61" s="1"/>
-      <x:c r="N61" s="1"/>
-      <x:c r="O61" s="1"/>
-      <x:c r="P61" s="1"/>
-      <x:c r="Q61" s="7"/>
-      <x:c r="R61" s="9"/>
-      <x:c r="S61" s="7"/>
-      <x:c r="T61" s="9"/>
+      <x:c r="N61" s="7"/>
+      <x:c r="O61" s="9"/>
+      <x:c r="P61" s="7"/>
+      <x:c r="Q61" s="9"/>
     </x:row>
     <x:row r="62">
-      <x:c r="A62" s="1"/>
-      <x:c r="B62" s="7"/>
-      <x:c r="C62" s="9"/>
+      <x:c r="A62" s="7"/>
+      <x:c r="B62" s="9"/>
+      <x:c r="C62" s="1"/>
       <x:c r="D62" s="1"/>
       <x:c r="E62" s="1"/>
       <x:c r="F62" s="1"/>
@@ -1725,18 +1544,15 @@
       <x:c r="K62" s="1"/>
       <x:c r="L62" s="1"/>
       <x:c r="M62" s="1"/>
-      <x:c r="N62" s="1"/>
-      <x:c r="O62" s="1"/>
-      <x:c r="P62" s="1"/>
-      <x:c r="Q62" s="7"/>
-      <x:c r="R62" s="9"/>
-      <x:c r="S62" s="7"/>
-      <x:c r="T62" s="9"/>
+      <x:c r="N62" s="7"/>
+      <x:c r="O62" s="9"/>
+      <x:c r="P62" s="7"/>
+      <x:c r="Q62" s="9"/>
     </x:row>
     <x:row r="63">
-      <x:c r="A63" s="1"/>
-      <x:c r="B63" s="7"/>
-      <x:c r="C63" s="9"/>
+      <x:c r="A63" s="7"/>
+      <x:c r="B63" s="9"/>
+      <x:c r="C63" s="1"/>
       <x:c r="D63" s="1"/>
       <x:c r="E63" s="1"/>
       <x:c r="F63" s="1"/>
@@ -1747,18 +1563,15 @@
       <x:c r="K63" s="1"/>
       <x:c r="L63" s="1"/>
       <x:c r="M63" s="1"/>
-      <x:c r="N63" s="1"/>
-      <x:c r="O63" s="1"/>
-      <x:c r="P63" s="1"/>
-      <x:c r="Q63" s="7"/>
-      <x:c r="R63" s="9"/>
-      <x:c r="S63" s="7"/>
-      <x:c r="T63" s="9"/>
+      <x:c r="N63" s="7"/>
+      <x:c r="O63" s="9"/>
+      <x:c r="P63" s="7"/>
+      <x:c r="Q63" s="9"/>
     </x:row>
     <x:row r="64">
-      <x:c r="A64" s="1"/>
-      <x:c r="B64" s="7"/>
-      <x:c r="C64" s="9"/>
+      <x:c r="A64" s="7"/>
+      <x:c r="B64" s="9"/>
+      <x:c r="C64" s="1"/>
       <x:c r="D64" s="1"/>
       <x:c r="E64" s="1"/>
       <x:c r="F64" s="1"/>
@@ -1769,18 +1582,15 @@
       <x:c r="K64" s="1"/>
       <x:c r="L64" s="1"/>
       <x:c r="M64" s="1"/>
-      <x:c r="N64" s="1"/>
-      <x:c r="O64" s="1"/>
-      <x:c r="P64" s="1"/>
-      <x:c r="Q64" s="7"/>
-      <x:c r="R64" s="9"/>
-      <x:c r="S64" s="7"/>
-      <x:c r="T64" s="9"/>
+      <x:c r="N64" s="7"/>
+      <x:c r="O64" s="9"/>
+      <x:c r="P64" s="7"/>
+      <x:c r="Q64" s="9"/>
     </x:row>
     <x:row r="65">
-      <x:c r="A65" s="1"/>
-      <x:c r="B65" s="7"/>
-      <x:c r="C65" s="9"/>
+      <x:c r="A65" s="7"/>
+      <x:c r="B65" s="9"/>
+      <x:c r="C65" s="1"/>
       <x:c r="D65" s="1"/>
       <x:c r="E65" s="1"/>
       <x:c r="F65" s="1"/>
@@ -1791,18 +1601,15 @@
       <x:c r="K65" s="1"/>
       <x:c r="L65" s="1"/>
       <x:c r="M65" s="1"/>
-      <x:c r="N65" s="1"/>
-      <x:c r="O65" s="1"/>
-      <x:c r="P65" s="1"/>
-      <x:c r="Q65" s="7"/>
-      <x:c r="R65" s="9"/>
-      <x:c r="S65" s="7"/>
-      <x:c r="T65" s="9"/>
+      <x:c r="N65" s="7"/>
+      <x:c r="O65" s="9"/>
+      <x:c r="P65" s="7"/>
+      <x:c r="Q65" s="9"/>
     </x:row>
     <x:row r="66">
-      <x:c r="A66" s="1"/>
-      <x:c r="B66" s="7"/>
-      <x:c r="C66" s="9"/>
+      <x:c r="A66" s="7"/>
+      <x:c r="B66" s="9"/>
+      <x:c r="C66" s="1"/>
       <x:c r="D66" s="1"/>
       <x:c r="E66" s="1"/>
       <x:c r="F66" s="1"/>
@@ -1813,18 +1620,15 @@
       <x:c r="K66" s="1"/>
       <x:c r="L66" s="1"/>
       <x:c r="M66" s="1"/>
-      <x:c r="N66" s="1"/>
-      <x:c r="O66" s="1"/>
-      <x:c r="P66" s="1"/>
-      <x:c r="Q66" s="7"/>
-      <x:c r="R66" s="9"/>
-      <x:c r="S66" s="7"/>
-      <x:c r="T66" s="9"/>
+      <x:c r="N66" s="7"/>
+      <x:c r="O66" s="9"/>
+      <x:c r="P66" s="7"/>
+      <x:c r="Q66" s="9"/>
     </x:row>
     <x:row r="67">
-      <x:c r="A67" s="1"/>
-      <x:c r="B67" s="7"/>
-      <x:c r="C67" s="9"/>
+      <x:c r="A67" s="7"/>
+      <x:c r="B67" s="9"/>
+      <x:c r="C67" s="1"/>
       <x:c r="D67" s="1"/>
       <x:c r="E67" s="1"/>
       <x:c r="F67" s="1"/>
@@ -1835,18 +1639,15 @@
       <x:c r="K67" s="1"/>
       <x:c r="L67" s="1"/>
       <x:c r="M67" s="1"/>
-      <x:c r="N67" s="1"/>
-      <x:c r="O67" s="1"/>
-      <x:c r="P67" s="1"/>
-      <x:c r="Q67" s="7"/>
-      <x:c r="R67" s="9"/>
-      <x:c r="S67" s="7"/>
-      <x:c r="T67" s="9"/>
+      <x:c r="N67" s="7"/>
+      <x:c r="O67" s="9"/>
+      <x:c r="P67" s="7"/>
+      <x:c r="Q67" s="9"/>
     </x:row>
     <x:row r="68">
-      <x:c r="A68" s="1"/>
-      <x:c r="B68" s="7"/>
-      <x:c r="C68" s="9"/>
+      <x:c r="A68" s="7"/>
+      <x:c r="B68" s="9"/>
+      <x:c r="C68" s="1"/>
       <x:c r="D68" s="1"/>
       <x:c r="E68" s="1"/>
       <x:c r="F68" s="1"/>
@@ -1857,18 +1658,15 @@
       <x:c r="K68" s="1"/>
       <x:c r="L68" s="1"/>
       <x:c r="M68" s="1"/>
-      <x:c r="N68" s="1"/>
-      <x:c r="O68" s="1"/>
-      <x:c r="P68" s="1"/>
-      <x:c r="Q68" s="7"/>
-      <x:c r="R68" s="9"/>
-      <x:c r="S68" s="7"/>
-      <x:c r="T68" s="9"/>
+      <x:c r="N68" s="7"/>
+      <x:c r="O68" s="9"/>
+      <x:c r="P68" s="7"/>
+      <x:c r="Q68" s="9"/>
     </x:row>
     <x:row r="69">
-      <x:c r="A69" s="1"/>
-      <x:c r="B69" s="7"/>
-      <x:c r="C69" s="9"/>
+      <x:c r="A69" s="7"/>
+      <x:c r="B69" s="9"/>
+      <x:c r="C69" s="1"/>
       <x:c r="D69" s="1"/>
       <x:c r="E69" s="1"/>
       <x:c r="F69" s="1"/>
@@ -1879,18 +1677,15 @@
       <x:c r="K69" s="1"/>
       <x:c r="L69" s="1"/>
       <x:c r="M69" s="1"/>
-      <x:c r="N69" s="1"/>
-      <x:c r="O69" s="1"/>
-      <x:c r="P69" s="1"/>
-      <x:c r="Q69" s="7"/>
-      <x:c r="R69" s="9"/>
-      <x:c r="S69" s="7"/>
-      <x:c r="T69" s="9"/>
+      <x:c r="N69" s="7"/>
+      <x:c r="O69" s="9"/>
+      <x:c r="P69" s="7"/>
+      <x:c r="Q69" s="9"/>
     </x:row>
     <x:row r="70">
-      <x:c r="A70" s="1"/>
-      <x:c r="B70" s="7"/>
-      <x:c r="C70" s="9"/>
+      <x:c r="A70" s="7"/>
+      <x:c r="B70" s="9"/>
+      <x:c r="C70" s="1"/>
       <x:c r="D70" s="1"/>
       <x:c r="E70" s="1"/>
       <x:c r="F70" s="1"/>
@@ -1901,18 +1696,15 @@
       <x:c r="K70" s="1"/>
       <x:c r="L70" s="1"/>
       <x:c r="M70" s="1"/>
-      <x:c r="N70" s="1"/>
-      <x:c r="O70" s="1"/>
-      <x:c r="P70" s="1"/>
-      <x:c r="Q70" s="7"/>
-      <x:c r="R70" s="9"/>
-      <x:c r="S70" s="7"/>
-      <x:c r="T70" s="9"/>
+      <x:c r="N70" s="7"/>
+      <x:c r="O70" s="9"/>
+      <x:c r="P70" s="7"/>
+      <x:c r="Q70" s="9"/>
     </x:row>
     <x:row r="71">
-      <x:c r="A71" s="1"/>
-      <x:c r="B71" s="7"/>
-      <x:c r="C71" s="9"/>
+      <x:c r="A71" s="7"/>
+      <x:c r="B71" s="9"/>
+      <x:c r="C71" s="1"/>
       <x:c r="D71" s="1"/>
       <x:c r="E71" s="1"/>
       <x:c r="F71" s="1"/>
@@ -1923,18 +1715,15 @@
       <x:c r="K71" s="1"/>
       <x:c r="L71" s="1"/>
       <x:c r="M71" s="1"/>
-      <x:c r="N71" s="1"/>
-      <x:c r="O71" s="1"/>
-      <x:c r="P71" s="1"/>
-      <x:c r="Q71" s="7"/>
-      <x:c r="R71" s="9"/>
-      <x:c r="S71" s="7"/>
-      <x:c r="T71" s="9"/>
+      <x:c r="N71" s="7"/>
+      <x:c r="O71" s="9"/>
+      <x:c r="P71" s="7"/>
+      <x:c r="Q71" s="9"/>
     </x:row>
     <x:row r="72">
-      <x:c r="A72" s="1"/>
-      <x:c r="B72" s="7"/>
-      <x:c r="C72" s="9"/>
+      <x:c r="A72" s="7"/>
+      <x:c r="B72" s="9"/>
+      <x:c r="C72" s="1"/>
       <x:c r="D72" s="1"/>
       <x:c r="E72" s="1"/>
       <x:c r="F72" s="1"/>
@@ -1945,18 +1734,15 @@
       <x:c r="K72" s="1"/>
       <x:c r="L72" s="1"/>
       <x:c r="M72" s="1"/>
-      <x:c r="N72" s="1"/>
-      <x:c r="O72" s="1"/>
-      <x:c r="P72" s="1"/>
-      <x:c r="Q72" s="7"/>
-      <x:c r="R72" s="9"/>
-      <x:c r="S72" s="7"/>
-      <x:c r="T72" s="9"/>
+      <x:c r="N72" s="7"/>
+      <x:c r="O72" s="9"/>
+      <x:c r="P72" s="7"/>
+      <x:c r="Q72" s="9"/>
     </x:row>
     <x:row r="73">
-      <x:c r="A73" s="1"/>
-      <x:c r="B73" s="7"/>
-      <x:c r="C73" s="9"/>
+      <x:c r="A73" s="7"/>
+      <x:c r="B73" s="9"/>
+      <x:c r="C73" s="1"/>
       <x:c r="D73" s="1"/>
       <x:c r="E73" s="1"/>
       <x:c r="F73" s="1"/>
@@ -1967,18 +1753,15 @@
       <x:c r="K73" s="1"/>
       <x:c r="L73" s="1"/>
       <x:c r="M73" s="1"/>
-      <x:c r="N73" s="1"/>
-      <x:c r="O73" s="1"/>
-      <x:c r="P73" s="1"/>
-      <x:c r="Q73" s="7"/>
-      <x:c r="R73" s="9"/>
-      <x:c r="S73" s="7"/>
-      <x:c r="T73" s="9"/>
+      <x:c r="N73" s="7"/>
+      <x:c r="O73" s="9"/>
+      <x:c r="P73" s="7"/>
+      <x:c r="Q73" s="9"/>
     </x:row>
     <x:row r="74">
-      <x:c r="A74" s="1"/>
-      <x:c r="B74" s="7"/>
-      <x:c r="C74" s="9"/>
+      <x:c r="A74" s="7"/>
+      <x:c r="B74" s="9"/>
+      <x:c r="C74" s="1"/>
       <x:c r="D74" s="1"/>
       <x:c r="E74" s="1"/>
       <x:c r="F74" s="1"/>
@@ -1989,18 +1772,15 @@
       <x:c r="K74" s="1"/>
       <x:c r="L74" s="1"/>
       <x:c r="M74" s="1"/>
-      <x:c r="N74" s="1"/>
-      <x:c r="O74" s="1"/>
-      <x:c r="P74" s="1"/>
-      <x:c r="Q74" s="7"/>
-      <x:c r="R74" s="9"/>
-      <x:c r="S74" s="7"/>
-      <x:c r="T74" s="9"/>
+      <x:c r="N74" s="7"/>
+      <x:c r="O74" s="9"/>
+      <x:c r="P74" s="7"/>
+      <x:c r="Q74" s="9"/>
     </x:row>
     <x:row r="75">
-      <x:c r="A75" s="1"/>
-      <x:c r="B75" s="7"/>
-      <x:c r="C75" s="9"/>
+      <x:c r="A75" s="7"/>
+      <x:c r="B75" s="9"/>
+      <x:c r="C75" s="1"/>
       <x:c r="D75" s="1"/>
       <x:c r="E75" s="1"/>
       <x:c r="F75" s="1"/>
@@ -2011,18 +1791,15 @@
       <x:c r="K75" s="1"/>
       <x:c r="L75" s="1"/>
       <x:c r="M75" s="1"/>
-      <x:c r="N75" s="1"/>
-      <x:c r="O75" s="1"/>
-      <x:c r="P75" s="1"/>
-      <x:c r="Q75" s="7"/>
-      <x:c r="R75" s="9"/>
-      <x:c r="S75" s="7"/>
-      <x:c r="T75" s="9"/>
+      <x:c r="N75" s="7"/>
+      <x:c r="O75" s="9"/>
+      <x:c r="P75" s="7"/>
+      <x:c r="Q75" s="9"/>
     </x:row>
     <x:row r="76">
-      <x:c r="A76" s="1"/>
-      <x:c r="B76" s="7"/>
-      <x:c r="C76" s="9"/>
+      <x:c r="A76" s="7"/>
+      <x:c r="B76" s="9"/>
+      <x:c r="C76" s="1"/>
       <x:c r="D76" s="1"/>
       <x:c r="E76" s="1"/>
       <x:c r="F76" s="1"/>
@@ -2033,18 +1810,15 @@
       <x:c r="K76" s="1"/>
       <x:c r="L76" s="1"/>
       <x:c r="M76" s="1"/>
-      <x:c r="N76" s="1"/>
-      <x:c r="O76" s="1"/>
-      <x:c r="P76" s="1"/>
-      <x:c r="Q76" s="7"/>
-      <x:c r="R76" s="9"/>
-      <x:c r="S76" s="7"/>
-      <x:c r="T76" s="9"/>
+      <x:c r="N76" s="7"/>
+      <x:c r="O76" s="9"/>
+      <x:c r="P76" s="7"/>
+      <x:c r="Q76" s="9"/>
     </x:row>
     <x:row r="77">
-      <x:c r="A77" s="1"/>
-      <x:c r="B77" s="7"/>
-      <x:c r="C77" s="9"/>
+      <x:c r="A77" s="7"/>
+      <x:c r="B77" s="9"/>
+      <x:c r="C77" s="1"/>
       <x:c r="D77" s="1"/>
       <x:c r="E77" s="1"/>
       <x:c r="F77" s="1"/>
@@ -2055,18 +1829,15 @@
       <x:c r="K77" s="1"/>
       <x:c r="L77" s="1"/>
       <x:c r="M77" s="1"/>
-      <x:c r="N77" s="1"/>
-      <x:c r="O77" s="1"/>
-      <x:c r="P77" s="1"/>
-      <x:c r="Q77" s="7"/>
-      <x:c r="R77" s="9"/>
-      <x:c r="S77" s="7"/>
-      <x:c r="T77" s="9"/>
+      <x:c r="N77" s="7"/>
+      <x:c r="O77" s="9"/>
+      <x:c r="P77" s="7"/>
+      <x:c r="Q77" s="9"/>
     </x:row>
     <x:row r="78">
-      <x:c r="A78" s="1"/>
-      <x:c r="B78" s="7"/>
-      <x:c r="C78" s="9"/>
+      <x:c r="A78" s="7"/>
+      <x:c r="B78" s="9"/>
+      <x:c r="C78" s="1"/>
       <x:c r="D78" s="1"/>
       <x:c r="E78" s="1"/>
       <x:c r="F78" s="1"/>
@@ -2077,18 +1848,15 @@
       <x:c r="K78" s="1"/>
       <x:c r="L78" s="1"/>
       <x:c r="M78" s="1"/>
-      <x:c r="N78" s="1"/>
-      <x:c r="O78" s="1"/>
-      <x:c r="P78" s="1"/>
-      <x:c r="Q78" s="7"/>
-      <x:c r="R78" s="9"/>
-      <x:c r="S78" s="7"/>
-      <x:c r="T78" s="9"/>
+      <x:c r="N78" s="7"/>
+      <x:c r="O78" s="9"/>
+      <x:c r="P78" s="7"/>
+      <x:c r="Q78" s="9"/>
     </x:row>
     <x:row r="79">
-      <x:c r="A79" s="1"/>
-      <x:c r="B79" s="7"/>
-      <x:c r="C79" s="9"/>
+      <x:c r="A79" s="7"/>
+      <x:c r="B79" s="9"/>
+      <x:c r="C79" s="1"/>
       <x:c r="D79" s="1"/>
       <x:c r="E79" s="1"/>
       <x:c r="F79" s="1"/>
@@ -2099,18 +1867,15 @@
       <x:c r="K79" s="1"/>
       <x:c r="L79" s="1"/>
       <x:c r="M79" s="1"/>
-      <x:c r="N79" s="1"/>
-      <x:c r="O79" s="1"/>
-      <x:c r="P79" s="1"/>
-      <x:c r="Q79" s="7"/>
-      <x:c r="R79" s="9"/>
-      <x:c r="S79" s="7"/>
-      <x:c r="T79" s="9"/>
+      <x:c r="N79" s="7"/>
+      <x:c r="O79" s="9"/>
+      <x:c r="P79" s="7"/>
+      <x:c r="Q79" s="9"/>
     </x:row>
     <x:row r="80">
-      <x:c r="A80" s="1"/>
-      <x:c r="B80" s="7"/>
-      <x:c r="C80" s="9"/>
+      <x:c r="A80" s="7"/>
+      <x:c r="B80" s="9"/>
+      <x:c r="C80" s="1"/>
       <x:c r="D80" s="1"/>
       <x:c r="E80" s="1"/>
       <x:c r="F80" s="1"/>
@@ -2121,18 +1886,15 @@
       <x:c r="K80" s="1"/>
       <x:c r="L80" s="1"/>
       <x:c r="M80" s="1"/>
-      <x:c r="N80" s="1"/>
-      <x:c r="O80" s="1"/>
-      <x:c r="P80" s="1"/>
-      <x:c r="Q80" s="7"/>
-      <x:c r="R80" s="9"/>
-      <x:c r="S80" s="7"/>
-      <x:c r="T80" s="9"/>
+      <x:c r="N80" s="7"/>
+      <x:c r="O80" s="9"/>
+      <x:c r="P80" s="7"/>
+      <x:c r="Q80" s="9"/>
     </x:row>
     <x:row r="81">
-      <x:c r="A81" s="1"/>
-      <x:c r="B81" s="7"/>
-      <x:c r="C81" s="9"/>
+      <x:c r="A81" s="7"/>
+      <x:c r="B81" s="9"/>
+      <x:c r="C81" s="1"/>
       <x:c r="D81" s="1"/>
       <x:c r="E81" s="1"/>
       <x:c r="F81" s="1"/>
@@ -2143,18 +1905,15 @@
       <x:c r="K81" s="1"/>
       <x:c r="L81" s="1"/>
       <x:c r="M81" s="1"/>
-      <x:c r="N81" s="1"/>
-      <x:c r="O81" s="1"/>
-      <x:c r="P81" s="1"/>
-      <x:c r="Q81" s="7"/>
-      <x:c r="R81" s="9"/>
-      <x:c r="S81" s="7"/>
-      <x:c r="T81" s="9"/>
+      <x:c r="N81" s="7"/>
+      <x:c r="O81" s="9"/>
+      <x:c r="P81" s="7"/>
+      <x:c r="Q81" s="9"/>
     </x:row>
     <x:row r="82">
-      <x:c r="A82" s="1"/>
-      <x:c r="B82" s="7"/>
-      <x:c r="C82" s="9"/>
+      <x:c r="A82" s="7"/>
+      <x:c r="B82" s="9"/>
+      <x:c r="C82" s="1"/>
       <x:c r="D82" s="1"/>
       <x:c r="E82" s="1"/>
       <x:c r="F82" s="1"/>
@@ -2165,18 +1924,15 @@
       <x:c r="K82" s="1"/>
       <x:c r="L82" s="1"/>
       <x:c r="M82" s="1"/>
-      <x:c r="N82" s="1"/>
-      <x:c r="O82" s="1"/>
-      <x:c r="P82" s="1"/>
-      <x:c r="Q82" s="7"/>
-      <x:c r="R82" s="9"/>
-      <x:c r="S82" s="7"/>
-      <x:c r="T82" s="9"/>
+      <x:c r="N82" s="7"/>
+      <x:c r="O82" s="9"/>
+      <x:c r="P82" s="7"/>
+      <x:c r="Q82" s="9"/>
     </x:row>
     <x:row r="83">
-      <x:c r="A83" s="1"/>
-      <x:c r="B83" s="7"/>
-      <x:c r="C83" s="9"/>
+      <x:c r="A83" s="7"/>
+      <x:c r="B83" s="9"/>
+      <x:c r="C83" s="1"/>
       <x:c r="D83" s="1"/>
       <x:c r="E83" s="1"/>
       <x:c r="F83" s="1"/>
@@ -2187,18 +1943,15 @@
       <x:c r="K83" s="1"/>
       <x:c r="L83" s="1"/>
       <x:c r="M83" s="1"/>
-      <x:c r="N83" s="1"/>
-      <x:c r="O83" s="1"/>
-      <x:c r="P83" s="1"/>
-      <x:c r="Q83" s="7"/>
-      <x:c r="R83" s="9"/>
-      <x:c r="S83" s="7"/>
-      <x:c r="T83" s="9"/>
+      <x:c r="N83" s="7"/>
+      <x:c r="O83" s="9"/>
+      <x:c r="P83" s="7"/>
+      <x:c r="Q83" s="9"/>
     </x:row>
     <x:row r="84">
-      <x:c r="A84" s="1"/>
-      <x:c r="B84" s="7"/>
-      <x:c r="C84" s="9"/>
+      <x:c r="A84" s="7"/>
+      <x:c r="B84" s="9"/>
+      <x:c r="C84" s="1"/>
       <x:c r="D84" s="1"/>
       <x:c r="E84" s="1"/>
       <x:c r="F84" s="1"/>
@@ -2209,18 +1962,15 @@
       <x:c r="K84" s="1"/>
       <x:c r="L84" s="1"/>
       <x:c r="M84" s="1"/>
-      <x:c r="N84" s="1"/>
-      <x:c r="O84" s="1"/>
-      <x:c r="P84" s="1"/>
-      <x:c r="Q84" s="7"/>
-      <x:c r="R84" s="9"/>
-      <x:c r="S84" s="7"/>
-      <x:c r="T84" s="9"/>
+      <x:c r="N84" s="7"/>
+      <x:c r="O84" s="9"/>
+      <x:c r="P84" s="7"/>
+      <x:c r="Q84" s="9"/>
     </x:row>
     <x:row r="85">
-      <x:c r="A85" s="1"/>
-      <x:c r="B85" s="7"/>
-      <x:c r="C85" s="9"/>
+      <x:c r="A85" s="7"/>
+      <x:c r="B85" s="9"/>
+      <x:c r="C85" s="1"/>
       <x:c r="D85" s="1"/>
       <x:c r="E85" s="1"/>
       <x:c r="F85" s="1"/>
@@ -2231,18 +1981,15 @@
       <x:c r="K85" s="1"/>
       <x:c r="L85" s="1"/>
       <x:c r="M85" s="1"/>
-      <x:c r="N85" s="1"/>
-      <x:c r="O85" s="1"/>
-      <x:c r="P85" s="1"/>
-      <x:c r="Q85" s="7"/>
-      <x:c r="R85" s="9"/>
-      <x:c r="S85" s="7"/>
-      <x:c r="T85" s="9"/>
+      <x:c r="N85" s="7"/>
+      <x:c r="O85" s="9"/>
+      <x:c r="P85" s="7"/>
+      <x:c r="Q85" s="9"/>
     </x:row>
     <x:row r="86">
-      <x:c r="A86" s="1"/>
-      <x:c r="B86" s="7"/>
-      <x:c r="C86" s="9"/>
+      <x:c r="A86" s="7"/>
+      <x:c r="B86" s="9"/>
+      <x:c r="C86" s="1"/>
       <x:c r="D86" s="1"/>
       <x:c r="E86" s="1"/>
       <x:c r="F86" s="1"/>
@@ -2253,18 +2000,15 @@
       <x:c r="K86" s="1"/>
       <x:c r="L86" s="1"/>
       <x:c r="M86" s="1"/>
-      <x:c r="N86" s="1"/>
-      <x:c r="O86" s="1"/>
-      <x:c r="P86" s="1"/>
-      <x:c r="Q86" s="7"/>
-      <x:c r="R86" s="9"/>
-      <x:c r="S86" s="7"/>
-      <x:c r="T86" s="9"/>
+      <x:c r="N86" s="7"/>
+      <x:c r="O86" s="9"/>
+      <x:c r="P86" s="7"/>
+      <x:c r="Q86" s="9"/>
     </x:row>
     <x:row r="87">
-      <x:c r="A87" s="1"/>
-      <x:c r="B87" s="7"/>
-      <x:c r="C87" s="9"/>
+      <x:c r="A87" s="7"/>
+      <x:c r="B87" s="9"/>
+      <x:c r="C87" s="1"/>
       <x:c r="D87" s="1"/>
       <x:c r="E87" s="1"/>
       <x:c r="F87" s="1"/>
@@ -2275,18 +2019,15 @@
       <x:c r="K87" s="1"/>
       <x:c r="L87" s="1"/>
       <x:c r="M87" s="1"/>
-      <x:c r="N87" s="1"/>
-      <x:c r="O87" s="1"/>
-      <x:c r="P87" s="1"/>
-      <x:c r="Q87" s="7"/>
-      <x:c r="R87" s="9"/>
-      <x:c r="S87" s="7"/>
-      <x:c r="T87" s="9"/>
+      <x:c r="N87" s="7"/>
+      <x:c r="O87" s="9"/>
+      <x:c r="P87" s="7"/>
+      <x:c r="Q87" s="9"/>
     </x:row>
     <x:row r="88">
-      <x:c r="A88" s="1"/>
-      <x:c r="B88" s="7"/>
-      <x:c r="C88" s="9"/>
+      <x:c r="A88" s="7"/>
+      <x:c r="B88" s="9"/>
+      <x:c r="C88" s="1"/>
       <x:c r="D88" s="1"/>
       <x:c r="E88" s="1"/>
       <x:c r="F88" s="1"/>
@@ -2297,18 +2038,15 @@
       <x:c r="K88" s="1"/>
       <x:c r="L88" s="1"/>
       <x:c r="M88" s="1"/>
-      <x:c r="N88" s="1"/>
-      <x:c r="O88" s="1"/>
-      <x:c r="P88" s="1"/>
-      <x:c r="Q88" s="7"/>
-      <x:c r="R88" s="9"/>
-      <x:c r="S88" s="7"/>
-      <x:c r="T88" s="9"/>
+      <x:c r="N88" s="7"/>
+      <x:c r="O88" s="9"/>
+      <x:c r="P88" s="7"/>
+      <x:c r="Q88" s="9"/>
     </x:row>
     <x:row r="89">
-      <x:c r="A89" s="1"/>
-      <x:c r="B89" s="7"/>
-      <x:c r="C89" s="9"/>
+      <x:c r="A89" s="7"/>
+      <x:c r="B89" s="9"/>
+      <x:c r="C89" s="1"/>
       <x:c r="D89" s="1"/>
       <x:c r="E89" s="1"/>
       <x:c r="F89" s="1"/>
@@ -2319,18 +2057,15 @@
       <x:c r="K89" s="1"/>
       <x:c r="L89" s="1"/>
       <x:c r="M89" s="1"/>
-      <x:c r="N89" s="1"/>
-      <x:c r="O89" s="1"/>
-      <x:c r="P89" s="1"/>
-      <x:c r="Q89" s="7"/>
-      <x:c r="R89" s="9"/>
-      <x:c r="S89" s="7"/>
-      <x:c r="T89" s="9"/>
+      <x:c r="N89" s="7"/>
+      <x:c r="O89" s="9"/>
+      <x:c r="P89" s="7"/>
+      <x:c r="Q89" s="9"/>
     </x:row>
     <x:row r="90">
-      <x:c r="A90" s="1"/>
-      <x:c r="B90" s="7"/>
-      <x:c r="C90" s="9"/>
+      <x:c r="A90" s="7"/>
+      <x:c r="B90" s="9"/>
+      <x:c r="C90" s="1"/>
       <x:c r="D90" s="1"/>
       <x:c r="E90" s="1"/>
       <x:c r="F90" s="1"/>
@@ -2341,18 +2076,15 @@
       <x:c r="K90" s="1"/>
       <x:c r="L90" s="1"/>
       <x:c r="M90" s="1"/>
-      <x:c r="N90" s="1"/>
-      <x:c r="O90" s="1"/>
-      <x:c r="P90" s="1"/>
-      <x:c r="Q90" s="7"/>
-      <x:c r="R90" s="9"/>
-      <x:c r="S90" s="7"/>
-      <x:c r="T90" s="9"/>
+      <x:c r="N90" s="7"/>
+      <x:c r="O90" s="9"/>
+      <x:c r="P90" s="7"/>
+      <x:c r="Q90" s="9"/>
     </x:row>
     <x:row r="91">
-      <x:c r="A91" s="1"/>
-      <x:c r="B91" s="7"/>
-      <x:c r="C91" s="9"/>
+      <x:c r="A91" s="7"/>
+      <x:c r="B91" s="9"/>
+      <x:c r="C91" s="1"/>
       <x:c r="D91" s="1"/>
       <x:c r="E91" s="1"/>
       <x:c r="F91" s="1"/>
@@ -2363,18 +2095,15 @@
       <x:c r="K91" s="1"/>
       <x:c r="L91" s="1"/>
       <x:c r="M91" s="1"/>
-      <x:c r="N91" s="1"/>
-      <x:c r="O91" s="1"/>
-      <x:c r="P91" s="1"/>
-      <x:c r="Q91" s="7"/>
-      <x:c r="R91" s="9"/>
-      <x:c r="S91" s="7"/>
-      <x:c r="T91" s="9"/>
+      <x:c r="N91" s="7"/>
+      <x:c r="O91" s="9"/>
+      <x:c r="P91" s="7"/>
+      <x:c r="Q91" s="9"/>
     </x:row>
     <x:row r="92">
-      <x:c r="A92" s="1"/>
-      <x:c r="B92" s="7"/>
-      <x:c r="C92" s="9"/>
+      <x:c r="A92" s="7"/>
+      <x:c r="B92" s="9"/>
+      <x:c r="C92" s="1"/>
       <x:c r="D92" s="1"/>
       <x:c r="E92" s="1"/>
       <x:c r="F92" s="1"/>
@@ -2385,18 +2114,15 @@
       <x:c r="K92" s="1"/>
       <x:c r="L92" s="1"/>
       <x:c r="M92" s="1"/>
-      <x:c r="N92" s="1"/>
-      <x:c r="O92" s="1"/>
-      <x:c r="P92" s="1"/>
-      <x:c r="Q92" s="7"/>
-      <x:c r="R92" s="9"/>
-      <x:c r="S92" s="7"/>
-      <x:c r="T92" s="9"/>
+      <x:c r="N92" s="7"/>
+      <x:c r="O92" s="9"/>
+      <x:c r="P92" s="7"/>
+      <x:c r="Q92" s="9"/>
     </x:row>
     <x:row r="93">
-      <x:c r="A93" s="1"/>
-      <x:c r="B93" s="7"/>
-      <x:c r="C93" s="9"/>
+      <x:c r="A93" s="7"/>
+      <x:c r="B93" s="9"/>
+      <x:c r="C93" s="1"/>
       <x:c r="D93" s="1"/>
       <x:c r="E93" s="1"/>
       <x:c r="F93" s="1"/>
@@ -2407,18 +2133,15 @@
       <x:c r="K93" s="1"/>
       <x:c r="L93" s="1"/>
       <x:c r="M93" s="1"/>
-      <x:c r="N93" s="1"/>
-      <x:c r="O93" s="1"/>
-      <x:c r="P93" s="1"/>
-      <x:c r="Q93" s="7"/>
-      <x:c r="R93" s="9"/>
-      <x:c r="S93" s="7"/>
-      <x:c r="T93" s="9"/>
+      <x:c r="N93" s="7"/>
+      <x:c r="O93" s="9"/>
+      <x:c r="P93" s="7"/>
+      <x:c r="Q93" s="9"/>
     </x:row>
     <x:row r="94">
-      <x:c r="A94" s="1"/>
-      <x:c r="B94" s="7"/>
-      <x:c r="C94" s="9"/>
+      <x:c r="A94" s="7"/>
+      <x:c r="B94" s="9"/>
+      <x:c r="C94" s="1"/>
       <x:c r="D94" s="1"/>
       <x:c r="E94" s="1"/>
       <x:c r="F94" s="1"/>
@@ -2429,18 +2152,15 @@
       <x:c r="K94" s="1"/>
       <x:c r="L94" s="1"/>
       <x:c r="M94" s="1"/>
-      <x:c r="N94" s="1"/>
-      <x:c r="O94" s="1"/>
-      <x:c r="P94" s="1"/>
-      <x:c r="Q94" s="7"/>
-      <x:c r="R94" s="9"/>
-      <x:c r="S94" s="7"/>
-      <x:c r="T94" s="9"/>
+      <x:c r="N94" s="7"/>
+      <x:c r="O94" s="9"/>
+      <x:c r="P94" s="7"/>
+      <x:c r="Q94" s="9"/>
     </x:row>
     <x:row r="95">
-      <x:c r="A95" s="1"/>
-      <x:c r="B95" s="7"/>
-      <x:c r="C95" s="9"/>
+      <x:c r="A95" s="7"/>
+      <x:c r="B95" s="9"/>
+      <x:c r="C95" s="1"/>
       <x:c r="D95" s="1"/>
       <x:c r="E95" s="1"/>
       <x:c r="F95" s="1"/>
@@ -2451,18 +2171,15 @@
       <x:c r="K95" s="1"/>
       <x:c r="L95" s="1"/>
       <x:c r="M95" s="1"/>
-      <x:c r="N95" s="1"/>
-      <x:c r="O95" s="1"/>
-      <x:c r="P95" s="1"/>
-      <x:c r="Q95" s="7"/>
-      <x:c r="R95" s="9"/>
-      <x:c r="S95" s="7"/>
-      <x:c r="T95" s="9"/>
+      <x:c r="N95" s="7"/>
+      <x:c r="O95" s="9"/>
+      <x:c r="P95" s="7"/>
+      <x:c r="Q95" s="9"/>
     </x:row>
     <x:row r="96">
-      <x:c r="A96" s="1"/>
-      <x:c r="B96" s="7"/>
-      <x:c r="C96" s="9"/>
+      <x:c r="A96" s="7"/>
+      <x:c r="B96" s="9"/>
+      <x:c r="C96" s="1"/>
       <x:c r="D96" s="1"/>
       <x:c r="E96" s="1"/>
       <x:c r="F96" s="1"/>
@@ -2473,18 +2190,15 @@
       <x:c r="K96" s="1"/>
       <x:c r="L96" s="1"/>
       <x:c r="M96" s="1"/>
-      <x:c r="N96" s="1"/>
-      <x:c r="O96" s="1"/>
-      <x:c r="P96" s="1"/>
-      <x:c r="Q96" s="7"/>
-      <x:c r="R96" s="9"/>
-      <x:c r="S96" s="7"/>
-      <x:c r="T96" s="9"/>
+      <x:c r="N96" s="7"/>
+      <x:c r="O96" s="9"/>
+      <x:c r="P96" s="7"/>
+      <x:c r="Q96" s="9"/>
     </x:row>
     <x:row r="97">
-      <x:c r="A97" s="1"/>
-      <x:c r="B97" s="7"/>
-      <x:c r="C97" s="9"/>
+      <x:c r="A97" s="7"/>
+      <x:c r="B97" s="9"/>
+      <x:c r="C97" s="1"/>
       <x:c r="D97" s="1"/>
       <x:c r="E97" s="1"/>
       <x:c r="F97" s="1"/>
@@ -2495,18 +2209,15 @@
       <x:c r="K97" s="1"/>
       <x:c r="L97" s="1"/>
       <x:c r="M97" s="1"/>
-      <x:c r="N97" s="1"/>
-      <x:c r="O97" s="1"/>
-      <x:c r="P97" s="1"/>
-      <x:c r="Q97" s="7"/>
-      <x:c r="R97" s="9"/>
-      <x:c r="S97" s="7"/>
-      <x:c r="T97" s="9"/>
+      <x:c r="N97" s="7"/>
+      <x:c r="O97" s="9"/>
+      <x:c r="P97" s="7"/>
+      <x:c r="Q97" s="9"/>
     </x:row>
     <x:row r="98">
-      <x:c r="A98" s="1"/>
-      <x:c r="B98" s="7"/>
-      <x:c r="C98" s="9"/>
+      <x:c r="A98" s="7"/>
+      <x:c r="B98" s="9"/>
+      <x:c r="C98" s="1"/>
       <x:c r="D98" s="1"/>
       <x:c r="E98" s="1"/>
       <x:c r="F98" s="1"/>
@@ -2517,18 +2228,15 @@
       <x:c r="K98" s="1"/>
       <x:c r="L98" s="1"/>
       <x:c r="M98" s="1"/>
-      <x:c r="N98" s="1"/>
-      <x:c r="O98" s="1"/>
-      <x:c r="P98" s="1"/>
-      <x:c r="Q98" s="7"/>
-      <x:c r="R98" s="9"/>
-      <x:c r="S98" s="7"/>
-      <x:c r="T98" s="9"/>
+      <x:c r="N98" s="7"/>
+      <x:c r="O98" s="9"/>
+      <x:c r="P98" s="7"/>
+      <x:c r="Q98" s="9"/>
     </x:row>
     <x:row r="99">
-      <x:c r="A99" s="1"/>
-      <x:c r="B99" s="7"/>
-      <x:c r="C99" s="9"/>
+      <x:c r="A99" s="7"/>
+      <x:c r="B99" s="9"/>
+      <x:c r="C99" s="1"/>
       <x:c r="D99" s="1"/>
       <x:c r="E99" s="1"/>
       <x:c r="F99" s="1"/>
@@ -2539,18 +2247,15 @@
       <x:c r="K99" s="1"/>
       <x:c r="L99" s="1"/>
       <x:c r="M99" s="1"/>
-      <x:c r="N99" s="1"/>
-      <x:c r="O99" s="1"/>
-      <x:c r="P99" s="1"/>
-      <x:c r="Q99" s="7"/>
-      <x:c r="R99" s="9"/>
-      <x:c r="S99" s="7"/>
-      <x:c r="T99" s="9"/>
+      <x:c r="N99" s="7"/>
+      <x:c r="O99" s="9"/>
+      <x:c r="P99" s="7"/>
+      <x:c r="Q99" s="9"/>
     </x:row>
     <x:row r="100">
-      <x:c r="A100" s="1"/>
-      <x:c r="B100" s="7"/>
-      <x:c r="C100" s="9"/>
+      <x:c r="A100" s="7"/>
+      <x:c r="B100" s="9"/>
+      <x:c r="C100" s="1"/>
       <x:c r="D100" s="1"/>
       <x:c r="E100" s="1"/>
       <x:c r="F100" s="1"/>
@@ -2561,18 +2266,15 @@
       <x:c r="K100" s="1"/>
       <x:c r="L100" s="1"/>
       <x:c r="M100" s="1"/>
-      <x:c r="N100" s="1"/>
-      <x:c r="O100" s="1"/>
-      <x:c r="P100" s="1"/>
-      <x:c r="Q100" s="7"/>
-      <x:c r="R100" s="9"/>
-      <x:c r="S100" s="7"/>
-      <x:c r="T100" s="9"/>
+      <x:c r="N100" s="7"/>
+      <x:c r="O100" s="9"/>
+      <x:c r="P100" s="7"/>
+      <x:c r="Q100" s="9"/>
     </x:row>
     <x:row r="101">
-      <x:c r="A101" s="1"/>
-      <x:c r="B101" s="7"/>
-      <x:c r="C101" s="9"/>
+      <x:c r="A101" s="7"/>
+      <x:c r="B101" s="9"/>
+      <x:c r="C101" s="1"/>
       <x:c r="D101" s="1"/>
       <x:c r="E101" s="1"/>
       <x:c r="F101" s="1"/>
@@ -2583,18 +2285,15 @@
       <x:c r="K101" s="1"/>
       <x:c r="L101" s="1"/>
       <x:c r="M101" s="1"/>
-      <x:c r="N101" s="1"/>
-      <x:c r="O101" s="1"/>
-      <x:c r="P101" s="1"/>
-      <x:c r="Q101" s="7"/>
-      <x:c r="R101" s="9"/>
-      <x:c r="S101" s="7"/>
-      <x:c r="T101" s="9"/>
+      <x:c r="N101" s="7"/>
+      <x:c r="O101" s="9"/>
+      <x:c r="P101" s="7"/>
+      <x:c r="Q101" s="9"/>
     </x:row>
     <x:row r="102">
-      <x:c r="A102" s="1"/>
-      <x:c r="B102" s="7"/>
-      <x:c r="C102" s="9"/>
+      <x:c r="A102" s="7"/>
+      <x:c r="B102" s="9"/>
+      <x:c r="C102" s="1"/>
       <x:c r="D102" s="1"/>
       <x:c r="E102" s="1"/>
       <x:c r="F102" s="1"/>
@@ -2605,18 +2304,15 @@
       <x:c r="K102" s="1"/>
       <x:c r="L102" s="1"/>
       <x:c r="M102" s="1"/>
-      <x:c r="N102" s="1"/>
-      <x:c r="O102" s="1"/>
-      <x:c r="P102" s="1"/>
-      <x:c r="Q102" s="7"/>
-      <x:c r="R102" s="9"/>
-      <x:c r="S102" s="7"/>
-      <x:c r="T102" s="9"/>
+      <x:c r="N102" s="7"/>
+      <x:c r="O102" s="9"/>
+      <x:c r="P102" s="7"/>
+      <x:c r="Q102" s="9"/>
     </x:row>
     <x:row r="103">
-      <x:c r="A103" s="1"/>
-      <x:c r="B103" s="7"/>
-      <x:c r="C103" s="9"/>
+      <x:c r="A103" s="7"/>
+      <x:c r="B103" s="9"/>
+      <x:c r="C103" s="1"/>
       <x:c r="D103" s="1"/>
       <x:c r="E103" s="1"/>
       <x:c r="F103" s="1"/>
@@ -2627,18 +2323,15 @@
       <x:c r="K103" s="1"/>
       <x:c r="L103" s="1"/>
       <x:c r="M103" s="1"/>
-      <x:c r="N103" s="1"/>
-      <x:c r="O103" s="1"/>
-      <x:c r="P103" s="1"/>
-      <x:c r="Q103" s="7"/>
-      <x:c r="R103" s="9"/>
-      <x:c r="S103" s="7"/>
-      <x:c r="T103" s="9"/>
+      <x:c r="N103" s="7"/>
+      <x:c r="O103" s="9"/>
+      <x:c r="P103" s="7"/>
+      <x:c r="Q103" s="9"/>
     </x:row>
     <x:row r="104">
-      <x:c r="A104" s="1"/>
-      <x:c r="B104" s="7"/>
-      <x:c r="C104" s="9"/>
+      <x:c r="A104" s="7"/>
+      <x:c r="B104" s="9"/>
+      <x:c r="C104" s="1"/>
       <x:c r="D104" s="1"/>
       <x:c r="E104" s="1"/>
       <x:c r="F104" s="1"/>
@@ -2649,18 +2342,15 @@
       <x:c r="K104" s="1"/>
       <x:c r="L104" s="1"/>
       <x:c r="M104" s="1"/>
-      <x:c r="N104" s="1"/>
-      <x:c r="O104" s="1"/>
-      <x:c r="P104" s="1"/>
-      <x:c r="Q104" s="7"/>
-      <x:c r="R104" s="9"/>
-      <x:c r="S104" s="7"/>
-      <x:c r="T104" s="9"/>
+      <x:c r="N104" s="7"/>
+      <x:c r="O104" s="9"/>
+      <x:c r="P104" s="7"/>
+      <x:c r="Q104" s="9"/>
     </x:row>
     <x:row r="105">
-      <x:c r="A105" s="1"/>
-      <x:c r="B105" s="7"/>
-      <x:c r="C105" s="9"/>
+      <x:c r="A105" s="7"/>
+      <x:c r="B105" s="9"/>
+      <x:c r="C105" s="1"/>
       <x:c r="D105" s="1"/>
       <x:c r="E105" s="1"/>
       <x:c r="F105" s="1"/>
@@ -2671,18 +2361,15 @@
       <x:c r="K105" s="1"/>
       <x:c r="L105" s="1"/>
       <x:c r="M105" s="1"/>
-      <x:c r="N105" s="1"/>
-      <x:c r="O105" s="1"/>
-      <x:c r="P105" s="1"/>
-      <x:c r="Q105" s="7"/>
-      <x:c r="R105" s="9"/>
-      <x:c r="S105" s="7"/>
-      <x:c r="T105" s="9"/>
+      <x:c r="N105" s="7"/>
+      <x:c r="O105" s="9"/>
+      <x:c r="P105" s="7"/>
+      <x:c r="Q105" s="9"/>
     </x:row>
     <x:row r="106">
-      <x:c r="A106" s="1"/>
-      <x:c r="B106" s="7"/>
-      <x:c r="C106" s="9"/>
+      <x:c r="A106" s="7"/>
+      <x:c r="B106" s="9"/>
+      <x:c r="C106" s="1"/>
       <x:c r="D106" s="1"/>
       <x:c r="E106" s="1"/>
       <x:c r="F106" s="1"/>
@@ -2693,18 +2380,15 @@
       <x:c r="K106" s="1"/>
       <x:c r="L106" s="1"/>
       <x:c r="M106" s="1"/>
-      <x:c r="N106" s="1"/>
-      <x:c r="O106" s="1"/>
-      <x:c r="P106" s="1"/>
-      <x:c r="Q106" s="7"/>
-      <x:c r="R106" s="9"/>
-      <x:c r="S106" s="7"/>
-      <x:c r="T106" s="9"/>
+      <x:c r="N106" s="7"/>
+      <x:c r="O106" s="9"/>
+      <x:c r="P106" s="7"/>
+      <x:c r="Q106" s="9"/>
     </x:row>
     <x:row r="107">
-      <x:c r="A107" s="1"/>
-      <x:c r="B107" s="7"/>
-      <x:c r="C107" s="9"/>
+      <x:c r="A107" s="7"/>
+      <x:c r="B107" s="9"/>
+      <x:c r="C107" s="1"/>
       <x:c r="D107" s="1"/>
       <x:c r="E107" s="1"/>
       <x:c r="F107" s="1"/>
@@ -2715,18 +2399,15 @@
       <x:c r="K107" s="1"/>
       <x:c r="L107" s="1"/>
       <x:c r="M107" s="1"/>
-      <x:c r="N107" s="1"/>
-      <x:c r="O107" s="1"/>
-      <x:c r="P107" s="1"/>
-      <x:c r="Q107" s="7"/>
-      <x:c r="R107" s="9"/>
-      <x:c r="S107" s="7"/>
-      <x:c r="T107" s="9"/>
+      <x:c r="N107" s="7"/>
+      <x:c r="O107" s="9"/>
+      <x:c r="P107" s="7"/>
+      <x:c r="Q107" s="9"/>
     </x:row>
     <x:row r="108">
-      <x:c r="A108" s="1"/>
-      <x:c r="B108" s="7"/>
-      <x:c r="C108" s="9"/>
+      <x:c r="A108" s="7"/>
+      <x:c r="B108" s="9"/>
+      <x:c r="C108" s="1"/>
       <x:c r="D108" s="1"/>
       <x:c r="E108" s="1"/>
       <x:c r="F108" s="1"/>
@@ -2737,18 +2418,15 @@
       <x:c r="K108" s="1"/>
       <x:c r="L108" s="1"/>
       <x:c r="M108" s="1"/>
-      <x:c r="N108" s="1"/>
-      <x:c r="O108" s="1"/>
-      <x:c r="P108" s="1"/>
-      <x:c r="Q108" s="7"/>
-      <x:c r="R108" s="9"/>
-      <x:c r="S108" s="7"/>
-      <x:c r="T108" s="9"/>
+      <x:c r="N108" s="7"/>
+      <x:c r="O108" s="9"/>
+      <x:c r="P108" s="7"/>
+      <x:c r="Q108" s="9"/>
     </x:row>
     <x:row r="109">
-      <x:c r="A109" s="1"/>
-      <x:c r="B109" s="7"/>
-      <x:c r="C109" s="9"/>
+      <x:c r="A109" s="7"/>
+      <x:c r="B109" s="9"/>
+      <x:c r="C109" s="1"/>
       <x:c r="D109" s="1"/>
       <x:c r="E109" s="1"/>
       <x:c r="F109" s="1"/>
@@ -2759,18 +2437,15 @@
       <x:c r="K109" s="1"/>
       <x:c r="L109" s="1"/>
       <x:c r="M109" s="1"/>
-      <x:c r="N109" s="1"/>
-      <x:c r="O109" s="1"/>
-      <x:c r="P109" s="1"/>
-      <x:c r="Q109" s="7"/>
-      <x:c r="R109" s="9"/>
-      <x:c r="S109" s="7"/>
-      <x:c r="T109" s="9"/>
+      <x:c r="N109" s="7"/>
+      <x:c r="O109" s="9"/>
+      <x:c r="P109" s="7"/>
+      <x:c r="Q109" s="9"/>
     </x:row>
     <x:row r="110">
-      <x:c r="A110" s="1"/>
-      <x:c r="B110" s="7"/>
-      <x:c r="C110" s="9"/>
+      <x:c r="A110" s="7"/>
+      <x:c r="B110" s="9"/>
+      <x:c r="C110" s="1"/>
       <x:c r="D110" s="1"/>
       <x:c r="E110" s="1"/>
       <x:c r="F110" s="1"/>
@@ -2781,18 +2456,15 @@
       <x:c r="K110" s="1"/>
       <x:c r="L110" s="1"/>
       <x:c r="M110" s="1"/>
-      <x:c r="N110" s="1"/>
-      <x:c r="O110" s="1"/>
-      <x:c r="P110" s="1"/>
-      <x:c r="Q110" s="7"/>
-      <x:c r="R110" s="9"/>
-      <x:c r="S110" s="7"/>
-      <x:c r="T110" s="9"/>
+      <x:c r="N110" s="7"/>
+      <x:c r="O110" s="9"/>
+      <x:c r="P110" s="7"/>
+      <x:c r="Q110" s="9"/>
     </x:row>
     <x:row r="111">
-      <x:c r="A111" s="1"/>
-      <x:c r="B111" s="7"/>
-      <x:c r="C111" s="9"/>
+      <x:c r="A111" s="7"/>
+      <x:c r="B111" s="9"/>
+      <x:c r="C111" s="1"/>
       <x:c r="D111" s="1"/>
       <x:c r="E111" s="1"/>
       <x:c r="F111" s="1"/>
@@ -2803,18 +2475,15 @@
       <x:c r="K111" s="1"/>
       <x:c r="L111" s="1"/>
       <x:c r="M111" s="1"/>
-      <x:c r="N111" s="1"/>
-      <x:c r="O111" s="1"/>
-      <x:c r="P111" s="1"/>
-      <x:c r="Q111" s="7"/>
-      <x:c r="R111" s="9"/>
-      <x:c r="S111" s="7"/>
-      <x:c r="T111" s="9"/>
+      <x:c r="N111" s="7"/>
+      <x:c r="O111" s="9"/>
+      <x:c r="P111" s="7"/>
+      <x:c r="Q111" s="9"/>
     </x:row>
     <x:row r="112">
-      <x:c r="A112" s="1"/>
-      <x:c r="B112" s="7"/>
-      <x:c r="C112" s="9"/>
+      <x:c r="A112" s="7"/>
+      <x:c r="B112" s="9"/>
+      <x:c r="C112" s="1"/>
       <x:c r="D112" s="1"/>
       <x:c r="E112" s="1"/>
       <x:c r="F112" s="1"/>
@@ -2825,18 +2494,15 @@
       <x:c r="K112" s="1"/>
       <x:c r="L112" s="1"/>
       <x:c r="M112" s="1"/>
-      <x:c r="N112" s="1"/>
-      <x:c r="O112" s="1"/>
-      <x:c r="P112" s="1"/>
-      <x:c r="Q112" s="7"/>
-      <x:c r="R112" s="9"/>
-      <x:c r="S112" s="7"/>
-      <x:c r="T112" s="9"/>
+      <x:c r="N112" s="7"/>
+      <x:c r="O112" s="9"/>
+      <x:c r="P112" s="7"/>
+      <x:c r="Q112" s="9"/>
     </x:row>
     <x:row r="113">
-      <x:c r="A113" s="1"/>
-      <x:c r="B113" s="7"/>
-      <x:c r="C113" s="9"/>
+      <x:c r="A113" s="7"/>
+      <x:c r="B113" s="9"/>
+      <x:c r="C113" s="1"/>
       <x:c r="D113" s="1"/>
       <x:c r="E113" s="1"/>
       <x:c r="F113" s="1"/>
@@ -2847,18 +2513,15 @@
       <x:c r="K113" s="1"/>
       <x:c r="L113" s="1"/>
       <x:c r="M113" s="1"/>
-      <x:c r="N113" s="1"/>
-      <x:c r="O113" s="1"/>
-      <x:c r="P113" s="1"/>
-      <x:c r="Q113" s="7"/>
-      <x:c r="R113" s="9"/>
-      <x:c r="S113" s="7"/>
-      <x:c r="T113" s="9"/>
+      <x:c r="N113" s="7"/>
+      <x:c r="O113" s="9"/>
+      <x:c r="P113" s="7"/>
+      <x:c r="Q113" s="9"/>
     </x:row>
     <x:row r="114">
-      <x:c r="A114" s="1"/>
-      <x:c r="B114" s="7"/>
-      <x:c r="C114" s="9"/>
+      <x:c r="A114" s="7"/>
+      <x:c r="B114" s="9"/>
+      <x:c r="C114" s="1"/>
       <x:c r="D114" s="1"/>
       <x:c r="E114" s="1"/>
       <x:c r="F114" s="1"/>
@@ -2869,18 +2532,15 @@
       <x:c r="K114" s="1"/>
       <x:c r="L114" s="1"/>
       <x:c r="M114" s="1"/>
-      <x:c r="N114" s="1"/>
-      <x:c r="O114" s="1"/>
-      <x:c r="P114" s="1"/>
-      <x:c r="Q114" s="7"/>
-      <x:c r="R114" s="9"/>
-      <x:c r="S114" s="7"/>
-      <x:c r="T114" s="9"/>
+      <x:c r="N114" s="7"/>
+      <x:c r="O114" s="9"/>
+      <x:c r="P114" s="7"/>
+      <x:c r="Q114" s="9"/>
     </x:row>
     <x:row r="115">
-      <x:c r="A115" s="1"/>
-      <x:c r="B115" s="7"/>
-      <x:c r="C115" s="9"/>
+      <x:c r="A115" s="7"/>
+      <x:c r="B115" s="9"/>
+      <x:c r="C115" s="1"/>
       <x:c r="D115" s="1"/>
       <x:c r="E115" s="1"/>
       <x:c r="F115" s="1"/>
@@ -2891,18 +2551,15 @@
       <x:c r="K115" s="1"/>
       <x:c r="L115" s="1"/>
       <x:c r="M115" s="1"/>
-      <x:c r="N115" s="1"/>
-      <x:c r="O115" s="1"/>
-      <x:c r="P115" s="1"/>
-      <x:c r="Q115" s="7"/>
-      <x:c r="R115" s="9"/>
-      <x:c r="S115" s="7"/>
-      <x:c r="T115" s="9"/>
+      <x:c r="N115" s="7"/>
+      <x:c r="O115" s="9"/>
+      <x:c r="P115" s="7"/>
+      <x:c r="Q115" s="9"/>
     </x:row>
     <x:row r="116">
-      <x:c r="A116" s="1"/>
-      <x:c r="B116" s="7"/>
-      <x:c r="C116" s="9"/>
+      <x:c r="A116" s="7"/>
+      <x:c r="B116" s="9"/>
+      <x:c r="C116" s="1"/>
       <x:c r="D116" s="1"/>
       <x:c r="E116" s="1"/>
       <x:c r="F116" s="1"/>
@@ -2913,18 +2570,15 @@
       <x:c r="K116" s="1"/>
       <x:c r="L116" s="1"/>
       <x:c r="M116" s="1"/>
-      <x:c r="N116" s="1"/>
-      <x:c r="O116" s="1"/>
-      <x:c r="P116" s="1"/>
-      <x:c r="Q116" s="7"/>
-      <x:c r="R116" s="9"/>
-      <x:c r="S116" s="7"/>
-      <x:c r="T116" s="9"/>
+      <x:c r="N116" s="7"/>
+      <x:c r="O116" s="9"/>
+      <x:c r="P116" s="7"/>
+      <x:c r="Q116" s="9"/>
     </x:row>
     <x:row r="117">
-      <x:c r="A117" s="1"/>
-      <x:c r="B117" s="7"/>
-      <x:c r="C117" s="9"/>
+      <x:c r="A117" s="7"/>
+      <x:c r="B117" s="9"/>
+      <x:c r="C117" s="1"/>
       <x:c r="D117" s="1"/>
       <x:c r="E117" s="1"/>
       <x:c r="F117" s="1"/>
@@ -2935,18 +2589,15 @@
       <x:c r="K117" s="1"/>
       <x:c r="L117" s="1"/>
       <x:c r="M117" s="1"/>
-      <x:c r="N117" s="1"/>
-      <x:c r="O117" s="1"/>
-      <x:c r="P117" s="1"/>
-      <x:c r="Q117" s="7"/>
-      <x:c r="R117" s="9"/>
-      <x:c r="S117" s="7"/>
-      <x:c r="T117" s="9"/>
+      <x:c r="N117" s="7"/>
+      <x:c r="O117" s="9"/>
+      <x:c r="P117" s="7"/>
+      <x:c r="Q117" s="9"/>
     </x:row>
     <x:row r="118">
-      <x:c r="A118" s="1"/>
-      <x:c r="B118" s="7"/>
-      <x:c r="C118" s="9"/>
+      <x:c r="A118" s="7"/>
+      <x:c r="B118" s="9"/>
+      <x:c r="C118" s="1"/>
       <x:c r="D118" s="1"/>
       <x:c r="E118" s="1"/>
       <x:c r="F118" s="1"/>
@@ -2957,18 +2608,15 @@
       <x:c r="K118" s="1"/>
       <x:c r="L118" s="1"/>
       <x:c r="M118" s="1"/>
-      <x:c r="N118" s="1"/>
-      <x:c r="O118" s="1"/>
-      <x:c r="P118" s="1"/>
-      <x:c r="Q118" s="7"/>
-      <x:c r="R118" s="9"/>
-      <x:c r="S118" s="7"/>
-      <x:c r="T118" s="9"/>
+      <x:c r="N118" s="7"/>
+      <x:c r="O118" s="9"/>
+      <x:c r="P118" s="7"/>
+      <x:c r="Q118" s="9"/>
     </x:row>
     <x:row r="119">
-      <x:c r="A119" s="1"/>
-      <x:c r="B119" s="7"/>
-      <x:c r="C119" s="9"/>
+      <x:c r="A119" s="7"/>
+      <x:c r="B119" s="9"/>
+      <x:c r="C119" s="1"/>
       <x:c r="D119" s="1"/>
       <x:c r="E119" s="1"/>
       <x:c r="F119" s="1"/>
@@ -2979,18 +2627,15 @@
       <x:c r="K119" s="1"/>
       <x:c r="L119" s="1"/>
       <x:c r="M119" s="1"/>
-      <x:c r="N119" s="1"/>
-      <x:c r="O119" s="1"/>
-      <x:c r="P119" s="1"/>
-      <x:c r="Q119" s="7"/>
-      <x:c r="R119" s="9"/>
-      <x:c r="S119" s="7"/>
-      <x:c r="T119" s="9"/>
+      <x:c r="N119" s="7"/>
+      <x:c r="O119" s="9"/>
+      <x:c r="P119" s="7"/>
+      <x:c r="Q119" s="9"/>
     </x:row>
     <x:row r="120">
-      <x:c r="A120" s="1"/>
-      <x:c r="B120" s="7"/>
-      <x:c r="C120" s="9"/>
+      <x:c r="A120" s="7"/>
+      <x:c r="B120" s="9"/>
+      <x:c r="C120" s="1"/>
       <x:c r="D120" s="1"/>
       <x:c r="E120" s="1"/>
       <x:c r="F120" s="1"/>
@@ -3001,18 +2646,15 @@
       <x:c r="K120" s="1"/>
       <x:c r="L120" s="1"/>
       <x:c r="M120" s="1"/>
-      <x:c r="N120" s="1"/>
-      <x:c r="O120" s="1"/>
-      <x:c r="P120" s="1"/>
-      <x:c r="Q120" s="7"/>
-      <x:c r="R120" s="9"/>
-      <x:c r="S120" s="7"/>
-      <x:c r="T120" s="9"/>
+      <x:c r="N120" s="7"/>
+      <x:c r="O120" s="9"/>
+      <x:c r="P120" s="7"/>
+      <x:c r="Q120" s="9"/>
     </x:row>
     <x:row r="121">
-      <x:c r="A121" s="1"/>
-      <x:c r="B121" s="7"/>
-      <x:c r="C121" s="9"/>
+      <x:c r="A121" s="7"/>
+      <x:c r="B121" s="9"/>
+      <x:c r="C121" s="1"/>
       <x:c r="D121" s="1"/>
       <x:c r="E121" s="1"/>
       <x:c r="F121" s="1"/>
@@ -3023,18 +2665,15 @@
       <x:c r="K121" s="1"/>
       <x:c r="L121" s="1"/>
       <x:c r="M121" s="1"/>
-      <x:c r="N121" s="1"/>
-      <x:c r="O121" s="1"/>
-      <x:c r="P121" s="1"/>
-      <x:c r="Q121" s="7"/>
-      <x:c r="R121" s="9"/>
-      <x:c r="S121" s="7"/>
-      <x:c r="T121" s="9"/>
+      <x:c r="N121" s="7"/>
+      <x:c r="O121" s="9"/>
+      <x:c r="P121" s="7"/>
+      <x:c r="Q121" s="9"/>
     </x:row>
     <x:row r="122">
-      <x:c r="A122" s="1"/>
-      <x:c r="B122" s="7"/>
-      <x:c r="C122" s="9"/>
+      <x:c r="A122" s="7"/>
+      <x:c r="B122" s="9"/>
+      <x:c r="C122" s="1"/>
       <x:c r="D122" s="1"/>
       <x:c r="E122" s="1"/>
       <x:c r="F122" s="1"/>
@@ -3045,18 +2684,15 @@
       <x:c r="K122" s="1"/>
       <x:c r="L122" s="1"/>
       <x:c r="M122" s="1"/>
-      <x:c r="N122" s="1"/>
-      <x:c r="O122" s="1"/>
-      <x:c r="P122" s="1"/>
-      <x:c r="Q122" s="7"/>
-      <x:c r="R122" s="9"/>
-      <x:c r="S122" s="7"/>
-      <x:c r="T122" s="9"/>
+      <x:c r="N122" s="7"/>
+      <x:c r="O122" s="9"/>
+      <x:c r="P122" s="7"/>
+      <x:c r="Q122" s="9"/>
     </x:row>
     <x:row r="123">
-      <x:c r="A123" s="1"/>
-      <x:c r="B123" s="7"/>
-      <x:c r="C123" s="9"/>
+      <x:c r="A123" s="7"/>
+      <x:c r="B123" s="9"/>
+      <x:c r="C123" s="1"/>
       <x:c r="D123" s="1"/>
       <x:c r="E123" s="1"/>
       <x:c r="F123" s="1"/>
@@ -3067,18 +2703,15 @@
       <x:c r="K123" s="1"/>
       <x:c r="L123" s="1"/>
       <x:c r="M123" s="1"/>
-      <x:c r="N123" s="1"/>
-      <x:c r="O123" s="1"/>
-      <x:c r="P123" s="1"/>
-      <x:c r="Q123" s="7"/>
-      <x:c r="R123" s="9"/>
-      <x:c r="S123" s="7"/>
-      <x:c r="T123" s="9"/>
+      <x:c r="N123" s="7"/>
+      <x:c r="O123" s="9"/>
+      <x:c r="P123" s="7"/>
+      <x:c r="Q123" s="9"/>
     </x:row>
     <x:row r="124">
-      <x:c r="A124" s="1"/>
-      <x:c r="B124" s="7"/>
-      <x:c r="C124" s="9"/>
+      <x:c r="A124" s="7"/>
+      <x:c r="B124" s="9"/>
+      <x:c r="C124" s="1"/>
       <x:c r="D124" s="1"/>
       <x:c r="E124" s="1"/>
       <x:c r="F124" s="1"/>
@@ -3089,18 +2722,15 @@
       <x:c r="K124" s="1"/>
       <x:c r="L124" s="1"/>
       <x:c r="M124" s="1"/>
-      <x:c r="N124" s="1"/>
-      <x:c r="O124" s="1"/>
-      <x:c r="P124" s="1"/>
-      <x:c r="Q124" s="7"/>
-      <x:c r="R124" s="9"/>
-      <x:c r="S124" s="7"/>
-      <x:c r="T124" s="9"/>
+      <x:c r="N124" s="7"/>
+      <x:c r="O124" s="9"/>
+      <x:c r="P124" s="7"/>
+      <x:c r="Q124" s="9"/>
     </x:row>
     <x:row r="125">
-      <x:c r="A125" s="1"/>
-      <x:c r="B125" s="7"/>
-      <x:c r="C125" s="9"/>
+      <x:c r="A125" s="7"/>
+      <x:c r="B125" s="9"/>
+      <x:c r="C125" s="1"/>
       <x:c r="D125" s="1"/>
       <x:c r="E125" s="1"/>
       <x:c r="F125" s="1"/>
@@ -3111,18 +2741,15 @@
       <x:c r="K125" s="1"/>
       <x:c r="L125" s="1"/>
       <x:c r="M125" s="1"/>
-      <x:c r="N125" s="1"/>
-      <x:c r="O125" s="1"/>
-      <x:c r="P125" s="1"/>
-      <x:c r="Q125" s="7"/>
-      <x:c r="R125" s="9"/>
-      <x:c r="S125" s="7"/>
-      <x:c r="T125" s="9"/>
+      <x:c r="N125" s="7"/>
+      <x:c r="O125" s="9"/>
+      <x:c r="P125" s="7"/>
+      <x:c r="Q125" s="9"/>
     </x:row>
     <x:row r="126">
-      <x:c r="A126" s="1"/>
-      <x:c r="B126" s="7"/>
-      <x:c r="C126" s="9"/>
+      <x:c r="A126" s="7"/>
+      <x:c r="B126" s="9"/>
+      <x:c r="C126" s="1"/>
       <x:c r="D126" s="1"/>
       <x:c r="E126" s="1"/>
       <x:c r="F126" s="1"/>
@@ -3133,18 +2760,15 @@
       <x:c r="K126" s="1"/>
       <x:c r="L126" s="1"/>
       <x:c r="M126" s="1"/>
-      <x:c r="N126" s="1"/>
-      <x:c r="O126" s="1"/>
-      <x:c r="P126" s="1"/>
-      <x:c r="Q126" s="7"/>
-      <x:c r="R126" s="9"/>
-      <x:c r="S126" s="7"/>
-      <x:c r="T126" s="9"/>
+      <x:c r="N126" s="7"/>
+      <x:c r="O126" s="9"/>
+      <x:c r="P126" s="7"/>
+      <x:c r="Q126" s="9"/>
     </x:row>
     <x:row r="127">
-      <x:c r="A127" s="1"/>
-      <x:c r="B127" s="7"/>
-      <x:c r="C127" s="9"/>
+      <x:c r="A127" s="7"/>
+      <x:c r="B127" s="9"/>
+      <x:c r="C127" s="1"/>
       <x:c r="D127" s="1"/>
       <x:c r="E127" s="1"/>
       <x:c r="F127" s="1"/>
@@ -3155,18 +2779,15 @@
       <x:c r="K127" s="1"/>
       <x:c r="L127" s="1"/>
       <x:c r="M127" s="1"/>
-      <x:c r="N127" s="1"/>
-      <x:c r="O127" s="1"/>
-      <x:c r="P127" s="1"/>
-      <x:c r="Q127" s="7"/>
-      <x:c r="R127" s="9"/>
-      <x:c r="S127" s="7"/>
-      <x:c r="T127" s="9"/>
+      <x:c r="N127" s="7"/>
+      <x:c r="O127" s="9"/>
+      <x:c r="P127" s="7"/>
+      <x:c r="Q127" s="9"/>
     </x:row>
     <x:row r="128">
-      <x:c r="A128" s="1"/>
-      <x:c r="B128" s="7"/>
-      <x:c r="C128" s="9"/>
+      <x:c r="A128" s="7"/>
+      <x:c r="B128" s="9"/>
+      <x:c r="C128" s="1"/>
       <x:c r="D128" s="1"/>
       <x:c r="E128" s="1"/>
       <x:c r="F128" s="1"/>
@@ -3177,18 +2798,15 @@
       <x:c r="K128" s="1"/>
       <x:c r="L128" s="1"/>
       <x:c r="M128" s="1"/>
-      <x:c r="N128" s="1"/>
-      <x:c r="O128" s="1"/>
-      <x:c r="P128" s="1"/>
-      <x:c r="Q128" s="7"/>
-      <x:c r="R128" s="9"/>
-      <x:c r="S128" s="7"/>
-      <x:c r="T128" s="9"/>
+      <x:c r="N128" s="7"/>
+      <x:c r="O128" s="9"/>
+      <x:c r="P128" s="7"/>
+      <x:c r="Q128" s="9"/>
     </x:row>
     <x:row r="129">
-      <x:c r="A129" s="1"/>
-      <x:c r="B129" s="7"/>
-      <x:c r="C129" s="9"/>
+      <x:c r="A129" s="7"/>
+      <x:c r="B129" s="9"/>
+      <x:c r="C129" s="1"/>
       <x:c r="D129" s="1"/>
       <x:c r="E129" s="1"/>
       <x:c r="F129" s="1"/>
@@ -3199,18 +2817,15 @@
       <x:c r="K129" s="1"/>
       <x:c r="L129" s="1"/>
       <x:c r="M129" s="1"/>
-      <x:c r="N129" s="1"/>
-      <x:c r="O129" s="1"/>
-      <x:c r="P129" s="1"/>
-      <x:c r="Q129" s="7"/>
-      <x:c r="R129" s="9"/>
-      <x:c r="S129" s="7"/>
-      <x:c r="T129" s="9"/>
+      <x:c r="N129" s="7"/>
+      <x:c r="O129" s="9"/>
+      <x:c r="P129" s="7"/>
+      <x:c r="Q129" s="9"/>
     </x:row>
     <x:row r="130">
-      <x:c r="A130" s="1"/>
-      <x:c r="B130" s="7"/>
-      <x:c r="C130" s="9"/>
+      <x:c r="A130" s="7"/>
+      <x:c r="B130" s="9"/>
+      <x:c r="C130" s="1"/>
       <x:c r="D130" s="1"/>
       <x:c r="E130" s="1"/>
       <x:c r="F130" s="1"/>
@@ -3221,18 +2836,15 @@
       <x:c r="K130" s="1"/>
       <x:c r="L130" s="1"/>
       <x:c r="M130" s="1"/>
-      <x:c r="N130" s="1"/>
-      <x:c r="O130" s="1"/>
-      <x:c r="P130" s="1"/>
-      <x:c r="Q130" s="7"/>
-      <x:c r="R130" s="9"/>
-      <x:c r="S130" s="7"/>
-      <x:c r="T130" s="9"/>
+      <x:c r="N130" s="7"/>
+      <x:c r="O130" s="9"/>
+      <x:c r="P130" s="7"/>
+      <x:c r="Q130" s="9"/>
     </x:row>
     <x:row r="131">
-      <x:c r="A131" s="1"/>
-      <x:c r="B131" s="7"/>
-      <x:c r="C131" s="9"/>
+      <x:c r="A131" s="7"/>
+      <x:c r="B131" s="9"/>
+      <x:c r="C131" s="1"/>
       <x:c r="D131" s="1"/>
       <x:c r="E131" s="1"/>
       <x:c r="F131" s="1"/>
@@ -3243,18 +2855,15 @@
       <x:c r="K131" s="1"/>
       <x:c r="L131" s="1"/>
       <x:c r="M131" s="1"/>
-      <x:c r="N131" s="1"/>
-      <x:c r="O131" s="1"/>
-      <x:c r="P131" s="1"/>
-      <x:c r="Q131" s="7"/>
-      <x:c r="R131" s="9"/>
-      <x:c r="S131" s="7"/>
-      <x:c r="T131" s="9"/>
+      <x:c r="N131" s="7"/>
+      <x:c r="O131" s="9"/>
+      <x:c r="P131" s="7"/>
+      <x:c r="Q131" s="9"/>
     </x:row>
     <x:row r="132">
-      <x:c r="A132" s="1"/>
-      <x:c r="B132" s="7"/>
-      <x:c r="C132" s="9"/>
+      <x:c r="A132" s="7"/>
+      <x:c r="B132" s="9"/>
+      <x:c r="C132" s="1"/>
       <x:c r="D132" s="1"/>
       <x:c r="E132" s="1"/>
       <x:c r="F132" s="1"/>
@@ -3265,18 +2874,15 @@
       <x:c r="K132" s="1"/>
       <x:c r="L132" s="1"/>
       <x:c r="M132" s="1"/>
-      <x:c r="N132" s="1"/>
-      <x:c r="O132" s="1"/>
-      <x:c r="P132" s="1"/>
-      <x:c r="Q132" s="7"/>
-      <x:c r="R132" s="9"/>
-      <x:c r="S132" s="7"/>
-      <x:c r="T132" s="9"/>
+      <x:c r="N132" s="7"/>
+      <x:c r="O132" s="9"/>
+      <x:c r="P132" s="7"/>
+      <x:c r="Q132" s="9"/>
     </x:row>
     <x:row r="133">
-      <x:c r="A133" s="1"/>
-      <x:c r="B133" s="7"/>
-      <x:c r="C133" s="9"/>
+      <x:c r="A133" s="7"/>
+      <x:c r="B133" s="9"/>
+      <x:c r="C133" s="1"/>
       <x:c r="D133" s="1"/>
       <x:c r="E133" s="1"/>
       <x:c r="F133" s="1"/>
@@ -3287,18 +2893,15 @@
       <x:c r="K133" s="1"/>
       <x:c r="L133" s="1"/>
       <x:c r="M133" s="1"/>
-      <x:c r="N133" s="1"/>
-      <x:c r="O133" s="1"/>
-      <x:c r="P133" s="1"/>
-      <x:c r="Q133" s="7"/>
-      <x:c r="R133" s="9"/>
-      <x:c r="S133" s="7"/>
-      <x:c r="T133" s="9"/>
+      <x:c r="N133" s="7"/>
+      <x:c r="O133" s="9"/>
+      <x:c r="P133" s="7"/>
+      <x:c r="Q133" s="9"/>
     </x:row>
     <x:row r="134">
-      <x:c r="A134" s="1"/>
-      <x:c r="B134" s="7"/>
-      <x:c r="C134" s="9"/>
+      <x:c r="A134" s="7"/>
+      <x:c r="B134" s="9"/>
+      <x:c r="C134" s="1"/>
       <x:c r="D134" s="1"/>
       <x:c r="E134" s="1"/>
       <x:c r="F134" s="1"/>
@@ -3309,18 +2912,15 @@
       <x:c r="K134" s="1"/>
       <x:c r="L134" s="1"/>
       <x:c r="M134" s="1"/>
-      <x:c r="N134" s="1"/>
-      <x:c r="O134" s="1"/>
-      <x:c r="P134" s="1"/>
-      <x:c r="Q134" s="7"/>
-      <x:c r="R134" s="9"/>
-      <x:c r="S134" s="7"/>
-      <x:c r="T134" s="9"/>
+      <x:c r="N134" s="7"/>
+      <x:c r="O134" s="9"/>
+      <x:c r="P134" s="7"/>
+      <x:c r="Q134" s="9"/>
     </x:row>
     <x:row r="135">
-      <x:c r="A135" s="1"/>
-      <x:c r="B135" s="7"/>
-      <x:c r="C135" s="9"/>
+      <x:c r="A135" s="7"/>
+      <x:c r="B135" s="9"/>
+      <x:c r="C135" s="1"/>
       <x:c r="D135" s="1"/>
       <x:c r="E135" s="1"/>
       <x:c r="F135" s="1"/>
@@ -3331,18 +2931,15 @@
       <x:c r="K135" s="1"/>
       <x:c r="L135" s="1"/>
       <x:c r="M135" s="1"/>
-      <x:c r="N135" s="1"/>
-      <x:c r="O135" s="1"/>
-      <x:c r="P135" s="1"/>
-      <x:c r="Q135" s="7"/>
-      <x:c r="R135" s="9"/>
-      <x:c r="S135" s="7"/>
-      <x:c r="T135" s="9"/>
+      <x:c r="N135" s="7"/>
+      <x:c r="O135" s="9"/>
+      <x:c r="P135" s="7"/>
+      <x:c r="Q135" s="9"/>
     </x:row>
     <x:row r="136">
-      <x:c r="A136" s="1"/>
-      <x:c r="B136" s="7"/>
-      <x:c r="C136" s="9"/>
+      <x:c r="A136" s="7"/>
+      <x:c r="B136" s="9"/>
+      <x:c r="C136" s="1"/>
       <x:c r="D136" s="1"/>
       <x:c r="E136" s="1"/>
       <x:c r="F136" s="1"/>
@@ -3353,18 +2950,15 @@
       <x:c r="K136" s="1"/>
       <x:c r="L136" s="1"/>
       <x:c r="M136" s="1"/>
-      <x:c r="N136" s="1"/>
-      <x:c r="O136" s="1"/>
-      <x:c r="P136" s="1"/>
-      <x:c r="Q136" s="7"/>
-      <x:c r="R136" s="9"/>
-      <x:c r="S136" s="7"/>
-      <x:c r="T136" s="9"/>
+      <x:c r="N136" s="7"/>
+      <x:c r="O136" s="9"/>
+      <x:c r="P136" s="7"/>
+      <x:c r="Q136" s="9"/>
     </x:row>
     <x:row r="137">
-      <x:c r="A137" s="1"/>
-      <x:c r="B137" s="7"/>
-      <x:c r="C137" s="9"/>
+      <x:c r="A137" s="7"/>
+      <x:c r="B137" s="9"/>
+      <x:c r="C137" s="1"/>
       <x:c r="D137" s="1"/>
       <x:c r="E137" s="1"/>
       <x:c r="F137" s="1"/>
@@ -3375,18 +2969,15 @@
       <x:c r="K137" s="1"/>
       <x:c r="L137" s="1"/>
       <x:c r="M137" s="1"/>
-      <x:c r="N137" s="1"/>
-      <x:c r="O137" s="1"/>
-      <x:c r="P137" s="1"/>
-      <x:c r="Q137" s="7"/>
-      <x:c r="R137" s="9"/>
-      <x:c r="S137" s="7"/>
-      <x:c r="T137" s="9"/>
+      <x:c r="N137" s="7"/>
+      <x:c r="O137" s="9"/>
+      <x:c r="P137" s="7"/>
+      <x:c r="Q137" s="9"/>
     </x:row>
     <x:row r="138">
-      <x:c r="A138" s="1"/>
-      <x:c r="B138" s="7"/>
-      <x:c r="C138" s="9"/>
+      <x:c r="A138" s="7"/>
+      <x:c r="B138" s="9"/>
+      <x:c r="C138" s="1"/>
       <x:c r="D138" s="1"/>
       <x:c r="E138" s="1"/>
       <x:c r="F138" s="1"/>
@@ -3397,18 +2988,15 @@
       <x:c r="K138" s="1"/>
       <x:c r="L138" s="1"/>
       <x:c r="M138" s="1"/>
-      <x:c r="N138" s="1"/>
-      <x:c r="O138" s="1"/>
-      <x:c r="P138" s="1"/>
-      <x:c r="Q138" s="7"/>
-      <x:c r="R138" s="9"/>
-      <x:c r="S138" s="7"/>
-      <x:c r="T138" s="9"/>
+      <x:c r="N138" s="7"/>
+      <x:c r="O138" s="9"/>
+      <x:c r="P138" s="7"/>
+      <x:c r="Q138" s="9"/>
     </x:row>
     <x:row r="139">
-      <x:c r="A139" s="1"/>
-      <x:c r="B139" s="7"/>
-      <x:c r="C139" s="9"/>
+      <x:c r="A139" s="7"/>
+      <x:c r="B139" s="9"/>
+      <x:c r="C139" s="1"/>
       <x:c r="D139" s="1"/>
       <x:c r="E139" s="1"/>
       <x:c r="F139" s="1"/>
@@ -3419,18 +3007,15 @@
       <x:c r="K139" s="1"/>
       <x:c r="L139" s="1"/>
       <x:c r="M139" s="1"/>
-      <x:c r="N139" s="1"/>
-      <x:c r="O139" s="1"/>
-      <x:c r="P139" s="1"/>
-      <x:c r="Q139" s="7"/>
-      <x:c r="R139" s="9"/>
-      <x:c r="S139" s="7"/>
-      <x:c r="T139" s="9"/>
+      <x:c r="N139" s="7"/>
+      <x:c r="O139" s="9"/>
+      <x:c r="P139" s="7"/>
+      <x:c r="Q139" s="9"/>
     </x:row>
     <x:row r="140">
-      <x:c r="A140" s="1"/>
-      <x:c r="B140" s="7"/>
-      <x:c r="C140" s="9"/>
+      <x:c r="A140" s="7"/>
+      <x:c r="B140" s="9"/>
+      <x:c r="C140" s="1"/>
       <x:c r="D140" s="1"/>
       <x:c r="E140" s="1"/>
       <x:c r="F140" s="1"/>
@@ -3441,18 +3026,15 @@
       <x:c r="K140" s="1"/>
       <x:c r="L140" s="1"/>
       <x:c r="M140" s="1"/>
-      <x:c r="N140" s="1"/>
-      <x:c r="O140" s="1"/>
-      <x:c r="P140" s="1"/>
-      <x:c r="Q140" s="7"/>
-      <x:c r="R140" s="9"/>
-      <x:c r="S140" s="7"/>
-      <x:c r="T140" s="9"/>
+      <x:c r="N140" s="7"/>
+      <x:c r="O140" s="9"/>
+      <x:c r="P140" s="7"/>
+      <x:c r="Q140" s="9"/>
     </x:row>
     <x:row r="141">
-      <x:c r="A141" s="1"/>
-      <x:c r="B141" s="7"/>
-      <x:c r="C141" s="9"/>
+      <x:c r="A141" s="7"/>
+      <x:c r="B141" s="9"/>
+      <x:c r="C141" s="1"/>
       <x:c r="D141" s="1"/>
       <x:c r="E141" s="1"/>
       <x:c r="F141" s="1"/>
@@ -3463,18 +3045,15 @@
       <x:c r="K141" s="1"/>
       <x:c r="L141" s="1"/>
       <x:c r="M141" s="1"/>
-      <x:c r="N141" s="1"/>
-      <x:c r="O141" s="1"/>
-      <x:c r="P141" s="1"/>
-      <x:c r="Q141" s="7"/>
-      <x:c r="R141" s="9"/>
-      <x:c r="S141" s="7"/>
-      <x:c r="T141" s="9"/>
+      <x:c r="N141" s="7"/>
+      <x:c r="O141" s="9"/>
+      <x:c r="P141" s="7"/>
+      <x:c r="Q141" s="9"/>
     </x:row>
     <x:row r="142">
-      <x:c r="A142" s="1"/>
-      <x:c r="B142" s="7"/>
-      <x:c r="C142" s="9"/>
+      <x:c r="A142" s="7"/>
+      <x:c r="B142" s="9"/>
+      <x:c r="C142" s="1"/>
       <x:c r="D142" s="1"/>
       <x:c r="E142" s="1"/>
       <x:c r="F142" s="1"/>
@@ -3485,18 +3064,15 @@
       <x:c r="K142" s="1"/>
       <x:c r="L142" s="1"/>
       <x:c r="M142" s="1"/>
-      <x:c r="N142" s="1"/>
-      <x:c r="O142" s="1"/>
-      <x:c r="P142" s="1"/>
-      <x:c r="Q142" s="7"/>
-      <x:c r="R142" s="9"/>
-      <x:c r="S142" s="7"/>
-      <x:c r="T142" s="9"/>
+      <x:c r="N142" s="7"/>
+      <x:c r="O142" s="9"/>
+      <x:c r="P142" s="7"/>
+      <x:c r="Q142" s="9"/>
     </x:row>
     <x:row r="143">
-      <x:c r="A143" s="1"/>
-      <x:c r="B143" s="7"/>
-      <x:c r="C143" s="9"/>
+      <x:c r="A143" s="7"/>
+      <x:c r="B143" s="9"/>
+      <x:c r="C143" s="1"/>
       <x:c r="D143" s="1"/>
       <x:c r="E143" s="1"/>
       <x:c r="F143" s="1"/>
@@ -3507,18 +3083,15 @@
       <x:c r="K143" s="1"/>
       <x:c r="L143" s="1"/>
       <x:c r="M143" s="1"/>
-      <x:c r="N143" s="1"/>
-      <x:c r="O143" s="1"/>
-      <x:c r="P143" s="1"/>
-      <x:c r="Q143" s="7"/>
-      <x:c r="R143" s="9"/>
-      <x:c r="S143" s="7"/>
-      <x:c r="T143" s="9"/>
+      <x:c r="N143" s="7"/>
+      <x:c r="O143" s="9"/>
+      <x:c r="P143" s="7"/>
+      <x:c r="Q143" s="9"/>
     </x:row>
     <x:row r="144">
-      <x:c r="A144" s="1"/>
-      <x:c r="B144" s="7"/>
-      <x:c r="C144" s="9"/>
+      <x:c r="A144" s="7"/>
+      <x:c r="B144" s="9"/>
+      <x:c r="C144" s="1"/>
       <x:c r="D144" s="1"/>
       <x:c r="E144" s="1"/>
       <x:c r="F144" s="1"/>
@@ -3529,18 +3102,15 @@
       <x:c r="K144" s="1"/>
       <x:c r="L144" s="1"/>
       <x:c r="M144" s="1"/>
-      <x:c r="N144" s="1"/>
-      <x:c r="O144" s="1"/>
-      <x:c r="P144" s="1"/>
-      <x:c r="Q144" s="7"/>
-      <x:c r="R144" s="9"/>
-      <x:c r="S144" s="7"/>
-      <x:c r="T144" s="9"/>
+      <x:c r="N144" s="7"/>
+      <x:c r="O144" s="9"/>
+      <x:c r="P144" s="7"/>
+      <x:c r="Q144" s="9"/>
     </x:row>
     <x:row r="145">
-      <x:c r="A145" s="1"/>
-      <x:c r="B145" s="7"/>
-      <x:c r="C145" s="9"/>
+      <x:c r="A145" s="7"/>
+      <x:c r="B145" s="9"/>
+      <x:c r="C145" s="1"/>
       <x:c r="D145" s="1"/>
       <x:c r="E145" s="1"/>
       <x:c r="F145" s="1"/>
@@ -3551,18 +3121,15 @@
       <x:c r="K145" s="1"/>
       <x:c r="L145" s="1"/>
       <x:c r="M145" s="1"/>
-      <x:c r="N145" s="1"/>
-      <x:c r="O145" s="1"/>
-      <x:c r="P145" s="1"/>
-      <x:c r="Q145" s="7"/>
-      <x:c r="R145" s="9"/>
-      <x:c r="S145" s="7"/>
-      <x:c r="T145" s="9"/>
+      <x:c r="N145" s="7"/>
+      <x:c r="O145" s="9"/>
+      <x:c r="P145" s="7"/>
+      <x:c r="Q145" s="9"/>
     </x:row>
     <x:row r="146">
-      <x:c r="A146" s="1"/>
-      <x:c r="B146" s="7"/>
-      <x:c r="C146" s="9"/>
+      <x:c r="A146" s="7"/>
+      <x:c r="B146" s="9"/>
+      <x:c r="C146" s="1"/>
       <x:c r="D146" s="1"/>
       <x:c r="E146" s="1"/>
       <x:c r="F146" s="1"/>
@@ -3573,18 +3140,15 @@
       <x:c r="K146" s="1"/>
       <x:c r="L146" s="1"/>
       <x:c r="M146" s="1"/>
-      <x:c r="N146" s="1"/>
-      <x:c r="O146" s="1"/>
-      <x:c r="P146" s="1"/>
-      <x:c r="Q146" s="7"/>
-      <x:c r="R146" s="9"/>
-      <x:c r="S146" s="7"/>
-      <x:c r="T146" s="9"/>
+      <x:c r="N146" s="7"/>
+      <x:c r="O146" s="9"/>
+      <x:c r="P146" s="7"/>
+      <x:c r="Q146" s="9"/>
     </x:row>
     <x:row r="147">
-      <x:c r="A147" s="1"/>
-      <x:c r="B147" s="7"/>
-      <x:c r="C147" s="9"/>
+      <x:c r="A147" s="7"/>
+      <x:c r="B147" s="9"/>
+      <x:c r="C147" s="1"/>
       <x:c r="D147" s="1"/>
       <x:c r="E147" s="1"/>
       <x:c r="F147" s="1"/>
@@ -3595,18 +3159,15 @@
       <x:c r="K147" s="1"/>
       <x:c r="L147" s="1"/>
       <x:c r="M147" s="1"/>
-      <x:c r="N147" s="1"/>
-      <x:c r="O147" s="1"/>
-      <x:c r="P147" s="1"/>
-      <x:c r="Q147" s="7"/>
-      <x:c r="R147" s="9"/>
-      <x:c r="S147" s="7"/>
-      <x:c r="T147" s="9"/>
+      <x:c r="N147" s="7"/>
+      <x:c r="O147" s="9"/>
+      <x:c r="P147" s="7"/>
+      <x:c r="Q147" s="9"/>
     </x:row>
     <x:row r="148">
-      <x:c r="A148" s="1"/>
-      <x:c r="B148" s="7"/>
-      <x:c r="C148" s="9"/>
+      <x:c r="A148" s="7"/>
+      <x:c r="B148" s="9"/>
+      <x:c r="C148" s="1"/>
       <x:c r="D148" s="1"/>
       <x:c r="E148" s="1"/>
       <x:c r="F148" s="1"/>
@@ -3617,18 +3178,15 @@
       <x:c r="K148" s="1"/>
       <x:c r="L148" s="1"/>
       <x:c r="M148" s="1"/>
-      <x:c r="N148" s="1"/>
-      <x:c r="O148" s="1"/>
-      <x:c r="P148" s="1"/>
-      <x:c r="Q148" s="7"/>
-      <x:c r="R148" s="9"/>
-      <x:c r="S148" s="7"/>
-      <x:c r="T148" s="9"/>
+      <x:c r="N148" s="7"/>
+      <x:c r="O148" s="9"/>
+      <x:c r="P148" s="7"/>
+      <x:c r="Q148" s="9"/>
     </x:row>
     <x:row r="149">
-      <x:c r="A149" s="1"/>
-      <x:c r="B149" s="7"/>
-      <x:c r="C149" s="9"/>
+      <x:c r="A149" s="7"/>
+      <x:c r="B149" s="9"/>
+      <x:c r="C149" s="1"/>
       <x:c r="D149" s="1"/>
       <x:c r="E149" s="1"/>
       <x:c r="F149" s="1"/>
@@ -3639,18 +3197,15 @@
       <x:c r="K149" s="1"/>
       <x:c r="L149" s="1"/>
       <x:c r="M149" s="1"/>
-      <x:c r="N149" s="1"/>
-      <x:c r="O149" s="1"/>
-      <x:c r="P149" s="1"/>
-      <x:c r="Q149" s="7"/>
-      <x:c r="R149" s="9"/>
-      <x:c r="S149" s="7"/>
-      <x:c r="T149" s="9"/>
+      <x:c r="N149" s="7"/>
+      <x:c r="O149" s="9"/>
+      <x:c r="P149" s="7"/>
+      <x:c r="Q149" s="9"/>
     </x:row>
     <x:row r="150">
-      <x:c r="A150" s="1"/>
-      <x:c r="B150" s="7"/>
-      <x:c r="C150" s="9"/>
+      <x:c r="A150" s="7"/>
+      <x:c r="B150" s="9"/>
+      <x:c r="C150" s="1"/>
       <x:c r="D150" s="1"/>
       <x:c r="E150" s="1"/>
       <x:c r="F150" s="1"/>
@@ -3661,18 +3216,15 @@
       <x:c r="K150" s="1"/>
       <x:c r="L150" s="1"/>
       <x:c r="M150" s="1"/>
-      <x:c r="N150" s="1"/>
-      <x:c r="O150" s="1"/>
-      <x:c r="P150" s="1"/>
-      <x:c r="Q150" s="7"/>
-      <x:c r="R150" s="9"/>
-      <x:c r="S150" s="7"/>
-      <x:c r="T150" s="9"/>
+      <x:c r="N150" s="7"/>
+      <x:c r="O150" s="9"/>
+      <x:c r="P150" s="7"/>
+      <x:c r="Q150" s="9"/>
     </x:row>
     <x:row r="151">
-      <x:c r="A151" s="1"/>
-      <x:c r="B151" s="7"/>
-      <x:c r="C151" s="9"/>
+      <x:c r="A151" s="7"/>
+      <x:c r="B151" s="9"/>
+      <x:c r="C151" s="1"/>
       <x:c r="D151" s="1"/>
       <x:c r="E151" s="1"/>
       <x:c r="F151" s="1"/>
@@ -3683,18 +3235,15 @@
       <x:c r="K151" s="1"/>
       <x:c r="L151" s="1"/>
       <x:c r="M151" s="1"/>
-      <x:c r="N151" s="1"/>
-      <x:c r="O151" s="1"/>
-      <x:c r="P151" s="1"/>
-      <x:c r="Q151" s="7"/>
-      <x:c r="R151" s="9"/>
-      <x:c r="S151" s="7"/>
-      <x:c r="T151" s="9"/>
+      <x:c r="N151" s="7"/>
+      <x:c r="O151" s="9"/>
+      <x:c r="P151" s="7"/>
+      <x:c r="Q151" s="9"/>
     </x:row>
     <x:row r="152">
-      <x:c r="A152" s="1"/>
-      <x:c r="B152" s="7"/>
-      <x:c r="C152" s="9"/>
+      <x:c r="A152" s="7"/>
+      <x:c r="B152" s="9"/>
+      <x:c r="C152" s="1"/>
       <x:c r="D152" s="1"/>
       <x:c r="E152" s="1"/>
       <x:c r="F152" s="1"/>
@@ -3705,18 +3254,15 @@
       <x:c r="K152" s="1"/>
       <x:c r="L152" s="1"/>
       <x:c r="M152" s="1"/>
-      <x:c r="N152" s="1"/>
-      <x:c r="O152" s="1"/>
-      <x:c r="P152" s="1"/>
-      <x:c r="Q152" s="7"/>
-      <x:c r="R152" s="9"/>
-      <x:c r="S152" s="7"/>
-      <x:c r="T152" s="9"/>
+      <x:c r="N152" s="7"/>
+      <x:c r="O152" s="9"/>
+      <x:c r="P152" s="7"/>
+      <x:c r="Q152" s="9"/>
     </x:row>
     <x:row r="153">
-      <x:c r="A153" s="1"/>
-      <x:c r="B153" s="7"/>
-      <x:c r="C153" s="9"/>
+      <x:c r="A153" s="7"/>
+      <x:c r="B153" s="9"/>
+      <x:c r="C153" s="1"/>
       <x:c r="D153" s="1"/>
       <x:c r="E153" s="1"/>
       <x:c r="F153" s="1"/>
@@ -3727,18 +3273,15 @@
       <x:c r="K153" s="1"/>
       <x:c r="L153" s="1"/>
       <x:c r="M153" s="1"/>
-      <x:c r="N153" s="1"/>
-      <x:c r="O153" s="1"/>
-      <x:c r="P153" s="1"/>
-      <x:c r="Q153" s="7"/>
-      <x:c r="R153" s="9"/>
-      <x:c r="S153" s="7"/>
-      <x:c r="T153" s="9"/>
+      <x:c r="N153" s="7"/>
+      <x:c r="O153" s="9"/>
+      <x:c r="P153" s="7"/>
+      <x:c r="Q153" s="9"/>
     </x:row>
     <x:row r="154">
-      <x:c r="A154" s="1"/>
-      <x:c r="B154" s="7"/>
-      <x:c r="C154" s="9"/>
+      <x:c r="A154" s="7"/>
+      <x:c r="B154" s="9"/>
+      <x:c r="C154" s="1"/>
       <x:c r="D154" s="1"/>
       <x:c r="E154" s="1"/>
       <x:c r="F154" s="1"/>
@@ -3749,18 +3292,15 @@
       <x:c r="K154" s="1"/>
       <x:c r="L154" s="1"/>
       <x:c r="M154" s="1"/>
-      <x:c r="N154" s="1"/>
-      <x:c r="O154" s="1"/>
-      <x:c r="P154" s="1"/>
-      <x:c r="Q154" s="7"/>
-      <x:c r="R154" s="9"/>
-      <x:c r="S154" s="7"/>
-      <x:c r="T154" s="9"/>
+      <x:c r="N154" s="7"/>
+      <x:c r="O154" s="9"/>
+      <x:c r="P154" s="7"/>
+      <x:c r="Q154" s="9"/>
     </x:row>
     <x:row r="155">
-      <x:c r="A155" s="1"/>
-      <x:c r="B155" s="7"/>
-      <x:c r="C155" s="9"/>
+      <x:c r="A155" s="7"/>
+      <x:c r="B155" s="9"/>
+      <x:c r="C155" s="1"/>
       <x:c r="D155" s="1"/>
       <x:c r="E155" s="1"/>
       <x:c r="F155" s="1"/>
@@ -3771,18 +3311,15 @@
       <x:c r="K155" s="1"/>
       <x:c r="L155" s="1"/>
       <x:c r="M155" s="1"/>
-      <x:c r="N155" s="1"/>
-      <x:c r="O155" s="1"/>
-      <x:c r="P155" s="1"/>
-      <x:c r="Q155" s="7"/>
-      <x:c r="R155" s="9"/>
-      <x:c r="S155" s="7"/>
-      <x:c r="T155" s="9"/>
+      <x:c r="N155" s="7"/>
+      <x:c r="O155" s="9"/>
+      <x:c r="P155" s="7"/>
+      <x:c r="Q155" s="9"/>
     </x:row>
     <x:row r="156">
-      <x:c r="A156" s="1"/>
-      <x:c r="B156" s="7"/>
-      <x:c r="C156" s="9"/>
+      <x:c r="A156" s="7"/>
+      <x:c r="B156" s="9"/>
+      <x:c r="C156" s="1"/>
       <x:c r="D156" s="1"/>
       <x:c r="E156" s="1"/>
       <x:c r="F156" s="1"/>
@@ -3793,18 +3330,15 @@
       <x:c r="K156" s="1"/>
       <x:c r="L156" s="1"/>
       <x:c r="M156" s="1"/>
-      <x:c r="N156" s="1"/>
-      <x:c r="O156" s="1"/>
-      <x:c r="P156" s="1"/>
-      <x:c r="Q156" s="7"/>
-      <x:c r="R156" s="9"/>
-      <x:c r="S156" s="7"/>
-      <x:c r="T156" s="9"/>
+      <x:c r="N156" s="7"/>
+      <x:c r="O156" s="9"/>
+      <x:c r="P156" s="7"/>
+      <x:c r="Q156" s="9"/>
     </x:row>
     <x:row r="157">
-      <x:c r="A157" s="1"/>
-      <x:c r="B157" s="7"/>
-      <x:c r="C157" s="9"/>
+      <x:c r="A157" s="7"/>
+      <x:c r="B157" s="9"/>
+      <x:c r="C157" s="1"/>
       <x:c r="D157" s="1"/>
       <x:c r="E157" s="1"/>
       <x:c r="F157" s="1"/>
@@ -3815,18 +3349,15 @@
       <x:c r="K157" s="1"/>
       <x:c r="L157" s="1"/>
       <x:c r="M157" s="1"/>
-      <x:c r="N157" s="1"/>
-      <x:c r="O157" s="1"/>
-      <x:c r="P157" s="1"/>
-      <x:c r="Q157" s="7"/>
-      <x:c r="R157" s="9"/>
-      <x:c r="S157" s="7"/>
-      <x:c r="T157" s="9"/>
+      <x:c r="N157" s="7"/>
+      <x:c r="O157" s="9"/>
+      <x:c r="P157" s="7"/>
+      <x:c r="Q157" s="9"/>
     </x:row>
     <x:row r="158">
-      <x:c r="A158" s="1"/>
-      <x:c r="B158" s="7"/>
-      <x:c r="C158" s="9"/>
+      <x:c r="A158" s="7"/>
+      <x:c r="B158" s="9"/>
+      <x:c r="C158" s="1"/>
       <x:c r="D158" s="1"/>
       <x:c r="E158" s="1"/>
       <x:c r="F158" s="1"/>
@@ -3837,18 +3368,15 @@
       <x:c r="K158" s="1"/>
       <x:c r="L158" s="1"/>
       <x:c r="M158" s="1"/>
-      <x:c r="N158" s="1"/>
-      <x:c r="O158" s="1"/>
-      <x:c r="P158" s="1"/>
-      <x:c r="Q158" s="7"/>
-      <x:c r="R158" s="9"/>
-      <x:c r="S158" s="7"/>
-      <x:c r="T158" s="9"/>
+      <x:c r="N158" s="7"/>
+      <x:c r="O158" s="9"/>
+      <x:c r="P158" s="7"/>
+      <x:c r="Q158" s="9"/>
     </x:row>
     <x:row r="159">
-      <x:c r="A159" s="1"/>
-      <x:c r="B159" s="7"/>
-      <x:c r="C159" s="9"/>
+      <x:c r="A159" s="7"/>
+      <x:c r="B159" s="9"/>
+      <x:c r="C159" s="1"/>
       <x:c r="D159" s="1"/>
       <x:c r="E159" s="1"/>
       <x:c r="F159" s="1"/>
@@ -3859,18 +3387,15 @@
       <x:c r="K159" s="1"/>
       <x:c r="L159" s="1"/>
       <x:c r="M159" s="1"/>
-      <x:c r="N159" s="1"/>
-      <x:c r="O159" s="1"/>
-      <x:c r="P159" s="1"/>
-      <x:c r="Q159" s="7"/>
-      <x:c r="R159" s="9"/>
-      <x:c r="S159" s="7"/>
-      <x:c r="T159" s="9"/>
+      <x:c r="N159" s="7"/>
+      <x:c r="O159" s="9"/>
+      <x:c r="P159" s="7"/>
+      <x:c r="Q159" s="9"/>
     </x:row>
     <x:row r="160">
-      <x:c r="A160" s="1"/>
-      <x:c r="B160" s="7"/>
-      <x:c r="C160" s="9"/>
+      <x:c r="A160" s="7"/>
+      <x:c r="B160" s="9"/>
+      <x:c r="C160" s="1"/>
       <x:c r="D160" s="1"/>
       <x:c r="E160" s="1"/>
       <x:c r="F160" s="1"/>
@@ -3881,18 +3406,15 @@
       <x:c r="K160" s="1"/>
       <x:c r="L160" s="1"/>
       <x:c r="M160" s="1"/>
-      <x:c r="N160" s="1"/>
-      <x:c r="O160" s="1"/>
-      <x:c r="P160" s="1"/>
-      <x:c r="Q160" s="7"/>
-      <x:c r="R160" s="9"/>
-      <x:c r="S160" s="7"/>
-      <x:c r="T160" s="9"/>
+      <x:c r="N160" s="7"/>
+      <x:c r="O160" s="9"/>
+      <x:c r="P160" s="7"/>
+      <x:c r="Q160" s="9"/>
     </x:row>
     <x:row r="161">
-      <x:c r="A161" s="1"/>
-      <x:c r="B161" s="7"/>
-      <x:c r="C161" s="9"/>
+      <x:c r="A161" s="7"/>
+      <x:c r="B161" s="9"/>
+      <x:c r="C161" s="1"/>
       <x:c r="D161" s="1"/>
       <x:c r="E161" s="1"/>
       <x:c r="F161" s="1"/>
@@ -3903,18 +3425,15 @@
       <x:c r="K161" s="1"/>
       <x:c r="L161" s="1"/>
       <x:c r="M161" s="1"/>
-      <x:c r="N161" s="1"/>
-      <x:c r="O161" s="1"/>
-      <x:c r="P161" s="1"/>
-      <x:c r="Q161" s="7"/>
-      <x:c r="R161" s="9"/>
-      <x:c r="S161" s="7"/>
-      <x:c r="T161" s="9"/>
+      <x:c r="N161" s="7"/>
+      <x:c r="O161" s="9"/>
+      <x:c r="P161" s="7"/>
+      <x:c r="Q161" s="9"/>
     </x:row>
     <x:row r="162">
-      <x:c r="A162" s="1"/>
-      <x:c r="B162" s="7"/>
-      <x:c r="C162" s="9"/>
+      <x:c r="A162" s="7"/>
+      <x:c r="B162" s="9"/>
+      <x:c r="C162" s="1"/>
       <x:c r="D162" s="1"/>
       <x:c r="E162" s="1"/>
       <x:c r="F162" s="1"/>
@@ -3925,18 +3444,15 @@
       <x:c r="K162" s="1"/>
       <x:c r="L162" s="1"/>
       <x:c r="M162" s="1"/>
-      <x:c r="N162" s="1"/>
-      <x:c r="O162" s="1"/>
-      <x:c r="P162" s="1"/>
-      <x:c r="Q162" s="7"/>
-      <x:c r="R162" s="9"/>
-      <x:c r="S162" s="7"/>
-      <x:c r="T162" s="9"/>
+      <x:c r="N162" s="7"/>
+      <x:c r="O162" s="9"/>
+      <x:c r="P162" s="7"/>
+      <x:c r="Q162" s="9"/>
     </x:row>
     <x:row r="163">
-      <x:c r="A163" s="1"/>
-      <x:c r="B163" s="7"/>
-      <x:c r="C163" s="9"/>
+      <x:c r="A163" s="7"/>
+      <x:c r="B163" s="9"/>
+      <x:c r="C163" s="1"/>
       <x:c r="D163" s="1"/>
       <x:c r="E163" s="1"/>
       <x:c r="F163" s="1"/>
@@ -3947,18 +3463,15 @@
       <x:c r="K163" s="1"/>
       <x:c r="L163" s="1"/>
       <x:c r="M163" s="1"/>
-      <x:c r="N163" s="1"/>
-      <x:c r="O163" s="1"/>
-      <x:c r="P163" s="1"/>
-      <x:c r="Q163" s="7"/>
-      <x:c r="R163" s="9"/>
-      <x:c r="S163" s="7"/>
-      <x:c r="T163" s="9"/>
+      <x:c r="N163" s="7"/>
+      <x:c r="O163" s="9"/>
+      <x:c r="P163" s="7"/>
+      <x:c r="Q163" s="9"/>
     </x:row>
     <x:row r="164">
-      <x:c r="A164" s="1"/>
-      <x:c r="B164" s="7"/>
-      <x:c r="C164" s="9"/>
+      <x:c r="A164" s="7"/>
+      <x:c r="B164" s="9"/>
+      <x:c r="C164" s="1"/>
       <x:c r="D164" s="1"/>
       <x:c r="E164" s="1"/>
       <x:c r="F164" s="1"/>
@@ -3969,18 +3482,15 @@
       <x:c r="K164" s="1"/>
       <x:c r="L164" s="1"/>
       <x:c r="M164" s="1"/>
-      <x:c r="N164" s="1"/>
-      <x:c r="O164" s="1"/>
-      <x:c r="P164" s="1"/>
-      <x:c r="Q164" s="7"/>
-      <x:c r="R164" s="9"/>
-      <x:c r="S164" s="7"/>
-      <x:c r="T164" s="9"/>
+      <x:c r="N164" s="7"/>
+      <x:c r="O164" s="9"/>
+      <x:c r="P164" s="7"/>
+      <x:c r="Q164" s="9"/>
     </x:row>
     <x:row r="165">
-      <x:c r="A165" s="1"/>
-      <x:c r="B165" s="7"/>
-      <x:c r="C165" s="9"/>
+      <x:c r="A165" s="7"/>
+      <x:c r="B165" s="9"/>
+      <x:c r="C165" s="1"/>
       <x:c r="D165" s="1"/>
       <x:c r="E165" s="1"/>
       <x:c r="F165" s="1"/>
@@ -3991,18 +3501,15 @@
       <x:c r="K165" s="1"/>
       <x:c r="L165" s="1"/>
       <x:c r="M165" s="1"/>
-      <x:c r="N165" s="1"/>
-      <x:c r="O165" s="1"/>
-      <x:c r="P165" s="1"/>
-      <x:c r="Q165" s="7"/>
-      <x:c r="R165" s="9"/>
-      <x:c r="S165" s="7"/>
-      <x:c r="T165" s="9"/>
+      <x:c r="N165" s="7"/>
+      <x:c r="O165" s="9"/>
+      <x:c r="P165" s="7"/>
+      <x:c r="Q165" s="9"/>
     </x:row>
     <x:row r="166">
-      <x:c r="A166" s="1"/>
-      <x:c r="B166" s="7"/>
-      <x:c r="C166" s="9"/>
+      <x:c r="A166" s="7"/>
+      <x:c r="B166" s="9"/>
+      <x:c r="C166" s="1"/>
       <x:c r="D166" s="1"/>
       <x:c r="E166" s="1"/>
       <x:c r="F166" s="1"/>
@@ -4013,18 +3520,15 @@
       <x:c r="K166" s="1"/>
       <x:c r="L166" s="1"/>
       <x:c r="M166" s="1"/>
-      <x:c r="N166" s="1"/>
-      <x:c r="O166" s="1"/>
-      <x:c r="P166" s="1"/>
-      <x:c r="Q166" s="7"/>
-      <x:c r="R166" s="9"/>
-      <x:c r="S166" s="7"/>
-      <x:c r="T166" s="9"/>
+      <x:c r="N166" s="7"/>
+      <x:c r="O166" s="9"/>
+      <x:c r="P166" s="7"/>
+      <x:c r="Q166" s="9"/>
     </x:row>
     <x:row r="167">
-      <x:c r="A167" s="1"/>
-      <x:c r="B167" s="7"/>
-      <x:c r="C167" s="9"/>
+      <x:c r="A167" s="7"/>
+      <x:c r="B167" s="9"/>
+      <x:c r="C167" s="1"/>
       <x:c r="D167" s="1"/>
       <x:c r="E167" s="1"/>
       <x:c r="F167" s="1"/>
@@ -4035,18 +3539,15 @@
       <x:c r="K167" s="1"/>
       <x:c r="L167" s="1"/>
       <x:c r="M167" s="1"/>
-      <x:c r="N167" s="1"/>
-      <x:c r="O167" s="1"/>
-      <x:c r="P167" s="1"/>
-      <x:c r="Q167" s="7"/>
-      <x:c r="R167" s="9"/>
-      <x:c r="S167" s="7"/>
-      <x:c r="T167" s="9"/>
+      <x:c r="N167" s="7"/>
+      <x:c r="O167" s="9"/>
+      <x:c r="P167" s="7"/>
+      <x:c r="Q167" s="9"/>
     </x:row>
     <x:row r="168">
-      <x:c r="A168" s="1"/>
-      <x:c r="B168" s="7"/>
-      <x:c r="C168" s="9"/>
+      <x:c r="A168" s="7"/>
+      <x:c r="B168" s="9"/>
+      <x:c r="C168" s="1"/>
       <x:c r="D168" s="1"/>
       <x:c r="E168" s="1"/>
       <x:c r="F168" s="1"/>
@@ -4057,18 +3558,15 @@
       <x:c r="K168" s="1"/>
       <x:c r="L168" s="1"/>
       <x:c r="M168" s="1"/>
-      <x:c r="N168" s="1"/>
-      <x:c r="O168" s="1"/>
-      <x:c r="P168" s="1"/>
-      <x:c r="Q168" s="7"/>
-      <x:c r="R168" s="9"/>
-      <x:c r="S168" s="7"/>
-      <x:c r="T168" s="9"/>
+      <x:c r="N168" s="7"/>
+      <x:c r="O168" s="9"/>
+      <x:c r="P168" s="7"/>
+      <x:c r="Q168" s="9"/>
     </x:row>
     <x:row r="169">
-      <x:c r="A169" s="1"/>
-      <x:c r="B169" s="7"/>
-      <x:c r="C169" s="9"/>
+      <x:c r="A169" s="7"/>
+      <x:c r="B169" s="9"/>
+      <x:c r="C169" s="1"/>
       <x:c r="D169" s="1"/>
       <x:c r="E169" s="1"/>
       <x:c r="F169" s="1"/>
@@ -4079,18 +3577,15 @@
       <x:c r="K169" s="1"/>
       <x:c r="L169" s="1"/>
       <x:c r="M169" s="1"/>
-      <x:c r="N169" s="1"/>
-      <x:c r="O169" s="1"/>
-      <x:c r="P169" s="1"/>
-      <x:c r="Q169" s="7"/>
-      <x:c r="R169" s="9"/>
-      <x:c r="S169" s="7"/>
-      <x:c r="T169" s="9"/>
+      <x:c r="N169" s="7"/>
+      <x:c r="O169" s="9"/>
+      <x:c r="P169" s="7"/>
+      <x:c r="Q169" s="9"/>
     </x:row>
     <x:row r="170">
-      <x:c r="A170" s="1"/>
-      <x:c r="B170" s="7"/>
-      <x:c r="C170" s="9"/>
+      <x:c r="A170" s="7"/>
+      <x:c r="B170" s="9"/>
+      <x:c r="C170" s="1"/>
       <x:c r="D170" s="1"/>
       <x:c r="E170" s="1"/>
       <x:c r="F170" s="1"/>
@@ -4101,18 +3596,15 @@
       <x:c r="K170" s="1"/>
       <x:c r="L170" s="1"/>
       <x:c r="M170" s="1"/>
-      <x:c r="N170" s="1"/>
-      <x:c r="O170" s="1"/>
-      <x:c r="P170" s="1"/>
-      <x:c r="Q170" s="7"/>
-      <x:c r="R170" s="9"/>
-      <x:c r="S170" s="7"/>
-      <x:c r="T170" s="9"/>
+      <x:c r="N170" s="7"/>
+      <x:c r="O170" s="9"/>
+      <x:c r="P170" s="7"/>
+      <x:c r="Q170" s="9"/>
     </x:row>
     <x:row r="171">
-      <x:c r="A171" s="1"/>
-      <x:c r="B171" s="7"/>
-      <x:c r="C171" s="9"/>
+      <x:c r="A171" s="7"/>
+      <x:c r="B171" s="9"/>
+      <x:c r="C171" s="1"/>
       <x:c r="D171" s="1"/>
       <x:c r="E171" s="1"/>
       <x:c r="F171" s="1"/>
@@ -4123,18 +3615,15 @@
       <x:c r="K171" s="1"/>
       <x:c r="L171" s="1"/>
       <x:c r="M171" s="1"/>
-      <x:c r="N171" s="1"/>
-      <x:c r="O171" s="1"/>
-      <x:c r="P171" s="1"/>
-      <x:c r="Q171" s="7"/>
-      <x:c r="R171" s="9"/>
-      <x:c r="S171" s="7"/>
-      <x:c r="T171" s="9"/>
+      <x:c r="N171" s="7"/>
+      <x:c r="O171" s="9"/>
+      <x:c r="P171" s="7"/>
+      <x:c r="Q171" s="9"/>
     </x:row>
     <x:row r="172">
-      <x:c r="A172" s="1"/>
-      <x:c r="B172" s="7"/>
-      <x:c r="C172" s="9"/>
+      <x:c r="A172" s="7"/>
+      <x:c r="B172" s="9"/>
+      <x:c r="C172" s="1"/>
       <x:c r="D172" s="1"/>
       <x:c r="E172" s="1"/>
       <x:c r="F172" s="1"/>
@@ -4145,18 +3634,15 @@
       <x:c r="K172" s="1"/>
       <x:c r="L172" s="1"/>
       <x:c r="M172" s="1"/>
-      <x:c r="N172" s="1"/>
-      <x:c r="O172" s="1"/>
-      <x:c r="P172" s="1"/>
-      <x:c r="Q172" s="7"/>
-      <x:c r="R172" s="9"/>
-      <x:c r="S172" s="7"/>
-      <x:c r="T172" s="9"/>
+      <x:c r="N172" s="7"/>
+      <x:c r="O172" s="9"/>
+      <x:c r="P172" s="7"/>
+      <x:c r="Q172" s="9"/>
     </x:row>
     <x:row r="173">
-      <x:c r="A173" s="1"/>
-      <x:c r="B173" s="7"/>
-      <x:c r="C173" s="9"/>
+      <x:c r="A173" s="7"/>
+      <x:c r="B173" s="9"/>
+      <x:c r="C173" s="1"/>
       <x:c r="D173" s="1"/>
       <x:c r="E173" s="1"/>
       <x:c r="F173" s="1"/>
@@ -4167,18 +3653,15 @@
       <x:c r="K173" s="1"/>
       <x:c r="L173" s="1"/>
       <x:c r="M173" s="1"/>
-      <x:c r="N173" s="1"/>
-      <x:c r="O173" s="1"/>
-      <x:c r="P173" s="1"/>
-      <x:c r="Q173" s="7"/>
-      <x:c r="R173" s="9"/>
-      <x:c r="S173" s="7"/>
-      <x:c r="T173" s="9"/>
+      <x:c r="N173" s="7"/>
+      <x:c r="O173" s="9"/>
+      <x:c r="P173" s="7"/>
+      <x:c r="Q173" s="9"/>
     </x:row>
     <x:row r="174">
-      <x:c r="A174" s="1"/>
-      <x:c r="B174" s="7"/>
-      <x:c r="C174" s="9"/>
+      <x:c r="A174" s="7"/>
+      <x:c r="B174" s="9"/>
+      <x:c r="C174" s="1"/>
       <x:c r="D174" s="1"/>
       <x:c r="E174" s="1"/>
       <x:c r="F174" s="1"/>
@@ -4189,18 +3672,15 @@
       <x:c r="K174" s="1"/>
       <x:c r="L174" s="1"/>
       <x:c r="M174" s="1"/>
-      <x:c r="N174" s="1"/>
-      <x:c r="O174" s="1"/>
-      <x:c r="P174" s="1"/>
-      <x:c r="Q174" s="7"/>
-      <x:c r="R174" s="9"/>
-      <x:c r="S174" s="7"/>
-      <x:c r="T174" s="9"/>
+      <x:c r="N174" s="7"/>
+      <x:c r="O174" s="9"/>
+      <x:c r="P174" s="7"/>
+      <x:c r="Q174" s="9"/>
     </x:row>
     <x:row r="175">
-      <x:c r="A175" s="1"/>
-      <x:c r="B175" s="7"/>
-      <x:c r="C175" s="9"/>
+      <x:c r="A175" s="7"/>
+      <x:c r="B175" s="9"/>
+      <x:c r="C175" s="1"/>
       <x:c r="D175" s="1"/>
       <x:c r="E175" s="1"/>
       <x:c r="F175" s="1"/>
@@ -4211,18 +3691,15 @@
       <x:c r="K175" s="1"/>
       <x:c r="L175" s="1"/>
       <x:c r="M175" s="1"/>
-      <x:c r="N175" s="1"/>
-      <x:c r="O175" s="1"/>
-      <x:c r="P175" s="1"/>
-      <x:c r="Q175" s="7"/>
-      <x:c r="R175" s="9"/>
-      <x:c r="S175" s="7"/>
-      <x:c r="T175" s="9"/>
+      <x:c r="N175" s="7"/>
+      <x:c r="O175" s="9"/>
+      <x:c r="P175" s="7"/>
+      <x:c r="Q175" s="9"/>
     </x:row>
     <x:row r="176">
-      <x:c r="A176" s="1"/>
-      <x:c r="B176" s="7"/>
-      <x:c r="C176" s="9"/>
+      <x:c r="A176" s="7"/>
+      <x:c r="B176" s="9"/>
+      <x:c r="C176" s="1"/>
       <x:c r="D176" s="1"/>
       <x:c r="E176" s="1"/>
       <x:c r="F176" s="1"/>
@@ -4233,18 +3710,15 @@
       <x:c r="K176" s="1"/>
       <x:c r="L176" s="1"/>
       <x:c r="M176" s="1"/>
-      <x:c r="N176" s="1"/>
-      <x:c r="O176" s="1"/>
-      <x:c r="P176" s="1"/>
-      <x:c r="Q176" s="7"/>
-      <x:c r="R176" s="9"/>
-      <x:c r="S176" s="7"/>
-      <x:c r="T176" s="9"/>
+      <x:c r="N176" s="7"/>
+      <x:c r="O176" s="9"/>
+      <x:c r="P176" s="7"/>
+      <x:c r="Q176" s="9"/>
     </x:row>
     <x:row r="177">
-      <x:c r="A177" s="1"/>
-      <x:c r="B177" s="7"/>
-      <x:c r="C177" s="9"/>
+      <x:c r="A177" s="7"/>
+      <x:c r="B177" s="9"/>
+      <x:c r="C177" s="1"/>
       <x:c r="D177" s="1"/>
       <x:c r="E177" s="1"/>
       <x:c r="F177" s="1"/>
@@ -4255,18 +3729,15 @@
       <x:c r="K177" s="1"/>
       <x:c r="L177" s="1"/>
       <x:c r="M177" s="1"/>
-      <x:c r="N177" s="1"/>
-      <x:c r="O177" s="1"/>
-      <x:c r="P177" s="1"/>
-      <x:c r="Q177" s="7"/>
-      <x:c r="R177" s="9"/>
-      <x:c r="S177" s="7"/>
-      <x:c r="T177" s="9"/>
+      <x:c r="N177" s="7"/>
+      <x:c r="O177" s="9"/>
+      <x:c r="P177" s="7"/>
+      <x:c r="Q177" s="9"/>
     </x:row>
     <x:row r="178">
-      <x:c r="A178" s="1"/>
-      <x:c r="B178" s="7"/>
-      <x:c r="C178" s="9"/>
+      <x:c r="A178" s="7"/>
+      <x:c r="B178" s="9"/>
+      <x:c r="C178" s="1"/>
       <x:c r="D178" s="1"/>
       <x:c r="E178" s="1"/>
       <x:c r="F178" s="1"/>
@@ -4277,18 +3748,15 @@
       <x:c r="K178" s="1"/>
       <x:c r="L178" s="1"/>
       <x:c r="M178" s="1"/>
-      <x:c r="N178" s="1"/>
-      <x:c r="O178" s="1"/>
-      <x:c r="P178" s="1"/>
-      <x:c r="Q178" s="7"/>
-      <x:c r="R178" s="9"/>
-      <x:c r="S178" s="7"/>
-      <x:c r="T178" s="9"/>
+      <x:c r="N178" s="7"/>
+      <x:c r="O178" s="9"/>
+      <x:c r="P178" s="7"/>
+      <x:c r="Q178" s="9"/>
     </x:row>
     <x:row r="179">
-      <x:c r="A179" s="1"/>
-      <x:c r="B179" s="7"/>
-      <x:c r="C179" s="9"/>
+      <x:c r="A179" s="7"/>
+      <x:c r="B179" s="9"/>
+      <x:c r="C179" s="1"/>
       <x:c r="D179" s="1"/>
       <x:c r="E179" s="1"/>
       <x:c r="F179" s="1"/>
@@ -4299,18 +3767,15 @@
       <x:c r="K179" s="1"/>
       <x:c r="L179" s="1"/>
       <x:c r="M179" s="1"/>
-      <x:c r="N179" s="1"/>
-      <x:c r="O179" s="1"/>
-      <x:c r="P179" s="1"/>
-      <x:c r="Q179" s="7"/>
-      <x:c r="R179" s="9"/>
-      <x:c r="S179" s="7"/>
-      <x:c r="T179" s="9"/>
+      <x:c r="N179" s="7"/>
+      <x:c r="O179" s="9"/>
+      <x:c r="P179" s="7"/>
+      <x:c r="Q179" s="9"/>
     </x:row>
     <x:row r="180">
-      <x:c r="A180" s="1"/>
-      <x:c r="B180" s="7"/>
-      <x:c r="C180" s="9"/>
+      <x:c r="A180" s="7"/>
+      <x:c r="B180" s="9"/>
+      <x:c r="C180" s="1"/>
       <x:c r="D180" s="1"/>
       <x:c r="E180" s="1"/>
       <x:c r="F180" s="1"/>
@@ -4321,18 +3786,15 @@
       <x:c r="K180" s="1"/>
       <x:c r="L180" s="1"/>
       <x:c r="M180" s="1"/>
-      <x:c r="N180" s="1"/>
-      <x:c r="O180" s="1"/>
-      <x:c r="P180" s="1"/>
-      <x:c r="Q180" s="7"/>
-      <x:c r="R180" s="9"/>
-      <x:c r="S180" s="7"/>
-      <x:c r="T180" s="9"/>
+      <x:c r="N180" s="7"/>
+      <x:c r="O180" s="9"/>
+      <x:c r="P180" s="7"/>
+      <x:c r="Q180" s="9"/>
     </x:row>
     <x:row r="181">
-      <x:c r="A181" s="1"/>
-      <x:c r="B181" s="7"/>
-      <x:c r="C181" s="9"/>
+      <x:c r="A181" s="7"/>
+      <x:c r="B181" s="9"/>
+      <x:c r="C181" s="1"/>
       <x:c r="D181" s="1"/>
       <x:c r="E181" s="1"/>
       <x:c r="F181" s="1"/>
@@ -4343,18 +3805,15 @@
       <x:c r="K181" s="1"/>
       <x:c r="L181" s="1"/>
       <x:c r="M181" s="1"/>
-      <x:c r="N181" s="1"/>
-      <x:c r="O181" s="1"/>
-      <x:c r="P181" s="1"/>
-      <x:c r="Q181" s="7"/>
-      <x:c r="R181" s="9"/>
-      <x:c r="S181" s="7"/>
-      <x:c r="T181" s="9"/>
+      <x:c r="N181" s="7"/>
+      <x:c r="O181" s="9"/>
+      <x:c r="P181" s="7"/>
+      <x:c r="Q181" s="9"/>
     </x:row>
     <x:row r="182">
-      <x:c r="A182" s="1"/>
-      <x:c r="B182" s="7"/>
-      <x:c r="C182" s="9"/>
+      <x:c r="A182" s="7"/>
+      <x:c r="B182" s="9"/>
+      <x:c r="C182" s="1"/>
       <x:c r="D182" s="1"/>
       <x:c r="E182" s="1"/>
       <x:c r="F182" s="1"/>
@@ -4365,18 +3824,15 @@
       <x:c r="K182" s="1"/>
       <x:c r="L182" s="1"/>
       <x:c r="M182" s="1"/>
-      <x:c r="N182" s="1"/>
-      <x:c r="O182" s="1"/>
-      <x:c r="P182" s="1"/>
-      <x:c r="Q182" s="7"/>
-      <x:c r="R182" s="9"/>
-      <x:c r="S182" s="7"/>
-      <x:c r="T182" s="9"/>
+      <x:c r="N182" s="7"/>
+      <x:c r="O182" s="9"/>
+      <x:c r="P182" s="7"/>
+      <x:c r="Q182" s="9"/>
     </x:row>
     <x:row r="183">
-      <x:c r="A183" s="1"/>
-      <x:c r="B183" s="7"/>
-      <x:c r="C183" s="9"/>
+      <x:c r="A183" s="7"/>
+      <x:c r="B183" s="9"/>
+      <x:c r="C183" s="1"/>
       <x:c r="D183" s="1"/>
       <x:c r="E183" s="1"/>
       <x:c r="F183" s="1"/>
@@ -4387,18 +3843,15 @@
       <x:c r="K183" s="1"/>
       <x:c r="L183" s="1"/>
       <x:c r="M183" s="1"/>
-      <x:c r="N183" s="1"/>
-      <x:c r="O183" s="1"/>
-      <x:c r="P183" s="1"/>
-      <x:c r="Q183" s="7"/>
-      <x:c r="R183" s="9"/>
-      <x:c r="S183" s="7"/>
-      <x:c r="T183" s="9"/>
+      <x:c r="N183" s="7"/>
+      <x:c r="O183" s="9"/>
+      <x:c r="P183" s="7"/>
+      <x:c r="Q183" s="9"/>
     </x:row>
     <x:row r="184">
-      <x:c r="A184" s="1"/>
-      <x:c r="B184" s="7"/>
-      <x:c r="C184" s="9"/>
+      <x:c r="A184" s="7"/>
+      <x:c r="B184" s="9"/>
+      <x:c r="C184" s="1"/>
       <x:c r="D184" s="1"/>
       <x:c r="E184" s="1"/>
       <x:c r="F184" s="1"/>
@@ -4409,18 +3862,15 @@
       <x:c r="K184" s="1"/>
       <x:c r="L184" s="1"/>
       <x:c r="M184" s="1"/>
-      <x:c r="N184" s="1"/>
-      <x:c r="O184" s="1"/>
-      <x:c r="P184" s="1"/>
-      <x:c r="Q184" s="7"/>
-      <x:c r="R184" s="9"/>
-      <x:c r="S184" s="7"/>
-      <x:c r="T184" s="9"/>
+      <x:c r="N184" s="7"/>
+      <x:c r="O184" s="9"/>
+      <x:c r="P184" s="7"/>
+      <x:c r="Q184" s="9"/>
     </x:row>
     <x:row r="185">
-      <x:c r="A185" s="1"/>
-      <x:c r="B185" s="7"/>
-      <x:c r="C185" s="9"/>
+      <x:c r="A185" s="7"/>
+      <x:c r="B185" s="9"/>
+      <x:c r="C185" s="1"/>
       <x:c r="D185" s="1"/>
       <x:c r="E185" s="1"/>
       <x:c r="F185" s="1"/>
@@ -4431,18 +3881,15 @@
       <x:c r="K185" s="1"/>
       <x:c r="L185" s="1"/>
       <x:c r="M185" s="1"/>
-      <x:c r="N185" s="1"/>
-      <x:c r="O185" s="1"/>
-      <x:c r="P185" s="1"/>
-      <x:c r="Q185" s="7"/>
-      <x:c r="R185" s="9"/>
-      <x:c r="S185" s="7"/>
-      <x:c r="T185" s="9"/>
+      <x:c r="N185" s="7"/>
+      <x:c r="O185" s="9"/>
+      <x:c r="P185" s="7"/>
+      <x:c r="Q185" s="9"/>
     </x:row>
     <x:row r="186">
-      <x:c r="A186" s="1"/>
-      <x:c r="B186" s="7"/>
-      <x:c r="C186" s="9"/>
+      <x:c r="A186" s="7"/>
+      <x:c r="B186" s="9"/>
+      <x:c r="C186" s="1"/>
       <x:c r="D186" s="1"/>
       <x:c r="E186" s="1"/>
       <x:c r="F186" s="1"/>
@@ -4453,18 +3900,15 @@
       <x:c r="K186" s="1"/>
       <x:c r="L186" s="1"/>
       <x:c r="M186" s="1"/>
-      <x:c r="N186" s="1"/>
-      <x:c r="O186" s="1"/>
-      <x:c r="P186" s="1"/>
-      <x:c r="Q186" s="7"/>
-      <x:c r="R186" s="9"/>
-      <x:c r="S186" s="7"/>
-      <x:c r="T186" s="9"/>
+      <x:c r="N186" s="7"/>
+      <x:c r="O186" s="9"/>
+      <x:c r="P186" s="7"/>
+      <x:c r="Q186" s="9"/>
     </x:row>
     <x:row r="187">
-      <x:c r="A187" s="1"/>
-      <x:c r="B187" s="7"/>
-      <x:c r="C187" s="9"/>
+      <x:c r="A187" s="7"/>
+      <x:c r="B187" s="9"/>
+      <x:c r="C187" s="1"/>
       <x:c r="D187" s="1"/>
       <x:c r="E187" s="1"/>
       <x:c r="F187" s="1"/>
@@ -4475,18 +3919,15 @@
       <x:c r="K187" s="1"/>
       <x:c r="L187" s="1"/>
       <x:c r="M187" s="1"/>
-      <x:c r="N187" s="1"/>
-      <x:c r="O187" s="1"/>
-      <x:c r="P187" s="1"/>
-      <x:c r="Q187" s="7"/>
-      <x:c r="R187" s="9"/>
-      <x:c r="S187" s="7"/>
-      <x:c r="T187" s="9"/>
+      <x:c r="N187" s="7"/>
+      <x:c r="O187" s="9"/>
+      <x:c r="P187" s="7"/>
+      <x:c r="Q187" s="9"/>
     </x:row>
     <x:row r="188">
-      <x:c r="A188" s="1"/>
-      <x:c r="B188" s="7"/>
-      <x:c r="C188" s="9"/>
+      <x:c r="A188" s="7"/>
+      <x:c r="B188" s="9"/>
+      <x:c r="C188" s="1"/>
       <x:c r="D188" s="1"/>
       <x:c r="E188" s="1"/>
       <x:c r="F188" s="1"/>
@@ -4497,18 +3938,15 @@
       <x:c r="K188" s="1"/>
       <x:c r="L188" s="1"/>
       <x:c r="M188" s="1"/>
-      <x:c r="N188" s="1"/>
-      <x:c r="O188" s="1"/>
-      <x:c r="P188" s="1"/>
-      <x:c r="Q188" s="7"/>
-      <x:c r="R188" s="9"/>
-      <x:c r="S188" s="7"/>
-      <x:c r="T188" s="9"/>
+      <x:c r="N188" s="7"/>
+      <x:c r="O188" s="9"/>
+      <x:c r="P188" s="7"/>
+      <x:c r="Q188" s="9"/>
     </x:row>
     <x:row r="189">
-      <x:c r="A189" s="1"/>
-      <x:c r="B189" s="7"/>
-      <x:c r="C189" s="9"/>
+      <x:c r="A189" s="7"/>
+      <x:c r="B189" s="9"/>
+      <x:c r="C189" s="1"/>
       <x:c r="D189" s="1"/>
       <x:c r="E189" s="1"/>
       <x:c r="F189" s="1"/>
@@ -4519,18 +3957,15 @@
       <x:c r="K189" s="1"/>
       <x:c r="L189" s="1"/>
       <x:c r="M189" s="1"/>
-      <x:c r="N189" s="1"/>
-      <x:c r="O189" s="1"/>
-      <x:c r="P189" s="1"/>
-      <x:c r="Q189" s="7"/>
-      <x:c r="R189" s="9"/>
-      <x:c r="S189" s="7"/>
-      <x:c r="T189" s="9"/>
+      <x:c r="N189" s="7"/>
+      <x:c r="O189" s="9"/>
+      <x:c r="P189" s="7"/>
+      <x:c r="Q189" s="9"/>
     </x:row>
     <x:row r="190">
-      <x:c r="A190" s="1"/>
-      <x:c r="B190" s="7"/>
-      <x:c r="C190" s="9"/>
+      <x:c r="A190" s="7"/>
+      <x:c r="B190" s="9"/>
+      <x:c r="C190" s="1"/>
       <x:c r="D190" s="1"/>
       <x:c r="E190" s="1"/>
       <x:c r="F190" s="1"/>
@@ -4541,18 +3976,15 @@
       <x:c r="K190" s="1"/>
       <x:c r="L190" s="1"/>
       <x:c r="M190" s="1"/>
-      <x:c r="N190" s="1"/>
-      <x:c r="O190" s="1"/>
-      <x:c r="P190" s="1"/>
-      <x:c r="Q190" s="7"/>
-      <x:c r="R190" s="9"/>
-      <x:c r="S190" s="7"/>
-      <x:c r="T190" s="9"/>
+      <x:c r="N190" s="7"/>
+      <x:c r="O190" s="9"/>
+      <x:c r="P190" s="7"/>
+      <x:c r="Q190" s="9"/>
     </x:row>
     <x:row r="191">
-      <x:c r="A191" s="1"/>
-      <x:c r="B191" s="7"/>
-      <x:c r="C191" s="9"/>
+      <x:c r="A191" s="7"/>
+      <x:c r="B191" s="9"/>
+      <x:c r="C191" s="1"/>
       <x:c r="D191" s="1"/>
       <x:c r="E191" s="1"/>
       <x:c r="F191" s="1"/>
@@ -4563,18 +3995,15 @@
       <x:c r="K191" s="1"/>
       <x:c r="L191" s="1"/>
       <x:c r="M191" s="1"/>
-      <x:c r="N191" s="1"/>
-      <x:c r="O191" s="1"/>
-      <x:c r="P191" s="1"/>
-      <x:c r="Q191" s="7"/>
-      <x:c r="R191" s="9"/>
-      <x:c r="S191" s="7"/>
-      <x:c r="T191" s="9"/>
+      <x:c r="N191" s="7"/>
+      <x:c r="O191" s="9"/>
+      <x:c r="P191" s="7"/>
+      <x:c r="Q191" s="9"/>
     </x:row>
     <x:row r="192">
-      <x:c r="A192" s="1"/>
-      <x:c r="B192" s="7"/>
-      <x:c r="C192" s="9"/>
+      <x:c r="A192" s="7"/>
+      <x:c r="B192" s="9"/>
+      <x:c r="C192" s="1"/>
       <x:c r="D192" s="1"/>
       <x:c r="E192" s="1"/>
       <x:c r="F192" s="1"/>
@@ -4585,18 +4014,15 @@
       <x:c r="K192" s="1"/>
       <x:c r="L192" s="1"/>
       <x:c r="M192" s="1"/>
-      <x:c r="N192" s="1"/>
-      <x:c r="O192" s="1"/>
-      <x:c r="P192" s="1"/>
-      <x:c r="Q192" s="7"/>
-      <x:c r="R192" s="9"/>
-      <x:c r="S192" s="7"/>
-      <x:c r="T192" s="9"/>
+      <x:c r="N192" s="7"/>
+      <x:c r="O192" s="9"/>
+      <x:c r="P192" s="7"/>
+      <x:c r="Q192" s="9"/>
     </x:row>
     <x:row r="193">
-      <x:c r="A193" s="1"/>
-      <x:c r="B193" s="7"/>
-      <x:c r="C193" s="9"/>
+      <x:c r="A193" s="7"/>
+      <x:c r="B193" s="9"/>
+      <x:c r="C193" s="1"/>
       <x:c r="D193" s="1"/>
       <x:c r="E193" s="1"/>
       <x:c r="F193" s="1"/>
@@ -4607,18 +4033,15 @@
       <x:c r="K193" s="1"/>
       <x:c r="L193" s="1"/>
       <x:c r="M193" s="1"/>
-      <x:c r="N193" s="1"/>
-      <x:c r="O193" s="1"/>
-      <x:c r="P193" s="1"/>
-      <x:c r="Q193" s="7"/>
-      <x:c r="R193" s="9"/>
-      <x:c r="S193" s="7"/>
-      <x:c r="T193" s="9"/>
+      <x:c r="N193" s="7"/>
+      <x:c r="O193" s="9"/>
+      <x:c r="P193" s="7"/>
+      <x:c r="Q193" s="9"/>
     </x:row>
     <x:row r="194">
-      <x:c r="A194" s="1"/>
-      <x:c r="B194" s="7"/>
-      <x:c r="C194" s="9"/>
+      <x:c r="A194" s="7"/>
+      <x:c r="B194" s="9"/>
+      <x:c r="C194" s="1"/>
       <x:c r="D194" s="1"/>
       <x:c r="E194" s="1"/>
       <x:c r="F194" s="1"/>
@@ -4629,18 +4052,15 @@
       <x:c r="K194" s="1"/>
       <x:c r="L194" s="1"/>
       <x:c r="M194" s="1"/>
-      <x:c r="N194" s="1"/>
-      <x:c r="O194" s="1"/>
-      <x:c r="P194" s="1"/>
-      <x:c r="Q194" s="7"/>
-      <x:c r="R194" s="9"/>
-      <x:c r="S194" s="7"/>
-      <x:c r="T194" s="9"/>
+      <x:c r="N194" s="7"/>
+      <x:c r="O194" s="9"/>
+      <x:c r="P194" s="7"/>
+      <x:c r="Q194" s="9"/>
     </x:row>
     <x:row r="195">
-      <x:c r="A195" s="1"/>
-      <x:c r="B195" s="7"/>
-      <x:c r="C195" s="9"/>
+      <x:c r="A195" s="7"/>
+      <x:c r="B195" s="9"/>
+      <x:c r="C195" s="1"/>
       <x:c r="D195" s="1"/>
       <x:c r="E195" s="1"/>
       <x:c r="F195" s="1"/>
@@ -4651,18 +4071,15 @@
       <x:c r="K195" s="1"/>
       <x:c r="L195" s="1"/>
       <x:c r="M195" s="1"/>
-      <x:c r="N195" s="1"/>
-      <x:c r="O195" s="1"/>
-      <x:c r="P195" s="1"/>
-      <x:c r="Q195" s="7"/>
-      <x:c r="R195" s="9"/>
-      <x:c r="S195" s="7"/>
-      <x:c r="T195" s="9"/>
+      <x:c r="N195" s="7"/>
+      <x:c r="O195" s="9"/>
+      <x:c r="P195" s="7"/>
+      <x:c r="Q195" s="9"/>
     </x:row>
     <x:row r="196">
-      <x:c r="A196" s="1"/>
-      <x:c r="B196" s="7"/>
-      <x:c r="C196" s="9"/>
+      <x:c r="A196" s="7"/>
+      <x:c r="B196" s="9"/>
+      <x:c r="C196" s="1"/>
       <x:c r="D196" s="1"/>
       <x:c r="E196" s="1"/>
       <x:c r="F196" s="1"/>
@@ -4673,18 +4090,15 @@
       <x:c r="K196" s="1"/>
       <x:c r="L196" s="1"/>
       <x:c r="M196" s="1"/>
-      <x:c r="N196" s="1"/>
-      <x:c r="O196" s="1"/>
-      <x:c r="P196" s="1"/>
-      <x:c r="Q196" s="7"/>
-      <x:c r="R196" s="9"/>
-      <x:c r="S196" s="7"/>
-      <x:c r="T196" s="9"/>
+      <x:c r="N196" s="7"/>
+      <x:c r="O196" s="9"/>
+      <x:c r="P196" s="7"/>
+      <x:c r="Q196" s="9"/>
     </x:row>
     <x:row r="197">
-      <x:c r="A197" s="1"/>
-      <x:c r="B197" s="7"/>
-      <x:c r="C197" s="9"/>
+      <x:c r="A197" s="7"/>
+      <x:c r="B197" s="9"/>
+      <x:c r="C197" s="1"/>
       <x:c r="D197" s="1"/>
       <x:c r="E197" s="1"/>
       <x:c r="F197" s="1"/>
@@ -4695,18 +4109,15 @@
       <x:c r="K197" s="1"/>
       <x:c r="L197" s="1"/>
       <x:c r="M197" s="1"/>
-      <x:c r="N197" s="1"/>
-      <x:c r="O197" s="1"/>
-      <x:c r="P197" s="1"/>
-      <x:c r="Q197" s="7"/>
-      <x:c r="R197" s="9"/>
-      <x:c r="S197" s="7"/>
-      <x:c r="T197" s="9"/>
+      <x:c r="N197" s="7"/>
+      <x:c r="O197" s="9"/>
+      <x:c r="P197" s="7"/>
+      <x:c r="Q197" s="9"/>
     </x:row>
     <x:row r="198">
-      <x:c r="A198" s="1"/>
-      <x:c r="B198" s="7"/>
-      <x:c r="C198" s="9"/>
+      <x:c r="A198" s="7"/>
+      <x:c r="B198" s="9"/>
+      <x:c r="C198" s="1"/>
       <x:c r="D198" s="1"/>
       <x:c r="E198" s="1"/>
       <x:c r="F198" s="1"/>
@@ -4717,18 +4128,15 @@
       <x:c r="K198" s="1"/>
       <x:c r="L198" s="1"/>
       <x:c r="M198" s="1"/>
-      <x:c r="N198" s="1"/>
-      <x:c r="O198" s="1"/>
-      <x:c r="P198" s="1"/>
-      <x:c r="Q198" s="7"/>
-      <x:c r="R198" s="9"/>
-      <x:c r="S198" s="7"/>
-      <x:c r="T198" s="9"/>
+      <x:c r="N198" s="7"/>
+      <x:c r="O198" s="9"/>
+      <x:c r="P198" s="7"/>
+      <x:c r="Q198" s="9"/>
     </x:row>
     <x:row r="199">
-      <x:c r="A199" s="1"/>
-      <x:c r="B199" s="7"/>
-      <x:c r="C199" s="9"/>
+      <x:c r="A199" s="7"/>
+      <x:c r="B199" s="9"/>
+      <x:c r="C199" s="1"/>
       <x:c r="D199" s="1"/>
       <x:c r="E199" s="1"/>
       <x:c r="F199" s="1"/>
@@ -4739,18 +4147,15 @@
       <x:c r="K199" s="1"/>
       <x:c r="L199" s="1"/>
       <x:c r="M199" s="1"/>
-      <x:c r="N199" s="1"/>
-      <x:c r="O199" s="1"/>
-      <x:c r="P199" s="1"/>
-      <x:c r="Q199" s="7"/>
-      <x:c r="R199" s="9"/>
-      <x:c r="S199" s="7"/>
-      <x:c r="T199" s="9"/>
+      <x:c r="N199" s="7"/>
+      <x:c r="O199" s="9"/>
+      <x:c r="P199" s="7"/>
+      <x:c r="Q199" s="9"/>
     </x:row>
     <x:row r="200">
-      <x:c r="A200" s="1"/>
-      <x:c r="B200" s="7"/>
-      <x:c r="C200" s="9"/>
+      <x:c r="A200" s="7"/>
+      <x:c r="B200" s="9"/>
+      <x:c r="C200" s="1"/>
       <x:c r="D200" s="1"/>
       <x:c r="E200" s="1"/>
       <x:c r="F200" s="1"/>
@@ -4761,18 +4166,15 @@
       <x:c r="K200" s="1"/>
       <x:c r="L200" s="1"/>
       <x:c r="M200" s="1"/>
-      <x:c r="N200" s="1"/>
-      <x:c r="O200" s="1"/>
-      <x:c r="P200" s="1"/>
-      <x:c r="Q200" s="7"/>
-      <x:c r="R200" s="9"/>
-      <x:c r="S200" s="7"/>
-      <x:c r="T200" s="9"/>
+      <x:c r="N200" s="7"/>
+      <x:c r="O200" s="9"/>
+      <x:c r="P200" s="7"/>
+      <x:c r="Q200" s="9"/>
     </x:row>
     <x:row r="201">
-      <x:c r="A201" s="1"/>
-      <x:c r="B201" s="7"/>
-      <x:c r="C201" s="9"/>
+      <x:c r="A201" s="7"/>
+      <x:c r="B201" s="9"/>
+      <x:c r="C201" s="1"/>
       <x:c r="D201" s="1"/>
       <x:c r="E201" s="1"/>
       <x:c r="F201" s="1"/>
@@ -4783,30 +4185,65 @@
       <x:c r="K201" s="1"/>
       <x:c r="L201" s="1"/>
       <x:c r="M201" s="1"/>
-      <x:c r="N201" s="1"/>
-      <x:c r="O201" s="1"/>
-      <x:c r="P201" s="1"/>
-      <x:c r="Q201" s="7"/>
-      <x:c r="R201" s="9"/>
-      <x:c r="S201" s="7"/>
-      <x:c r="T201" s="9"/>
+      <x:c r="N201" s="7"/>
+      <x:c r="O201" s="9"/>
+      <x:c r="P201" s="7"/>
+      <x:c r="Q201" s="9"/>
+    </x:row>
+    <x:row r="202">
+      <x:c r="A202" s="7"/>
+      <x:c r="B202" s="9"/>
+      <x:c r="C202" s="1"/>
+      <x:c r="D202" s="1"/>
+      <x:c r="E202" s="1"/>
+      <x:c r="F202" s="1"/>
+      <x:c r="G202" s="1"/>
+      <x:c r="H202" s="1"/>
+      <x:c r="I202" s="1"/>
+      <x:c r="J202" s="1"/>
+      <x:c r="K202" s="1"/>
+      <x:c r="L202" s="1"/>
+      <x:c r="M202" s="1"/>
+      <x:c r="N202" s="7"/>
+      <x:c r="O202" s="9"/>
+      <x:c r="P202" s="7"/>
+      <x:c r="Q202" s="9"/>
+    </x:row>
+    <x:row r="203">
+      <x:c r="A203" s="7"/>
+      <x:c r="B203" s="9"/>
+      <x:c r="C203" s="1"/>
+      <x:c r="D203" s="1"/>
+      <x:c r="E203" s="1"/>
+      <x:c r="F203" s="1"/>
+      <x:c r="G203" s="1"/>
+      <x:c r="H203" s="1"/>
+      <x:c r="I203" s="1"/>
+      <x:c r="J203" s="1"/>
+      <x:c r="K203" s="1"/>
+      <x:c r="L203" s="1"/>
+      <x:c r="M203" s="1"/>
+      <x:c r="N203" s="7"/>
+      <x:c r="O203" s="9"/>
+      <x:c r="P203" s="7"/>
+      <x:c r="Q203" s="9"/>
     </x:row>
   </x:sheetData>
-  <x:dataValidations count="5">
-    <x:dataValidation type="list" sqref="A2:A201">
-      <x:formula1>"导入,示例"</x:formula1>
-    </x:dataValidation>
-    <x:dataValidation type="list" sqref="H2:H201">
+  <x:mergeCells>
+    <x:mergeCell ref="A2:F2"/>
+  </x:mergeCells>
+  <x:dataValidations count="4">
+    <x:dataValidation type="list" sqref="G3:G203">
       <x:formula1>"演出舞台,影视宣传,站台活动,颁奖红毯,线上直播,其他"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" sqref="I2:I201">
+    <x:dataValidation type="list" sqref="H3:H203">
       <x:formula1>"中国,泰国,其他国家或地区,线上"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" sqref="K2:K201">
+    <x:dataValidation type="list" sqref="I3:I203">
+      <x:formula1>"无限制,需预先填表,仅限购票者,仅限资格者,仅限受邀"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="J3:J203">
       <x:formula1>"是,否"</x:formula1>
-    </x:dataValidation>
-    <x:dataValidation type="list" sqref="P2:P201">
-      <x:formula1>"演员,歌手,CP,组合,乐队,BL,GL,其他"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4834,7 +4271,7 @@
         <x:v>开始填写</x:v>
       </x:c>
       <x:c r="B2" s="2" t="str">
-        <x:v>第一张表第 2 行为示例。替换真实内容后，把行用途改为“导入”；保持“示例”会跳过此行。</x:v>
+        <x:v>删除提示行和示例活动，保留英文表头后填写真实内容。</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="48" customHeight="1">
@@ -4842,7 +4279,7 @@
         <x:v>艺人名称</x:v>
       </x:c>
       <x:c r="B3" s="2" t="str">
-        <x:v>先在后台艺人资料库建立资料。填写名称、显示名称或唯一别名；多人用英文分号分隔。</x:v>
+        <x:v>多位艺人用 / 分隔。公司和艺人类别由后台资料自动带出；未匹配名称可先导入草稿再匹配。</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="48" customHeight="1">
@@ -4890,7 +4327,7 @@
         <x:v>开票信息</x:v>
       </x:c>
       <x:c r="B9" s="2" t="str">
-        <x:v>没有开票事项可全部留空；填写时需有开票日期，开始和结束时间填 HH:mm。</x:v>
+        <x:v>没有开票事项可全部留空；填写时需有开票日期；结束可留空，表示售完即止。</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="48" customHeight="1">
@@ -4898,7 +4335,7 @@
         <x:v>导入与发布</x:v>
       </x:c>
       <x:c r="B10" s="2" t="str">
-        <x:v>每批最多 200 条。先查看预览中的错误，修正后导入为草稿，再在后台检查并发布。</x:v>
+        <x:v>每批最多 200 条。可在预览中直接修正，也可先导入可导入的行，剩余行继续修改。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/public/templates/events-import.xlsx
+++ b/public/templates/events-import.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="活动导入" sheetId="1" r:id="R1e2e94096a51434e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="填写说明" sheetId="2" r:id="R8515639d00464497"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="活动导入" sheetId="1" r:id="R6defe0a624d440f9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="填写说明" sheetId="2" r:id="R9bbc751da35a484a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -393,7 +393,7 @@
         <x:v>0.7916666666666666</x:v>
       </x:c>
       <x:c r="C3" s="5" t="str">
-        <x:v>Auau Thanaphum / Patji Jirachart / Ryujin Tinnapat / Save Worapong</x:v>
+        <x:v>AuAuSave / RyujinPatji</x:v>
       </x:c>
       <x:c r="D3" s="5" t="str">
         <x:v>Flex Talk电台</x:v>
@@ -4279,7 +4279,7 @@
         <x:v>艺人名称</x:v>
       </x:c>
       <x:c r="B3" s="2" t="str">
-        <x:v>多位艺人用 / 分隔。公司和艺人类别由后台资料自动带出；未匹配名称可先导入草稿再匹配。</x:v>
+        <x:v>CP 直接填写后台 CP 名称，不展开成员全名；多位艺人或 CP 用 / 分隔。公司和艺人类别由后台资料自动带出；未匹配名称可先导入草稿再匹配。</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="48" customHeight="1">

--- a/public/templates/events-import.xlsx
+++ b/public/templates/events-import.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="活动导入" sheetId="1" r:id="R6defe0a624d440f9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="填写说明" sheetId="2" r:id="R9bbc751da35a484a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="活动导入" sheetId="1" r:id="R7d87dd5f411d44d4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="填写说明" sheetId="2" r:id="R261203150ae144a8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -4234,7 +4234,7 @@
   </x:mergeCells>
   <x:dataValidations count="4">
     <x:dataValidation type="list" sqref="G3:G203">
-      <x:formula1>"演出舞台,影视宣传,站台活动,颁奖红毯,线上直播,其他"</x:formula1>
+      <x:formula1>"演出舞台,影视宣传,见面会/签售,发布会/记者会,站台活动,颁奖红毯,线上直播,其他"</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" sqref="H3:H203">
       <x:formula1>"中国,泰国,其他国家或地区,线上"</x:formula1>
